--- a/raid_config.xlsx
+++ b/raid_config.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\new_bot\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{41A9981C-2B2A-4754-98C8-4678EEF3C0DE}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D37F5637-C477-4FC6-8E59-3BD920C337F8}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="1725" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="레이드설정" sheetId="1" r:id="rId1"/>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="235" uniqueCount="136">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="244" uniqueCount="138">
   <si>
     <t>활성화여부</t>
   </si>
@@ -170,15 +170,9 @@
     <t>헤티아</t>
   </si>
   <si>
-    <t>어리석은놈.. 겨우이정도밖에안되는거냐?</t>
-  </si>
-  <si>
     <t>일어나 다시나를위해싸워라</t>
   </si>
   <si>
-    <t>X</t>
-  </si>
-  <si>
     <t>지옥3</t>
   </si>
   <si>
@@ -186,21 +180,6 @@
   </si>
   <si>
     <t>B71C1C</t>
-  </si>
-  <si>
-    <t>모가로스</t>
-  </si>
-  <si>
-    <t>하하하.. 이것이 진정한 힘이다</t>
-  </si>
-  <si>
-    <t>어둠이여 일어나라!</t>
-  </si>
-  <si>
-    <t>미련한것들.. 최후를 맞이하여라</t>
-  </si>
-  <si>
-    <t>이것이 마지막이다!</t>
   </si>
   <si>
     <t>패턴KEY</t>
@@ -443,6 +422,42 @@
   </si>
   <si>
     <t>초기화꾸러미</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>파닥몬</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">왜..나만 진화못하는거야 </t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>파닥몬 진화…!</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>헤티아</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>어리석은놈.. 겨우이정도밖에안되는거냐?</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>어리석은놈.. 내가 직접 진화시켜주지</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>진화해서 나를 위해 싸우거라!</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>6,7</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>O</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -1225,7 +1240,7 @@
       <c r="Q2" s="5"/>
       <c r="R2" s="5"/>
       <c r="S2" s="5" t="s">
-        <v>120</v>
+        <v>113</v>
       </c>
       <c r="T2" s="5"/>
       <c r="U2" s="5"/>
@@ -1276,7 +1291,7 @@
       <c r="Q3" s="5"/>
       <c r="R3" s="5"/>
       <c r="S3" s="5" t="s">
-        <v>126</v>
+        <v>119</v>
       </c>
       <c r="T3" s="5"/>
       <c r="U3" s="5"/>
@@ -1327,7 +1342,7 @@
       <c r="Q4" s="5"/>
       <c r="R4" s="5"/>
       <c r="S4" s="5" t="s">
-        <v>127</v>
+        <v>120</v>
       </c>
       <c r="T4" s="5"/>
       <c r="U4" s="5"/>
@@ -1378,7 +1393,7 @@
       <c r="Q5" s="5"/>
       <c r="R5" s="5"/>
       <c r="S5" s="5" t="s">
-        <v>127</v>
+        <v>120</v>
       </c>
       <c r="T5" s="5"/>
       <c r="U5" s="5"/>
@@ -1429,7 +1444,7 @@
       <c r="Q6" s="5"/>
       <c r="R6" s="5"/>
       <c r="S6" s="5" t="s">
-        <v>128</v>
+        <v>121</v>
       </c>
       <c r="T6" s="5"/>
       <c r="U6" s="5"/>
@@ -1480,7 +1495,7 @@
       <c r="Q7" s="5"/>
       <c r="R7" s="5"/>
       <c r="S7" s="5" t="s">
-        <v>129</v>
+        <v>122</v>
       </c>
       <c r="T7" s="5"/>
       <c r="U7" s="5"/>
@@ -1535,16 +1550,16 @@
       <c r="Q8" s="5"/>
       <c r="R8" s="5"/>
       <c r="S8" s="5" t="s">
-        <v>130</v>
+        <v>123</v>
       </c>
       <c r="T8" s="5" t="s">
         <v>48</v>
       </c>
       <c r="U8" s="5" t="s">
+        <v>133</v>
+      </c>
+      <c r="V8" s="5" t="s">
         <v>49</v>
-      </c>
-      <c r="V8" s="5" t="s">
-        <v>50</v>
       </c>
       <c r="W8" s="5"/>
       <c r="X8" s="5"/>
@@ -1552,31 +1567,31 @@
     </row>
     <row r="9" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A9" s="5" t="s">
+        <v>137</v>
+      </c>
+      <c r="B9" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="C9" s="5" t="s">
         <v>51</v>
       </c>
-      <c r="B9" s="5" t="s">
+      <c r="D9" s="5" t="s">
         <v>52</v>
       </c>
-      <c r="C9" s="5" t="s">
-        <v>53</v>
-      </c>
-      <c r="D9" s="5" t="s">
-        <v>54</v>
-      </c>
       <c r="E9" s="5">
-        <v>1000</v>
+        <v>45</v>
       </c>
       <c r="F9" s="5">
-        <v>1500000</v>
+        <v>700000</v>
       </c>
       <c r="G9" s="5">
-        <v>1600000</v>
+        <v>720000</v>
       </c>
       <c r="H9" s="5">
-        <v>50000</v>
+        <v>30000</v>
       </c>
       <c r="I9" s="5">
-        <v>1200</v>
+        <v>900</v>
       </c>
       <c r="J9" s="5"/>
       <c r="K9" s="5">
@@ -1586,39 +1601,41 @@
         <v>5</v>
       </c>
       <c r="M9" s="5">
-        <v>200000</v>
+        <v>100000</v>
       </c>
       <c r="N9" s="5">
-        <v>120</v>
+        <v>60</v>
       </c>
       <c r="O9" s="5"/>
       <c r="P9" s="5">
-        <v>300000</v>
+        <v>1000000</v>
       </c>
       <c r="Q9" s="5">
-        <v>900</v>
+        <v>600</v>
       </c>
       <c r="R9" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="S9" s="5"/>
+      <c r="S9" s="5" t="s">
+        <v>136</v>
+      </c>
       <c r="T9" s="5" t="s">
-        <v>55</v>
+        <v>129</v>
       </c>
       <c r="U9" s="5" t="s">
-        <v>56</v>
+        <v>130</v>
       </c>
       <c r="V9" s="5" t="s">
-        <v>57</v>
+        <v>131</v>
       </c>
       <c r="W9" s="5" t="s">
-        <v>55</v>
+        <v>132</v>
       </c>
       <c r="X9" s="5" t="s">
-        <v>58</v>
+        <v>134</v>
       </c>
       <c r="Y9" s="5" t="s">
-        <v>59</v>
+        <v>135</v>
       </c>
     </row>
     <row r="12" spans="1:25" x14ac:dyDescent="0.3">
@@ -1629,7 +1646,7 @@
         <v>1</v>
       </c>
       <c r="R15" t="s">
-        <v>64</v>
+        <v>57</v>
       </c>
     </row>
     <row r="16" spans="1:25" x14ac:dyDescent="0.3">
@@ -1637,7 +1654,7 @@
         <v>2</v>
       </c>
       <c r="R16" t="s">
-        <v>66</v>
+        <v>59</v>
       </c>
     </row>
     <row r="17" spans="16:18" x14ac:dyDescent="0.3">
@@ -1645,7 +1662,7 @@
         <v>3</v>
       </c>
       <c r="R17" t="s">
-        <v>68</v>
+        <v>61</v>
       </c>
     </row>
     <row r="18" spans="16:18" x14ac:dyDescent="0.3">
@@ -1653,7 +1670,7 @@
         <v>4</v>
       </c>
       <c r="R18" t="s">
-        <v>70</v>
+        <v>63</v>
       </c>
     </row>
     <row r="19" spans="16:18" x14ac:dyDescent="0.3">
@@ -1661,7 +1678,7 @@
         <v>5</v>
       </c>
       <c r="R19" t="s">
-        <v>72</v>
+        <v>65</v>
       </c>
     </row>
     <row r="20" spans="16:18" x14ac:dyDescent="0.3">
@@ -1669,7 +1686,7 @@
         <v>6</v>
       </c>
       <c r="R20" t="s">
-        <v>74</v>
+        <v>67</v>
       </c>
     </row>
     <row r="21" spans="16:18" x14ac:dyDescent="0.3">
@@ -1677,7 +1694,7 @@
         <v>7</v>
       </c>
       <c r="R21" t="s">
-        <v>76</v>
+        <v>69</v>
       </c>
     </row>
     <row r="22" spans="16:18" x14ac:dyDescent="0.3">
@@ -1685,7 +1702,7 @@
         <v>8</v>
       </c>
       <c r="R22" t="s">
-        <v>78</v>
+        <v>71</v>
       </c>
     </row>
     <row r="23" spans="16:18" x14ac:dyDescent="0.3">
@@ -1693,7 +1710,7 @@
         <v>9</v>
       </c>
       <c r="R23" t="s">
-        <v>131</v>
+        <v>124</v>
       </c>
     </row>
     <row r="24" spans="16:18" x14ac:dyDescent="0.3">
@@ -1701,7 +1718,7 @@
         <v>10</v>
       </c>
       <c r="R24" t="s">
-        <v>81</v>
+        <v>74</v>
       </c>
     </row>
     <row r="25" spans="16:18" x14ac:dyDescent="0.3">
@@ -1709,7 +1726,7 @@
         <v>11</v>
       </c>
       <c r="R25" t="s">
-        <v>83</v>
+        <v>76</v>
       </c>
     </row>
     <row r="26" spans="16:18" x14ac:dyDescent="0.3">
@@ -1717,7 +1734,7 @@
         <v>12</v>
       </c>
       <c r="R26" t="s">
-        <v>85</v>
+        <v>78</v>
       </c>
     </row>
     <row r="27" spans="16:18" x14ac:dyDescent="0.3">
@@ -1725,7 +1742,7 @@
         <v>13</v>
       </c>
       <c r="R27" t="s">
-        <v>87</v>
+        <v>80</v>
       </c>
     </row>
   </sheetData>
@@ -1737,7 +1754,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:D76"/>
+  <dimension ref="A1:D78"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
@@ -1748,13 +1765,13 @@
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1" s="6" t="s">
-        <v>60</v>
+        <v>53</v>
       </c>
       <c r="B1" s="6" t="s">
-        <v>61</v>
+        <v>54</v>
       </c>
       <c r="C1" s="6" t="s">
-        <v>62</v>
+        <v>55</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.3">
@@ -1762,10 +1779,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="7" t="s">
-        <v>63</v>
+        <v>56</v>
       </c>
       <c r="C2" s="7" t="s">
-        <v>64</v>
+        <v>57</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.3">
@@ -1773,10 +1790,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="7" t="s">
-        <v>65</v>
+        <v>58</v>
       </c>
       <c r="C3" s="7" t="s">
-        <v>66</v>
+        <v>59</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.3">
@@ -1784,10 +1801,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="7" t="s">
-        <v>67</v>
+        <v>60</v>
       </c>
       <c r="C4" s="7" t="s">
-        <v>68</v>
+        <v>61</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.3">
@@ -1795,10 +1812,10 @@
         <v>4</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>69</v>
+        <v>62</v>
       </c>
       <c r="C5" s="7" t="s">
-        <v>70</v>
+        <v>63</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.3">
@@ -1806,10 +1823,10 @@
         <v>5</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>71</v>
+        <v>64</v>
       </c>
       <c r="C6" s="7" t="s">
-        <v>72</v>
+        <v>65</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.3">
@@ -1817,10 +1834,10 @@
         <v>6</v>
       </c>
       <c r="B7" s="7" t="s">
-        <v>73</v>
+        <v>66</v>
       </c>
       <c r="C7" s="7" t="s">
-        <v>133</v>
+        <v>126</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.3">
@@ -1828,10 +1845,10 @@
         <v>7</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>75</v>
+        <v>68</v>
       </c>
       <c r="C8" s="7" t="s">
-        <v>134</v>
+        <v>127</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.3">
@@ -1839,10 +1856,10 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>77</v>
+        <v>70</v>
       </c>
       <c r="C9" t="s">
-        <v>78</v>
+        <v>71</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.3">
@@ -1850,10 +1867,10 @@
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>79</v>
+        <v>72</v>
       </c>
       <c r="C10" t="s">
-        <v>132</v>
+        <v>125</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.3">
@@ -1861,10 +1878,10 @@
         <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>80</v>
+        <v>73</v>
       </c>
       <c r="C11" t="s">
-        <v>81</v>
+        <v>74</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.3">
@@ -1872,10 +1889,10 @@
         <v>11</v>
       </c>
       <c r="B12" t="s">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="C12" t="s">
-        <v>83</v>
+        <v>76</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.3">
@@ -1883,10 +1900,10 @@
         <v>12</v>
       </c>
       <c r="B13" t="s">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="C13" t="s">
-        <v>85</v>
+        <v>78</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.3">
@@ -1894,24 +1911,24 @@
         <v>13</v>
       </c>
       <c r="B14" t="s">
-        <v>86</v>
+        <v>79</v>
       </c>
       <c r="C14" t="s">
-        <v>87</v>
+        <v>80</v>
       </c>
     </row>
     <row r="16" spans="1:4" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A16" s="8" t="s">
-        <v>88</v>
+        <v>81</v>
       </c>
       <c r="B16" s="8" t="s">
-        <v>89</v>
+        <v>82</v>
       </c>
       <c r="C16" s="8" t="s">
-        <v>90</v>
+        <v>83</v>
       </c>
       <c r="D16" s="8" t="s">
-        <v>91</v>
+        <v>84</v>
       </c>
     </row>
     <row r="17" spans="1:4" ht="17.25" thickTop="1" x14ac:dyDescent="0.3">
@@ -1919,7 +1936,7 @@
         <v>26</v>
       </c>
       <c r="B17" s="10" t="s">
-        <v>92</v>
+        <v>85</v>
       </c>
       <c r="C17" s="10">
         <v>60</v>
@@ -1934,7 +1951,7 @@
         <v>26</v>
       </c>
       <c r="B18" s="7" t="s">
-        <v>93</v>
+        <v>86</v>
       </c>
       <c r="C18" s="7">
         <v>20</v>
@@ -1946,7 +1963,7 @@
         <v>26</v>
       </c>
       <c r="B19" s="7" t="s">
-        <v>94</v>
+        <v>87</v>
       </c>
       <c r="C19" s="7">
         <v>10</v>
@@ -1958,7 +1975,7 @@
         <v>26</v>
       </c>
       <c r="B20" s="7" t="s">
-        <v>95</v>
+        <v>88</v>
       </c>
       <c r="C20" s="7">
         <v>5</v>
@@ -1970,7 +1987,7 @@
         <v>26</v>
       </c>
       <c r="B21" s="7" t="s">
-        <v>96</v>
+        <v>89</v>
       </c>
       <c r="C21" s="7">
         <v>3</v>
@@ -1982,7 +1999,7 @@
         <v>26</v>
       </c>
       <c r="B22" s="13" t="s">
-        <v>135</v>
+        <v>128</v>
       </c>
       <c r="C22" s="13">
         <v>2</v>
@@ -1994,7 +2011,7 @@
         <v>30</v>
       </c>
       <c r="B23" s="10" t="s">
-        <v>98</v>
+        <v>91</v>
       </c>
       <c r="C23" s="10">
         <v>60</v>
@@ -2009,7 +2026,7 @@
         <v>30</v>
       </c>
       <c r="B24" s="7" t="s">
-        <v>99</v>
+        <v>92</v>
       </c>
       <c r="C24" s="7">
         <v>20</v>
@@ -2021,7 +2038,7 @@
         <v>30</v>
       </c>
       <c r="B25" s="7" t="s">
-        <v>100</v>
+        <v>93</v>
       </c>
       <c r="C25" s="7">
         <v>5</v>
@@ -2033,7 +2050,7 @@
         <v>30</v>
       </c>
       <c r="B26" s="7" t="s">
-        <v>101</v>
+        <v>94</v>
       </c>
       <c r="C26" s="7">
         <v>5</v>
@@ -2045,7 +2062,7 @@
         <v>30</v>
       </c>
       <c r="B27" s="7" t="s">
-        <v>102</v>
+        <v>95</v>
       </c>
       <c r="C27" s="7">
         <v>5</v>
@@ -2057,7 +2074,7 @@
         <v>30</v>
       </c>
       <c r="B28" s="7" t="s">
-        <v>103</v>
+        <v>96</v>
       </c>
       <c r="C28" s="7">
         <v>3</v>
@@ -2069,7 +2086,7 @@
         <v>30</v>
       </c>
       <c r="B29" s="13" t="s">
-        <v>104</v>
+        <v>97</v>
       </c>
       <c r="C29" s="13">
         <v>2</v>
@@ -2081,7 +2098,7 @@
         <v>33</v>
       </c>
       <c r="B30" s="10" t="s">
-        <v>99</v>
+        <v>92</v>
       </c>
       <c r="C30" s="10">
         <v>61.5</v>
@@ -2096,7 +2113,7 @@
         <v>33</v>
       </c>
       <c r="B31" s="7" t="s">
-        <v>105</v>
+        <v>98</v>
       </c>
       <c r="C31" s="7">
         <v>10</v>
@@ -2108,7 +2125,7 @@
         <v>33</v>
       </c>
       <c r="B32" s="7" t="s">
-        <v>106</v>
+        <v>99</v>
       </c>
       <c r="C32" s="7">
         <v>10</v>
@@ -2120,7 +2137,7 @@
         <v>33</v>
       </c>
       <c r="B33" s="7" t="s">
-        <v>107</v>
+        <v>100</v>
       </c>
       <c r="C33" s="7">
         <v>10</v>
@@ -2132,7 +2149,7 @@
         <v>33</v>
       </c>
       <c r="B34" s="7" t="s">
-        <v>108</v>
+        <v>101</v>
       </c>
       <c r="C34" s="7">
         <v>5</v>
@@ -2144,7 +2161,7 @@
         <v>33</v>
       </c>
       <c r="B35" s="7" t="s">
-        <v>109</v>
+        <v>102</v>
       </c>
       <c r="C35" s="7">
         <v>1</v>
@@ -2156,7 +2173,7 @@
         <v>33</v>
       </c>
       <c r="B36" s="7" t="s">
-        <v>110</v>
+        <v>103</v>
       </c>
       <c r="C36" s="7">
         <v>1</v>
@@ -2168,7 +2185,7 @@
         <v>33</v>
       </c>
       <c r="B37" s="7" t="s">
-        <v>111</v>
+        <v>104</v>
       </c>
       <c r="C37" s="7">
         <v>1</v>
@@ -2180,7 +2197,7 @@
         <v>33</v>
       </c>
       <c r="B38" s="13" t="s">
-        <v>121</v>
+        <v>114</v>
       </c>
       <c r="C38" s="13">
         <v>0.5</v>
@@ -2192,7 +2209,7 @@
         <v>36</v>
       </c>
       <c r="B39" s="10" t="s">
-        <v>105</v>
+        <v>98</v>
       </c>
       <c r="C39" s="10">
         <v>65.5</v>
@@ -2207,7 +2224,7 @@
         <v>36</v>
       </c>
       <c r="B40" s="7" t="s">
-        <v>112</v>
+        <v>105</v>
       </c>
       <c r="C40" s="7">
         <v>20</v>
@@ -2219,7 +2236,7 @@
         <v>36</v>
       </c>
       <c r="B41" s="7" t="s">
-        <v>113</v>
+        <v>106</v>
       </c>
       <c r="C41" s="7">
         <v>10</v>
@@ -2231,7 +2248,7 @@
         <v>36</v>
       </c>
       <c r="B42" s="7" t="s">
-        <v>111</v>
+        <v>104</v>
       </c>
       <c r="C42" s="7">
         <v>2</v>
@@ -2243,7 +2260,7 @@
         <v>36</v>
       </c>
       <c r="B43" s="7" t="s">
-        <v>114</v>
+        <v>107</v>
       </c>
       <c r="C43" s="7">
         <v>1</v>
@@ -2255,7 +2272,7 @@
         <v>36</v>
       </c>
       <c r="B44" s="7" t="s">
-        <v>115</v>
+        <v>108</v>
       </c>
       <c r="C44" s="7">
         <v>1</v>
@@ -2267,7 +2284,7 @@
         <v>36</v>
       </c>
       <c r="B45" s="13" t="s">
-        <v>122</v>
+        <v>115</v>
       </c>
       <c r="C45" s="13">
         <v>0.5</v>
@@ -2279,7 +2296,7 @@
         <v>39</v>
       </c>
       <c r="B46" s="10" t="s">
-        <v>112</v>
+        <v>105</v>
       </c>
       <c r="C46" s="10">
         <v>60</v>
@@ -2294,7 +2311,7 @@
         <v>39</v>
       </c>
       <c r="B47" s="7" t="s">
-        <v>92</v>
+        <v>85</v>
       </c>
       <c r="C47" s="7">
         <v>20</v>
@@ -2306,7 +2323,7 @@
         <v>39</v>
       </c>
       <c r="B48" s="7" t="s">
-        <v>116</v>
+        <v>109</v>
       </c>
       <c r="C48" s="7">
         <v>13</v>
@@ -2318,7 +2335,7 @@
         <v>39</v>
       </c>
       <c r="B49" s="7" t="s">
-        <v>111</v>
+        <v>104</v>
       </c>
       <c r="C49" s="7">
         <v>3</v>
@@ -2330,7 +2347,7 @@
         <v>39</v>
       </c>
       <c r="B50" s="7" t="s">
-        <v>95</v>
+        <v>88</v>
       </c>
       <c r="C50" s="7">
         <v>1.5</v>
@@ -2342,7 +2359,7 @@
         <v>39</v>
       </c>
       <c r="B51" s="7" t="s">
-        <v>97</v>
+        <v>90</v>
       </c>
       <c r="C51" s="7">
         <v>1</v>
@@ -2354,7 +2371,7 @@
         <v>39</v>
       </c>
       <c r="B52" s="7" t="s">
-        <v>117</v>
+        <v>110</v>
       </c>
       <c r="C52" s="7">
         <v>1</v>
@@ -2366,7 +2383,7 @@
         <v>39</v>
       </c>
       <c r="B53" s="7" t="s">
-        <v>118</v>
+        <v>111</v>
       </c>
       <c r="C53" s="7">
         <v>0.5</v>
@@ -2378,7 +2395,7 @@
         <v>39</v>
       </c>
       <c r="B54" s="13" t="s">
-        <v>123</v>
+        <v>116</v>
       </c>
       <c r="C54" s="13">
         <v>0.5</v>
@@ -2390,7 +2407,7 @@
         <v>42</v>
       </c>
       <c r="B55" s="10" t="s">
-        <v>92</v>
+        <v>85</v>
       </c>
       <c r="C55" s="10">
         <v>59.5</v>
@@ -2405,7 +2422,7 @@
         <v>42</v>
       </c>
       <c r="B56" s="7" t="s">
-        <v>94</v>
+        <v>87</v>
       </c>
       <c r="C56" s="7">
         <v>29</v>
@@ -2417,7 +2434,7 @@
         <v>42</v>
       </c>
       <c r="B57" s="7" t="s">
-        <v>111</v>
+        <v>104</v>
       </c>
       <c r="C57" s="7">
         <v>4</v>
@@ -2429,7 +2446,7 @@
         <v>42</v>
       </c>
       <c r="B58" s="7" t="s">
-        <v>117</v>
+        <v>110</v>
       </c>
       <c r="C58" s="7">
         <v>2</v>
@@ -2441,7 +2458,7 @@
         <v>42</v>
       </c>
       <c r="B59" s="7" t="s">
-        <v>97</v>
+        <v>90</v>
       </c>
       <c r="C59" s="7">
         <v>1</v>
@@ -2453,7 +2470,7 @@
         <v>42</v>
       </c>
       <c r="B60" s="7" t="s">
-        <v>96</v>
+        <v>89</v>
       </c>
       <c r="C60" s="7">
         <v>2</v>
@@ -2465,7 +2482,7 @@
         <v>42</v>
       </c>
       <c r="B61" s="7" t="s">
-        <v>118</v>
+        <v>111</v>
       </c>
       <c r="C61" s="7">
         <v>2</v>
@@ -2477,7 +2494,7 @@
         <v>42</v>
       </c>
       <c r="B62" s="13" t="s">
-        <v>124</v>
+        <v>117</v>
       </c>
       <c r="C62" s="13">
         <v>0.5</v>
@@ -2489,7 +2506,7 @@
         <v>45</v>
       </c>
       <c r="B63" s="10" t="s">
-        <v>92</v>
+        <v>85</v>
       </c>
       <c r="C63" s="10">
         <v>50</v>
@@ -2504,7 +2521,7 @@
         <v>45</v>
       </c>
       <c r="B64" s="7" t="s">
-        <v>135</v>
+        <v>128</v>
       </c>
       <c r="C64" s="7">
         <v>20</v>
@@ -2516,7 +2533,7 @@
         <v>45</v>
       </c>
       <c r="B65" s="7" t="s">
-        <v>96</v>
+        <v>89</v>
       </c>
       <c r="C65" s="7">
         <v>4</v>
@@ -2528,7 +2545,7 @@
         <v>45</v>
       </c>
       <c r="B66" s="7" t="s">
-        <v>119</v>
+        <v>112</v>
       </c>
       <c r="C66" s="7">
         <v>20</v>
@@ -2537,10 +2554,10 @@
     </row>
     <row r="67" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A67" s="11" t="s">
-        <v>125</v>
+        <v>118</v>
       </c>
       <c r="B67" s="7" t="s">
-        <v>97</v>
+        <v>90</v>
       </c>
       <c r="C67" s="7">
         <v>2</v>
@@ -2552,7 +2569,7 @@
         <v>45</v>
       </c>
       <c r="B68" s="7" t="s">
-        <v>122</v>
+        <v>115</v>
       </c>
       <c r="C68" s="7">
         <v>1</v>
@@ -2564,7 +2581,7 @@
         <v>45</v>
       </c>
       <c r="B69" s="7" t="s">
-        <v>123</v>
+        <v>116</v>
       </c>
       <c r="C69" s="7">
         <v>1</v>
@@ -2576,7 +2593,7 @@
         <v>45</v>
       </c>
       <c r="B70" s="15" t="s">
-        <v>124</v>
+        <v>117</v>
       </c>
       <c r="C70" s="7">
         <v>1</v>
@@ -2588,7 +2605,7 @@
         <v>45</v>
       </c>
       <c r="B71" s="17" t="s">
-        <v>121</v>
+        <v>114</v>
       </c>
       <c r="C71" s="13">
         <v>1</v>
@@ -2597,44 +2614,84 @@
     </row>
     <row r="72" spans="1:4" ht="17.25" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
       <c r="A72" s="9" t="s">
-        <v>52</v>
-      </c>
-      <c r="B72" s="10"/>
-      <c r="C72" s="10"/>
+        <v>50</v>
+      </c>
+      <c r="B72" s="10" t="s">
+        <v>85</v>
+      </c>
+      <c r="C72" s="10">
+        <v>40</v>
+      </c>
       <c r="D72" s="18">
-        <f>SUM(C72:C75)/100</f>
-        <v>0</v>
+        <f>SUM(C72:C77)/100</f>
+        <v>1</v>
       </c>
     </row>
     <row r="73" spans="1:4" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A73" s="11" t="s">
-        <v>52</v>
-      </c>
-      <c r="B73" s="7"/>
-      <c r="C73" s="7"/>
+        <v>50</v>
+      </c>
+      <c r="B73" s="7" t="s">
+        <v>112</v>
+      </c>
+      <c r="C73" s="7">
+        <v>30</v>
+      </c>
       <c r="D73" s="19"/>
     </row>
     <row r="74" spans="1:4" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A74" s="11" t="s">
-        <v>52</v>
-      </c>
-      <c r="B74" s="7"/>
-      <c r="C74" s="7"/>
+        <v>50</v>
+      </c>
+      <c r="B74" s="7" t="s">
+        <v>128</v>
+      </c>
+      <c r="C74" s="7">
+        <v>20</v>
+      </c>
       <c r="D74" s="19"/>
     </row>
-    <row r="75" spans="1:4" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A75" s="12" t="s">
-        <v>52</v>
-      </c>
-      <c r="B75" s="13"/>
-      <c r="C75" s="13"/>
-      <c r="D75" s="20"/>
-    </row>
-    <row r="76" spans="1:4" ht="17.25" thickTop="1" x14ac:dyDescent="0.3"/>
+    <row r="75" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A75" s="11" t="s">
+        <v>50</v>
+      </c>
+      <c r="B75" s="7" t="s">
+        <v>89</v>
+      </c>
+      <c r="C75" s="7">
+        <v>6</v>
+      </c>
+      <c r="D75" s="19"/>
+    </row>
+    <row r="76" spans="1:4" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A76" s="11" t="s">
+        <v>50</v>
+      </c>
+      <c r="B76" s="7" t="s">
+        <v>116</v>
+      </c>
+      <c r="C76" s="7">
+        <v>2</v>
+      </c>
+      <c r="D76" s="19"/>
+    </row>
+    <row r="77" spans="1:4" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A77" s="12" t="s">
+        <v>50</v>
+      </c>
+      <c r="B77" s="17" t="s">
+        <v>117</v>
+      </c>
+      <c r="C77" s="13">
+        <v>2</v>
+      </c>
+      <c r="D77" s="20"/>
+    </row>
+    <row r="78" spans="1:4" ht="17.25" thickTop="1" x14ac:dyDescent="0.3"/>
   </sheetData>
   <mergeCells count="8">
     <mergeCell ref="D63:D71"/>
-    <mergeCell ref="D72:D75"/>
+    <mergeCell ref="D72:D77"/>
     <mergeCell ref="D17:D22"/>
     <mergeCell ref="D23:D29"/>
     <mergeCell ref="D30:D38"/>

--- a/raid_config.xlsx
+++ b/raid_config.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\new_bot\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D37F5637-C477-4FC6-8E59-3BD920C337F8}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{01275FB0-8C32-4F33-AF9E-824A92151D9D}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="1725" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,12 +16,15 @@
     <sheet name="레이드설정" sheetId="1" r:id="rId1"/>
     <sheet name="DATA" sheetId="2" r:id="rId2"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">DATA!$A$16:$D$79</definedName>
+  </definedNames>
   <calcPr calcId="191029"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="244" uniqueCount="138">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="248" uniqueCount="141">
   <si>
     <t>활성화여부</t>
   </si>
@@ -458,6 +461,18 @@
   </si>
   <si>
     <t>O</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>배진3강화제</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>상급</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>펫경문_3000</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -1754,7 +1769,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:D78"/>
+  <dimension ref="A1:D80"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
@@ -2101,10 +2116,10 @@
         <v>92</v>
       </c>
       <c r="C30" s="10">
-        <v>61.5</v>
+        <v>61</v>
       </c>
       <c r="D30" s="18">
-        <f>SUM(C30:C38)/100</f>
+        <f>SUM(C30:C39)/100</f>
         <v>1</v>
       </c>
     </row>
@@ -2192,54 +2207,54 @@
       </c>
       <c r="D37" s="19"/>
     </row>
-    <row r="38" spans="1:4" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A38" s="12" t="s">
+    <row r="38" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A38" s="11" t="s">
         <v>33</v>
       </c>
-      <c r="B38" s="13" t="s">
+      <c r="B38" s="7" t="s">
+        <v>138</v>
+      </c>
+      <c r="C38" s="7">
+        <v>0.5</v>
+      </c>
+      <c r="D38" s="19"/>
+    </row>
+    <row r="39" spans="1:4" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A39" s="12" t="s">
+        <v>33</v>
+      </c>
+      <c r="B39" s="13" t="s">
         <v>114</v>
       </c>
-      <c r="C38" s="13">
+      <c r="C39" s="13">
         <v>0.5</v>
       </c>
-      <c r="D38" s="20"/>
-    </row>
-    <row r="39" spans="1:4" ht="17.25" thickTop="1" x14ac:dyDescent="0.3">
-      <c r="A39" s="9" t="s">
+      <c r="D39" s="20"/>
+    </row>
+    <row r="40" spans="1:4" ht="17.25" thickTop="1" x14ac:dyDescent="0.3">
+      <c r="A40" s="9" t="s">
         <v>36</v>
       </c>
-      <c r="B39" s="10" t="s">
+      <c r="B40" s="10" t="s">
         <v>98</v>
       </c>
-      <c r="C39" s="10">
-        <v>65.5</v>
-      </c>
-      <c r="D39" s="18">
-        <f>SUM(C39:C45)/100</f>
+      <c r="C40" s="10">
+        <v>64.5</v>
+      </c>
+      <c r="D40" s="18">
+        <f>SUM(C40:C47)/100</f>
         <v>1</v>
       </c>
-    </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A40" s="11" t="s">
-        <v>36</v>
-      </c>
-      <c r="B40" s="7" t="s">
-        <v>105</v>
-      </c>
-      <c r="C40" s="7">
-        <v>20</v>
-      </c>
-      <c r="D40" s="19"/>
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A41" s="11" t="s">
         <v>36</v>
       </c>
       <c r="B41" s="7" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C41" s="7">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="D41" s="19"/>
     </row>
@@ -2248,10 +2263,10 @@
         <v>36</v>
       </c>
       <c r="B42" s="7" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="C42" s="7">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="D42" s="19"/>
     </row>
@@ -2260,85 +2275,85 @@
         <v>36</v>
       </c>
       <c r="B43" s="7" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="C43" s="7">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D43" s="19"/>
     </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A44" s="11" t="s">
-        <v>36</v>
+        <v>139</v>
       </c>
       <c r="B44" s="7" t="s">
-        <v>108</v>
+        <v>138</v>
       </c>
       <c r="C44" s="7">
         <v>1</v>
       </c>
       <c r="D44" s="19"/>
     </row>
-    <row r="45" spans="1:4" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A45" s="12" t="s">
+    <row r="45" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A45" s="11" t="s">
         <v>36</v>
       </c>
-      <c r="B45" s="13" t="s">
+      <c r="B45" s="7" t="s">
+        <v>107</v>
+      </c>
+      <c r="C45" s="7">
+        <v>1</v>
+      </c>
+      <c r="D45" s="19"/>
+    </row>
+    <row r="46" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A46" s="11" t="s">
+        <v>36</v>
+      </c>
+      <c r="B46" s="7" t="s">
+        <v>108</v>
+      </c>
+      <c r="C46" s="7">
+        <v>1</v>
+      </c>
+      <c r="D46" s="19"/>
+    </row>
+    <row r="47" spans="1:4" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A47" s="12" t="s">
+        <v>36</v>
+      </c>
+      <c r="B47" s="13" t="s">
         <v>115</v>
       </c>
-      <c r="C45" s="13">
+      <c r="C47" s="13">
         <v>0.5</v>
       </c>
-      <c r="D45" s="20"/>
-    </row>
-    <row r="46" spans="1:4" ht="17.25" thickTop="1" x14ac:dyDescent="0.3">
-      <c r="A46" s="9" t="s">
+      <c r="D47" s="20"/>
+    </row>
+    <row r="48" spans="1:4" ht="17.25" thickTop="1" x14ac:dyDescent="0.3">
+      <c r="A48" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="B46" s="10" t="s">
+      <c r="B48" s="10" t="s">
         <v>105</v>
       </c>
-      <c r="C46" s="10">
+      <c r="C48" s="10">
         <v>60</v>
       </c>
-      <c r="D46" s="18">
-        <f>SUM(C46:C54)/100</f>
+      <c r="D48" s="18">
+        <f>SUM(C48:C56)/100</f>
         <v>1.0049999999999999</v>
       </c>
-    </row>
-    <row r="47" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A47" s="11" t="s">
-        <v>39</v>
-      </c>
-      <c r="B47" s="7" t="s">
-        <v>85</v>
-      </c>
-      <c r="C47" s="7">
-        <v>20</v>
-      </c>
-      <c r="D47" s="19"/>
-    </row>
-    <row r="48" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A48" s="11" t="s">
-        <v>39</v>
-      </c>
-      <c r="B48" s="7" t="s">
-        <v>109</v>
-      </c>
-      <c r="C48" s="7">
-        <v>13</v>
-      </c>
-      <c r="D48" s="19"/>
     </row>
     <row r="49" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A49" s="11" t="s">
         <v>39</v>
       </c>
       <c r="B49" s="7" t="s">
-        <v>104</v>
+        <v>85</v>
       </c>
       <c r="C49" s="7">
-        <v>3</v>
+        <v>20</v>
       </c>
       <c r="D49" s="19"/>
     </row>
@@ -2347,10 +2362,10 @@
         <v>39</v>
       </c>
       <c r="B50" s="7" t="s">
-        <v>88</v>
+        <v>109</v>
       </c>
       <c r="C50" s="7">
-        <v>1.5</v>
+        <v>13</v>
       </c>
       <c r="D50" s="19"/>
     </row>
@@ -2359,10 +2374,10 @@
         <v>39</v>
       </c>
       <c r="B51" s="7" t="s">
-        <v>90</v>
+        <v>104</v>
       </c>
       <c r="C51" s="7">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D51" s="19"/>
     </row>
@@ -2371,10 +2386,10 @@
         <v>39</v>
       </c>
       <c r="B52" s="7" t="s">
-        <v>110</v>
+        <v>88</v>
       </c>
       <c r="C52" s="7">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="D52" s="19"/>
     </row>
@@ -2383,94 +2398,94 @@
         <v>39</v>
       </c>
       <c r="B53" s="7" t="s">
+        <v>90</v>
+      </c>
+      <c r="C53" s="7">
+        <v>1</v>
+      </c>
+      <c r="D53" s="19"/>
+    </row>
+    <row r="54" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A54" s="11" t="s">
+        <v>39</v>
+      </c>
+      <c r="B54" s="7" t="s">
+        <v>138</v>
+      </c>
+      <c r="C54" s="7">
+        <v>1</v>
+      </c>
+      <c r="D54" s="19"/>
+    </row>
+    <row r="55" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A55" s="11" t="s">
+        <v>39</v>
+      </c>
+      <c r="B55" s="7" t="s">
         <v>111</v>
       </c>
-      <c r="C53" s="7">
+      <c r="C55" s="7">
         <v>0.5</v>
       </c>
-      <c r="D53" s="19"/>
-    </row>
-    <row r="54" spans="1:4" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A54" s="12" t="s">
+      <c r="D55" s="19"/>
+    </row>
+    <row r="56" spans="1:4" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A56" s="12" t="s">
         <v>39</v>
       </c>
-      <c r="B54" s="13" t="s">
+      <c r="B56" s="13" t="s">
         <v>116</v>
       </c>
-      <c r="C54" s="13">
+      <c r="C56" s="13">
         <v>0.5</v>
       </c>
-      <c r="D54" s="20"/>
-    </row>
-    <row r="55" spans="1:4" ht="17.25" thickTop="1" x14ac:dyDescent="0.3">
-      <c r="A55" s="9" t="s">
+      <c r="D56" s="20"/>
+    </row>
+    <row r="57" spans="1:4" ht="17.25" thickTop="1" x14ac:dyDescent="0.3">
+      <c r="A57" s="10" t="s">
         <v>42</v>
       </c>
-      <c r="B55" s="10" t="s">
+      <c r="B57" s="10" t="s">
         <v>85</v>
       </c>
-      <c r="C55" s="10">
+      <c r="C57" s="10">
         <v>59.5</v>
       </c>
-      <c r="D55" s="18">
-        <f>SUM(C55:C62)/100</f>
+      <c r="D57" s="18">
+        <f>SUM(C57:C64)/100</f>
         <v>1</v>
       </c>
     </row>
-    <row r="56" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A56" s="11" t="s">
+    <row r="58" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A58" s="7" t="s">
         <v>42</v>
       </c>
-      <c r="B56" s="7" t="s">
+      <c r="B58" s="7" t="s">
         <v>87</v>
       </c>
-      <c r="C56" s="7">
+      <c r="C58" s="7">
         <v>29</v>
       </c>
-      <c r="D56" s="19"/>
-    </row>
-    <row r="57" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A57" s="11" t="s">
+      <c r="D58" s="19"/>
+    </row>
+    <row r="59" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A59" s="7" t="s">
         <v>42</v>
       </c>
-      <c r="B57" s="7" t="s">
+      <c r="B59" s="7" t="s">
         <v>104</v>
       </c>
-      <c r="C57" s="7">
+      <c r="C59" s="7">
         <v>4</v>
       </c>
-      <c r="D57" s="19"/>
-    </row>
-    <row r="58" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A58" s="11" t="s">
+      <c r="D59" s="19"/>
+    </row>
+    <row r="60" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A60" s="7" t="s">
         <v>42</v>
       </c>
-      <c r="B58" s="7" t="s">
+      <c r="B60" s="7" t="s">
         <v>110</v>
-      </c>
-      <c r="C58" s="7">
-        <v>2</v>
-      </c>
-      <c r="D58" s="19"/>
-    </row>
-    <row r="59" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A59" s="11" t="s">
-        <v>42</v>
-      </c>
-      <c r="B59" s="7" t="s">
-        <v>90</v>
-      </c>
-      <c r="C59" s="7">
-        <v>1</v>
-      </c>
-      <c r="D59" s="19"/>
-    </row>
-    <row r="60" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A60" s="11" t="s">
-        <v>42</v>
-      </c>
-      <c r="B60" s="7" t="s">
-        <v>89</v>
       </c>
       <c r="C60" s="7">
         <v>2</v>
@@ -2478,74 +2493,74 @@
       <c r="D60" s="19"/>
     </row>
     <row r="61" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A61" s="11" t="s">
+      <c r="A61" s="7" t="s">
         <v>42</v>
       </c>
       <c r="B61" s="7" t="s">
+        <v>90</v>
+      </c>
+      <c r="C61" s="7">
+        <v>1</v>
+      </c>
+      <c r="D61" s="19"/>
+    </row>
+    <row r="62" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A62" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="B62" s="7" t="s">
+        <v>89</v>
+      </c>
+      <c r="C62" s="7">
+        <v>2</v>
+      </c>
+      <c r="D62" s="19"/>
+    </row>
+    <row r="63" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A63" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="B63" s="7" t="s">
         <v>111</v>
       </c>
-      <c r="C61" s="7">
+      <c r="C63" s="7">
         <v>2</v>
       </c>
-      <c r="D61" s="19"/>
-    </row>
-    <row r="62" spans="1:4" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A62" s="12" t="s">
+      <c r="D63" s="19"/>
+    </row>
+    <row r="64" spans="1:4" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A64" s="13" t="s">
         <v>42</v>
       </c>
-      <c r="B62" s="13" t="s">
+      <c r="B64" s="13" t="s">
         <v>117</v>
       </c>
-      <c r="C62" s="13">
+      <c r="C64" s="13">
         <v>0.5</v>
       </c>
-      <c r="D62" s="20"/>
-    </row>
-    <row r="63" spans="1:4" ht="17.25" thickTop="1" x14ac:dyDescent="0.3">
-      <c r="A63" s="9" t="s">
+      <c r="D64" s="20"/>
+    </row>
+    <row r="65" spans="1:4" ht="17.25" thickTop="1" x14ac:dyDescent="0.3">
+      <c r="A65" s="10" t="s">
         <v>45</v>
       </c>
-      <c r="B63" s="10" t="s">
+      <c r="B65" s="10" t="s">
         <v>85</v>
       </c>
-      <c r="C63" s="10">
+      <c r="C65" s="10">
         <v>50</v>
       </c>
-      <c r="D63" s="18">
-        <f>SUM(C63:C71)/100</f>
+      <c r="D65" s="18">
+        <f>SUM(C65:C73)/100</f>
         <v>1</v>
       </c>
     </row>
-    <row r="64" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A64" s="11" t="s">
+    <row r="66" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A66" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="B64" s="7" t="s">
+      <c r="B66" s="7" t="s">
         <v>128</v>
-      </c>
-      <c r="C64" s="7">
-        <v>20</v>
-      </c>
-      <c r="D64" s="19"/>
-    </row>
-    <row r="65" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A65" s="11" t="s">
-        <v>45</v>
-      </c>
-      <c r="B65" s="7" t="s">
-        <v>89</v>
-      </c>
-      <c r="C65" s="7">
-        <v>4</v>
-      </c>
-      <c r="D65" s="19"/>
-    </row>
-    <row r="66" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A66" s="11" t="s">
-        <v>45</v>
-      </c>
-      <c r="B66" s="7" t="s">
-        <v>112</v>
       </c>
       <c r="C66" s="7">
         <v>20</v>
@@ -2553,151 +2568,176 @@
       <c r="D66" s="19"/>
     </row>
     <row r="67" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A67" s="11" t="s">
+      <c r="A67" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="B67" s="7" t="s">
+        <v>140</v>
+      </c>
+      <c r="C67" s="7">
+        <v>4</v>
+      </c>
+      <c r="D67" s="19"/>
+    </row>
+    <row r="68" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A68" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="B68" s="7" t="s">
+        <v>112</v>
+      </c>
+      <c r="C68" s="7">
+        <v>20</v>
+      </c>
+      <c r="D68" s="19"/>
+    </row>
+    <row r="69" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A69" s="7" t="s">
         <v>118</v>
       </c>
-      <c r="B67" s="7" t="s">
+      <c r="B69" s="7" t="s">
         <v>90</v>
       </c>
-      <c r="C67" s="7">
+      <c r="C69" s="7">
         <v>2</v>
       </c>
-      <c r="D67" s="19"/>
-    </row>
-    <row r="68" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A68" s="11" t="s">
+      <c r="D69" s="19"/>
+    </row>
+    <row r="70" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A70" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="B68" s="7" t="s">
+      <c r="B70" s="7" t="s">
         <v>115</v>
-      </c>
-      <c r="C68" s="7">
-        <v>1</v>
-      </c>
-      <c r="D68" s="19"/>
-    </row>
-    <row r="69" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A69" s="11" t="s">
-        <v>45</v>
-      </c>
-      <c r="B69" s="7" t="s">
-        <v>116</v>
-      </c>
-      <c r="C69" s="7">
-        <v>1</v>
-      </c>
-      <c r="D69" s="19"/>
-    </row>
-    <row r="70" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A70" s="14" t="s">
-        <v>45</v>
-      </c>
-      <c r="B70" s="15" t="s">
-        <v>117</v>
       </c>
       <c r="C70" s="7">
         <v>1</v>
       </c>
       <c r="D70" s="19"/>
     </row>
-    <row r="71" spans="1:4" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A71" s="16" t="s">
+    <row r="71" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A71" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="B71" s="17" t="s">
+      <c r="B71" s="7" t="s">
+        <v>116</v>
+      </c>
+      <c r="C71" s="7">
+        <v>1</v>
+      </c>
+      <c r="D71" s="19"/>
+    </row>
+    <row r="72" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A72" s="14" t="s">
+        <v>45</v>
+      </c>
+      <c r="B72" s="15" t="s">
+        <v>117</v>
+      </c>
+      <c r="C72" s="7">
+        <v>1</v>
+      </c>
+      <c r="D72" s="19"/>
+    </row>
+    <row r="73" spans="1:4" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A73" s="16" t="s">
+        <v>45</v>
+      </c>
+      <c r="B73" s="17" t="s">
         <v>114</v>
       </c>
-      <c r="C71" s="13">
+      <c r="C73" s="13">
         <v>1</v>
       </c>
-      <c r="D71" s="20"/>
-    </row>
-    <row r="72" spans="1:4" ht="17.25" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
-      <c r="A72" s="9" t="s">
+      <c r="D73" s="20"/>
+    </row>
+    <row r="74" spans="1:4" ht="17.25" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
+      <c r="A74" s="10" t="s">
         <v>50</v>
       </c>
-      <c r="B72" s="10" t="s">
+      <c r="B74" s="10" t="s">
         <v>85</v>
       </c>
-      <c r="C72" s="10">
+      <c r="C74" s="10">
         <v>40</v>
       </c>
-      <c r="D72" s="18">
-        <f>SUM(C72:C77)/100</f>
+      <c r="D74" s="18">
+        <f>SUM(C74:C79)/100</f>
         <v>1</v>
       </c>
     </row>
-    <row r="73" spans="1:4" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A73" s="11" t="s">
+    <row r="75" spans="1:4" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A75" s="7" t="s">
         <v>50</v>
       </c>
-      <c r="B73" s="7" t="s">
+      <c r="B75" s="7" t="s">
         <v>112</v>
       </c>
-      <c r="C73" s="7">
+      <c r="C75" s="7">
         <v>30</v>
       </c>
-      <c r="D73" s="19"/>
-    </row>
-    <row r="74" spans="1:4" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A74" s="11" t="s">
+      <c r="D75" s="19"/>
+    </row>
+    <row r="76" spans="1:4" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A76" s="7" t="s">
         <v>50</v>
       </c>
-      <c r="B74" s="7" t="s">
+      <c r="B76" s="7" t="s">
         <v>128</v>
       </c>
-      <c r="C74" s="7">
+      <c r="C76" s="7">
         <v>20</v>
       </c>
-      <c r="D74" s="19"/>
-    </row>
-    <row r="75" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A75" s="11" t="s">
+      <c r="D76" s="19"/>
+    </row>
+    <row r="77" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A77" s="7" t="s">
         <v>50</v>
       </c>
-      <c r="B75" s="7" t="s">
-        <v>89</v>
-      </c>
-      <c r="C75" s="7">
+      <c r="B77" s="7" t="s">
+        <v>140</v>
+      </c>
+      <c r="C77" s="7">
         <v>6</v>
       </c>
-      <c r="D75" s="19"/>
-    </row>
-    <row r="76" spans="1:4" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A76" s="11" t="s">
+      <c r="D77" s="19"/>
+    </row>
+    <row r="78" spans="1:4" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A78" s="7" t="s">
         <v>50</v>
       </c>
-      <c r="B76" s="7" t="s">
+      <c r="B78" s="7" t="s">
         <v>116</v>
       </c>
-      <c r="C76" s="7">
+      <c r="C78" s="7">
         <v>2</v>
       </c>
-      <c r="D76" s="19"/>
-    </row>
-    <row r="77" spans="1:4" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A77" s="12" t="s">
+      <c r="D78" s="19"/>
+    </row>
+    <row r="79" spans="1:4" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A79" s="13" t="s">
         <v>50</v>
       </c>
-      <c r="B77" s="17" t="s">
+      <c r="B79" s="17" t="s">
         <v>117</v>
       </c>
-      <c r="C77" s="13">
+      <c r="C79" s="13">
         <v>2</v>
       </c>
-      <c r="D77" s="20"/>
-    </row>
-    <row r="78" spans="1:4" ht="17.25" thickTop="1" x14ac:dyDescent="0.3"/>
+      <c r="D79" s="20"/>
+    </row>
+    <row r="80" spans="1:4" ht="17.25" thickTop="1" x14ac:dyDescent="0.3"/>
   </sheetData>
+  <autoFilter ref="A16:D79" xr:uid="{91CBCC93-600B-4657-92F3-9623C670C48B}"/>
   <mergeCells count="8">
-    <mergeCell ref="D63:D71"/>
-    <mergeCell ref="D72:D77"/>
+    <mergeCell ref="D65:D73"/>
+    <mergeCell ref="D74:D79"/>
     <mergeCell ref="D17:D22"/>
     <mergeCell ref="D23:D29"/>
-    <mergeCell ref="D30:D38"/>
-    <mergeCell ref="D39:D45"/>
-    <mergeCell ref="D46:D54"/>
-    <mergeCell ref="D55:D62"/>
+    <mergeCell ref="D30:D39"/>
+    <mergeCell ref="D40:D47"/>
+    <mergeCell ref="D48:D56"/>
+    <mergeCell ref="D57:D64"/>
   </mergeCells>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/raid_config.xlsx
+++ b/raid_config.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\new_bot\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{01275FB0-8C32-4F33-AF9E-824A92151D9D}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4DA38486-CD56-4F32-9C97-C56DC2BD46C8}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="1725" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -17,14 +17,14 @@
     <sheet name="DATA" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">DATA!$A$16:$D$79</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">DATA!$I$44:$K$44</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="248" uniqueCount="141">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="248" uniqueCount="146">
   <si>
     <t>활성화여부</t>
   </si>
@@ -385,10 +385,6 @@
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>지옥2</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
     <t>1,2,11</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
@@ -474,6 +470,24 @@
   <si>
     <t>펫경문_3000</t>
     <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>언딘알</t>
+  </si>
+  <si>
+    <t>카오닉스알</t>
+  </si>
+  <si>
+    <t>초기화꾸러미</t>
+  </si>
+  <si>
+    <t>펫경문_3000</t>
+  </si>
+  <si>
+    <t>공룡알</t>
+  </si>
+  <si>
+    <t>쿵야알</t>
   </si>
 </sst>
 </file>
@@ -772,7 +786,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
@@ -810,6 +824,7 @@
     <xf numFmtId="176" fontId="4" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
@@ -1306,7 +1321,7 @@
       <c r="Q3" s="5"/>
       <c r="R3" s="5"/>
       <c r="S3" s="5" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="T3" s="5"/>
       <c r="U3" s="5"/>
@@ -1357,7 +1372,7 @@
       <c r="Q4" s="5"/>
       <c r="R4" s="5"/>
       <c r="S4" s="5" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="T4" s="5"/>
       <c r="U4" s="5"/>
@@ -1408,7 +1423,7 @@
       <c r="Q5" s="5"/>
       <c r="R5" s="5"/>
       <c r="S5" s="5" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="T5" s="5"/>
       <c r="U5" s="5"/>
@@ -1459,7 +1474,7 @@
       <c r="Q6" s="5"/>
       <c r="R6" s="5"/>
       <c r="S6" s="5" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="T6" s="5"/>
       <c r="U6" s="5"/>
@@ -1510,7 +1525,7 @@
       <c r="Q7" s="5"/>
       <c r="R7" s="5"/>
       <c r="S7" s="5" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="T7" s="5"/>
       <c r="U7" s="5"/>
@@ -1536,10 +1551,10 @@
         <v>40</v>
       </c>
       <c r="F8" s="5">
-        <v>700000</v>
+        <v>600000</v>
       </c>
       <c r="G8" s="5">
-        <v>720000</v>
+        <v>620000</v>
       </c>
       <c r="H8" s="5">
         <v>30000</v>
@@ -1555,7 +1570,7 @@
         <v>5</v>
       </c>
       <c r="M8" s="5">
-        <v>80000</v>
+        <v>60000</v>
       </c>
       <c r="N8" s="5">
         <v>60</v>
@@ -1565,13 +1580,13 @@
       <c r="Q8" s="5"/>
       <c r="R8" s="5"/>
       <c r="S8" s="5" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="T8" s="5" t="s">
         <v>48</v>
       </c>
       <c r="U8" s="5" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="V8" s="5" t="s">
         <v>49</v>
@@ -1582,7 +1597,7 @@
     </row>
     <row r="9" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A9" s="5" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="B9" s="5" t="s">
         <v>50</v>
@@ -1597,10 +1612,10 @@
         <v>45</v>
       </c>
       <c r="F9" s="5">
-        <v>700000</v>
+        <v>600000</v>
       </c>
       <c r="G9" s="5">
-        <v>720000</v>
+        <v>620000</v>
       </c>
       <c r="H9" s="5">
         <v>30000</v>
@@ -1616,14 +1631,14 @@
         <v>5</v>
       </c>
       <c r="M9" s="5">
-        <v>100000</v>
+        <v>70000</v>
       </c>
       <c r="N9" s="5">
         <v>60</v>
       </c>
       <c r="O9" s="5"/>
       <c r="P9" s="5">
-        <v>1000000</v>
+        <v>600000</v>
       </c>
       <c r="Q9" s="5">
         <v>600</v>
@@ -1632,25 +1647,25 @@
         <v>29</v>
       </c>
       <c r="S9" s="5" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="T9" s="5" t="s">
+        <v>128</v>
+      </c>
+      <c r="U9" s="5" t="s">
         <v>129</v>
       </c>
-      <c r="U9" s="5" t="s">
+      <c r="V9" s="5" t="s">
         <v>130</v>
       </c>
-      <c r="V9" s="5" t="s">
+      <c r="W9" s="5" t="s">
         <v>131</v>
       </c>
-      <c r="W9" s="5" t="s">
-        <v>132</v>
-      </c>
       <c r="X9" s="5" t="s">
+        <v>133</v>
+      </c>
+      <c r="Y9" s="5" t="s">
         <v>134</v>
-      </c>
-      <c r="Y9" s="5" t="s">
-        <v>135</v>
       </c>
     </row>
     <row r="12" spans="1:25" x14ac:dyDescent="0.3">
@@ -1725,7 +1740,7 @@
         <v>9</v>
       </c>
       <c r="R23" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="24" spans="16:18" x14ac:dyDescent="0.3">
@@ -1769,7 +1784,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:D80"/>
+  <dimension ref="A1:M80"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
@@ -1852,7 +1867,7 @@
         <v>66</v>
       </c>
       <c r="C7" s="7" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.3">
@@ -1863,7 +1878,7 @@
         <v>68</v>
       </c>
       <c r="C8" s="7" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.3">
@@ -1885,7 +1900,7 @@
         <v>72</v>
       </c>
       <c r="C10" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.3">
@@ -2014,7 +2029,7 @@
         <v>26</v>
       </c>
       <c r="B22" s="13" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="C22" s="13">
         <v>2</v>
@@ -2147,7 +2162,7 @@
       </c>
       <c r="D32" s="19"/>
     </row>
-    <row r="33" spans="1:4" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A33" s="11" t="s">
         <v>33</v>
       </c>
@@ -2155,11 +2170,11 @@
         <v>100</v>
       </c>
       <c r="C33" s="7">
-        <v>10</v>
+        <v>9.5</v>
       </c>
       <c r="D33" s="19"/>
     </row>
-    <row r="34" spans="1:4" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A34" s="11" t="s">
         <v>33</v>
       </c>
@@ -2171,7 +2186,7 @@
       </c>
       <c r="D34" s="19"/>
     </row>
-    <row r="35" spans="1:4" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A35" s="11" t="s">
         <v>33</v>
       </c>
@@ -2183,7 +2198,7 @@
       </c>
       <c r="D35" s="19"/>
     </row>
-    <row r="36" spans="1:4" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A36" s="11" t="s">
         <v>33</v>
       </c>
@@ -2195,7 +2210,7 @@
       </c>
       <c r="D36" s="19"/>
     </row>
-    <row r="37" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A37" s="11" t="s">
         <v>33</v>
       </c>
@@ -2207,19 +2222,19 @@
       </c>
       <c r="D37" s="19"/>
     </row>
-    <row r="38" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A38" s="11" t="s">
         <v>33</v>
       </c>
       <c r="B38" s="7" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="C38" s="7">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="D38" s="19"/>
     </row>
-    <row r="39" spans="1:4" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:13" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A39" s="12" t="s">
         <v>33</v>
       </c>
@@ -2230,8 +2245,13 @@
         <v>0.5</v>
       </c>
       <c r="D39" s="20"/>
-    </row>
-    <row r="40" spans="1:4" ht="17.25" thickTop="1" x14ac:dyDescent="0.3">
+      <c r="H39" s="21"/>
+      <c r="I39" s="21"/>
+      <c r="J39" s="21"/>
+      <c r="K39" s="21"/>
+      <c r="L39" s="21"/>
+    </row>
+    <row r="40" spans="1:13" ht="17.25" thickTop="1" x14ac:dyDescent="0.3">
       <c r="A40" s="9" t="s">
         <v>36</v>
       </c>
@@ -2239,14 +2259,19 @@
         <v>98</v>
       </c>
       <c r="C40" s="10">
-        <v>64.5</v>
+        <v>63.5</v>
       </c>
       <c r="D40" s="18">
         <f>SUM(C40:C47)/100</f>
         <v>1</v>
       </c>
-    </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="H40" s="21"/>
+      <c r="I40" s="21"/>
+      <c r="J40" s="21"/>
+      <c r="K40" s="21"/>
+      <c r="L40" s="21"/>
+    </row>
+    <row r="41" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A41" s="11" t="s">
         <v>36</v>
       </c>
@@ -2257,8 +2282,13 @@
         <v>20</v>
       </c>
       <c r="D41" s="19"/>
-    </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="H41" s="21"/>
+      <c r="I41" s="21"/>
+      <c r="J41" s="21"/>
+      <c r="K41" s="21"/>
+      <c r="L41" s="21"/>
+    </row>
+    <row r="42" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A42" s="11" t="s">
         <v>36</v>
       </c>
@@ -2269,8 +2299,15 @@
         <v>10</v>
       </c>
       <c r="D42" s="19"/>
-    </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="G42" s="21"/>
+      <c r="H42" s="21"/>
+      <c r="I42" s="21"/>
+      <c r="J42" s="21"/>
+      <c r="K42" s="21"/>
+      <c r="L42" s="21"/>
+      <c r="M42" s="21"/>
+    </row>
+    <row r="43" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A43" s="11" t="s">
         <v>36</v>
       </c>
@@ -2281,20 +2318,34 @@
         <v>2</v>
       </c>
       <c r="D43" s="19"/>
-    </row>
-    <row r="44" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="G43" s="21"/>
+      <c r="H43" s="21"/>
+      <c r="I43" s="21"/>
+      <c r="J43" s="21"/>
+      <c r="K43" s="21"/>
+      <c r="L43" s="21"/>
+      <c r="M43" s="21"/>
+    </row>
+    <row r="44" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A44" s="11" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="B44" s="7" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="C44" s="7">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D44" s="19"/>
-    </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="G44" s="21"/>
+      <c r="H44" s="21"/>
+      <c r="I44" s="21"/>
+      <c r="J44" s="21"/>
+      <c r="K44" s="21"/>
+      <c r="L44" s="21"/>
+      <c r="M44" s="21"/>
+    </row>
+    <row r="45" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A45" s="11" t="s">
         <v>36</v>
       </c>
@@ -2305,8 +2356,15 @@
         <v>1</v>
       </c>
       <c r="D45" s="19"/>
-    </row>
-    <row r="46" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="G45" s="21"/>
+      <c r="H45" s="21"/>
+      <c r="I45" s="21"/>
+      <c r="J45" s="21"/>
+      <c r="K45" s="21"/>
+      <c r="L45" s="21"/>
+      <c r="M45" s="21"/>
+    </row>
+    <row r="46" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A46" s="11" t="s">
         <v>36</v>
       </c>
@@ -2317,8 +2375,15 @@
         <v>1</v>
       </c>
       <c r="D46" s="19"/>
-    </row>
-    <row r="47" spans="1:4" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="G46" s="21"/>
+      <c r="H46" s="21"/>
+      <c r="I46" s="21"/>
+      <c r="J46" s="21"/>
+      <c r="K46" s="21"/>
+      <c r="L46" s="21"/>
+      <c r="M46" s="21"/>
+    </row>
+    <row r="47" spans="1:13" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A47" s="12" t="s">
         <v>36</v>
       </c>
@@ -2329,8 +2394,15 @@
         <v>0.5</v>
       </c>
       <c r="D47" s="20"/>
-    </row>
-    <row r="48" spans="1:4" ht="17.25" thickTop="1" x14ac:dyDescent="0.3">
+      <c r="G47" s="21"/>
+      <c r="H47" s="21"/>
+      <c r="I47" s="21"/>
+      <c r="J47" s="21"/>
+      <c r="K47" s="21"/>
+      <c r="L47" s="21"/>
+      <c r="M47" s="21"/>
+    </row>
+    <row r="48" spans="1:13" ht="17.25" thickTop="1" x14ac:dyDescent="0.3">
       <c r="A48" s="9" t="s">
         <v>39</v>
       </c>
@@ -2342,10 +2414,17 @@
       </c>
       <c r="D48" s="18">
         <f>SUM(C48:C56)/100</f>
-        <v>1.0049999999999999</v>
-      </c>
-    </row>
-    <row r="49" spans="1:4" x14ac:dyDescent="0.3">
+        <v>1</v>
+      </c>
+      <c r="G48" s="21"/>
+      <c r="H48" s="21"/>
+      <c r="I48" s="21"/>
+      <c r="J48" s="21"/>
+      <c r="K48" s="21"/>
+      <c r="L48" s="21"/>
+      <c r="M48" s="21"/>
+    </row>
+    <row r="49" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A49" s="11" t="s">
         <v>39</v>
       </c>
@@ -2356,8 +2435,15 @@
         <v>20</v>
       </c>
       <c r="D49" s="19"/>
-    </row>
-    <row r="50" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="G49" s="21"/>
+      <c r="H49" s="21"/>
+      <c r="I49" s="21"/>
+      <c r="J49" s="21"/>
+      <c r="K49" s="21"/>
+      <c r="L49" s="21"/>
+      <c r="M49" s="21"/>
+    </row>
+    <row r="50" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A50" s="11" t="s">
         <v>39</v>
       </c>
@@ -2365,11 +2451,18 @@
         <v>109</v>
       </c>
       <c r="C50" s="7">
-        <v>13</v>
+        <v>8.5</v>
       </c>
       <c r="D50" s="19"/>
-    </row>
-    <row r="51" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="G50" s="21"/>
+      <c r="H50" s="21"/>
+      <c r="I50" s="21"/>
+      <c r="J50" s="21"/>
+      <c r="K50" s="21"/>
+      <c r="L50" s="21"/>
+      <c r="M50" s="21"/>
+    </row>
+    <row r="51" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A51" s="11" t="s">
         <v>39</v>
       </c>
@@ -2377,47 +2470,75 @@
         <v>104</v>
       </c>
       <c r="C51" s="7">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D51" s="19"/>
-    </row>
-    <row r="52" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="G51" s="21"/>
+      <c r="H51" s="21"/>
+      <c r="I51" s="21"/>
+      <c r="J51" s="21"/>
+      <c r="K51" s="21"/>
+      <c r="L51" s="21"/>
+      <c r="M51" s="21"/>
+    </row>
+    <row r="52" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A52" s="11" t="s">
         <v>39</v>
       </c>
       <c r="B52" s="7" t="s">
-        <v>88</v>
+        <v>110</v>
       </c>
       <c r="C52" s="7">
-        <v>1.5</v>
+        <v>4</v>
       </c>
       <c r="D52" s="19"/>
-    </row>
-    <row r="53" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="G52" s="21"/>
+      <c r="H52" s="21"/>
+      <c r="I52" s="21"/>
+      <c r="J52" s="21"/>
+      <c r="K52" s="21"/>
+      <c r="L52" s="21"/>
+      <c r="M52" s="21"/>
+    </row>
+    <row r="53" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A53" s="11" t="s">
         <v>39</v>
       </c>
       <c r="B53" s="7" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="C53" s="7">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="D53" s="19"/>
-    </row>
-    <row r="54" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="G53" s="21"/>
+      <c r="H53" s="21"/>
+      <c r="I53" s="21"/>
+      <c r="J53" s="21"/>
+      <c r="K53" s="21"/>
+      <c r="L53" s="21"/>
+      <c r="M53" s="21"/>
+    </row>
+    <row r="54" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A54" s="11" t="s">
         <v>39</v>
       </c>
       <c r="B54" s="7" t="s">
-        <v>138</v>
+        <v>90</v>
       </c>
       <c r="C54" s="7">
         <v>1</v>
       </c>
       <c r="D54" s="19"/>
-    </row>
-    <row r="55" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="G54" s="21"/>
+      <c r="H54" s="21"/>
+      <c r="I54" s="21"/>
+      <c r="J54" s="21"/>
+      <c r="K54" s="21"/>
+      <c r="L54" s="21"/>
+      <c r="M54" s="21"/>
+    </row>
+    <row r="55" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A55" s="11" t="s">
         <v>39</v>
       </c>
@@ -2428,20 +2549,33 @@
         <v>0.5</v>
       </c>
       <c r="D55" s="19"/>
-    </row>
-    <row r="56" spans="1:4" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="G55" s="21"/>
+      <c r="H55" s="21"/>
+      <c r="I55" s="21"/>
+      <c r="J55" s="21"/>
+      <c r="K55" s="21"/>
+      <c r="L55" s="21"/>
+      <c r="M55" s="21"/>
+    </row>
+    <row r="56" spans="1:13" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A56" s="12" t="s">
         <v>39</v>
       </c>
       <c r="B56" s="13" t="s">
-        <v>116</v>
+        <v>140</v>
       </c>
       <c r="C56" s="13">
         <v>0.5</v>
       </c>
       <c r="D56" s="20"/>
-    </row>
-    <row r="57" spans="1:4" ht="17.25" thickTop="1" x14ac:dyDescent="0.3">
+      <c r="G56" s="21"/>
+      <c r="H56" s="21"/>
+      <c r="I56" s="21"/>
+      <c r="J56" s="21"/>
+      <c r="K56" s="21"/>
+      <c r="L56" s="21"/>
+    </row>
+    <row r="57" spans="1:13" ht="17.25" thickTop="1" x14ac:dyDescent="0.3">
       <c r="A57" s="10" t="s">
         <v>42</v>
       </c>
@@ -2449,14 +2583,14 @@
         <v>85</v>
       </c>
       <c r="C57" s="10">
-        <v>59.5</v>
+        <v>58.5</v>
       </c>
       <c r="D57" s="18">
         <f>SUM(C57:C64)/100</f>
         <v>1</v>
       </c>
     </row>
-    <row r="58" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A58" s="7" t="s">
         <v>42</v>
       </c>
@@ -2464,11 +2598,11 @@
         <v>87</v>
       </c>
       <c r="C58" s="7">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="D58" s="19"/>
     </row>
-    <row r="59" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A59" s="7" t="s">
         <v>42</v>
       </c>
@@ -2476,11 +2610,11 @@
         <v>104</v>
       </c>
       <c r="C59" s="7">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="D59" s="19"/>
     </row>
-    <row r="60" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A60" s="7" t="s">
         <v>42</v>
       </c>
@@ -2488,52 +2622,52 @@
         <v>110</v>
       </c>
       <c r="C60" s="7">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="D60" s="19"/>
     </row>
-    <row r="61" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A61" s="7" t="s">
         <v>42</v>
       </c>
       <c r="B61" s="7" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C61" s="7">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D61" s="19"/>
     </row>
-    <row r="62" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A62" s="7" t="s">
         <v>42</v>
       </c>
       <c r="B62" s="7" t="s">
-        <v>89</v>
+        <v>111</v>
       </c>
       <c r="C62" s="7">
         <v>2</v>
       </c>
       <c r="D62" s="19"/>
     </row>
-    <row r="63" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A63" s="7" t="s">
         <v>42</v>
       </c>
       <c r="B63" s="7" t="s">
-        <v>111</v>
+        <v>90</v>
       </c>
       <c r="C63" s="7">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D63" s="19"/>
     </row>
-    <row r="64" spans="1:4" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:13" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A64" s="13" t="s">
         <v>42</v>
       </c>
       <c r="B64" s="13" t="s">
-        <v>117</v>
+        <v>141</v>
       </c>
       <c r="C64" s="13">
         <v>0.5</v>
@@ -2560,7 +2694,7 @@
         <v>45</v>
       </c>
       <c r="B66" s="7" t="s">
-        <v>128</v>
+        <v>142</v>
       </c>
       <c r="C66" s="7">
         <v>20</v>
@@ -2572,10 +2706,10 @@
         <v>45</v>
       </c>
       <c r="B67" s="7" t="s">
-        <v>140</v>
+        <v>112</v>
       </c>
       <c r="C67" s="7">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="D67" s="19"/>
     </row>
@@ -2584,16 +2718,16 @@
         <v>45</v>
       </c>
       <c r="B68" s="7" t="s">
-        <v>112</v>
+        <v>143</v>
       </c>
       <c r="C68" s="7">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="D68" s="19"/>
     </row>
     <row r="69" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A69" s="7" t="s">
-        <v>118</v>
+        <v>45</v>
       </c>
       <c r="B69" s="7" t="s">
         <v>90</v>
@@ -2608,7 +2742,7 @@
         <v>45</v>
       </c>
       <c r="B70" s="7" t="s">
-        <v>115</v>
+        <v>144</v>
       </c>
       <c r="C70" s="7">
         <v>1</v>
@@ -2620,7 +2754,7 @@
         <v>45</v>
       </c>
       <c r="B71" s="7" t="s">
-        <v>116</v>
+        <v>140</v>
       </c>
       <c r="C71" s="7">
         <v>1</v>
@@ -2632,7 +2766,7 @@
         <v>45</v>
       </c>
       <c r="B72" s="15" t="s">
-        <v>117</v>
+        <v>141</v>
       </c>
       <c r="C72" s="7">
         <v>1</v>
@@ -2644,7 +2778,7 @@
         <v>45</v>
       </c>
       <c r="B73" s="17" t="s">
-        <v>114</v>
+        <v>145</v>
       </c>
       <c r="C73" s="13">
         <v>1</v>
@@ -2683,7 +2817,7 @@
         <v>50</v>
       </c>
       <c r="B76" s="7" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="C76" s="7">
         <v>20</v>
@@ -2695,7 +2829,7 @@
         <v>50</v>
       </c>
       <c r="B77" s="7" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="C77" s="7">
         <v>6</v>
@@ -2728,7 +2862,11 @@
     </row>
     <row r="80" spans="1:4" ht="17.25" thickTop="1" x14ac:dyDescent="0.3"/>
   </sheetData>
-  <autoFilter ref="A16:D79" xr:uid="{91CBCC93-600B-4657-92F3-9623C670C48B}"/>
+  <autoFilter ref="I44:K44" xr:uid="{E7DB1D67-B4A6-4A8E-B4FB-E7773D6B854F}">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="I45:K52">
+      <sortCondition descending="1" ref="K44"/>
+    </sortState>
+  </autoFilter>
   <mergeCells count="8">
     <mergeCell ref="D65:D73"/>
     <mergeCell ref="D74:D79"/>

--- a/raid_config.xlsx
+++ b/raid_config.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\new_bot\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4DA38486-CD56-4F32-9C97-C56DC2BD46C8}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AE7413A9-869D-4FCC-BBF9-785362C5A6FD}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="1725" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="1725" windowWidth="29040" windowHeight="17520" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="레이드설정" sheetId="1" r:id="rId1"/>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="248" uniqueCount="146">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="260" uniqueCount="144">
   <si>
     <t>활성화여부</t>
   </si>
@@ -374,14 +374,6 @@
   </si>
   <si>
     <t>공룡알</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>언딘알</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>카오닉스알</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
@@ -815,6 +807,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="176" fontId="4" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -824,7 +817,6 @@
     <xf numFmtId="176" fontId="4" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
@@ -1321,7 +1313,7 @@
       <c r="Q3" s="5"/>
       <c r="R3" s="5"/>
       <c r="S3" s="5" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="T3" s="5"/>
       <c r="U3" s="5"/>
@@ -1372,7 +1364,7 @@
       <c r="Q4" s="5"/>
       <c r="R4" s="5"/>
       <c r="S4" s="5" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="T4" s="5"/>
       <c r="U4" s="5"/>
@@ -1423,7 +1415,7 @@
       <c r="Q5" s="5"/>
       <c r="R5" s="5"/>
       <c r="S5" s="5" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="T5" s="5"/>
       <c r="U5" s="5"/>
@@ -1474,7 +1466,7 @@
       <c r="Q6" s="5"/>
       <c r="R6" s="5"/>
       <c r="S6" s="5" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="T6" s="5"/>
       <c r="U6" s="5"/>
@@ -1525,7 +1517,7 @@
       <c r="Q7" s="5"/>
       <c r="R7" s="5"/>
       <c r="S7" s="5" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="T7" s="5"/>
       <c r="U7" s="5"/>
@@ -1580,13 +1572,13 @@
       <c r="Q8" s="5"/>
       <c r="R8" s="5"/>
       <c r="S8" s="5" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="T8" s="5" t="s">
         <v>48</v>
       </c>
       <c r="U8" s="5" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="V8" s="5" t="s">
         <v>49</v>
@@ -1597,7 +1589,7 @@
     </row>
     <row r="9" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A9" s="5" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="B9" s="5" t="s">
         <v>50</v>
@@ -1647,25 +1639,25 @@
         <v>29</v>
       </c>
       <c r="S9" s="5" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="T9" s="5" t="s">
+        <v>126</v>
+      </c>
+      <c r="U9" s="5" t="s">
+        <v>127</v>
+      </c>
+      <c r="V9" s="5" t="s">
         <v>128</v>
       </c>
-      <c r="U9" s="5" t="s">
+      <c r="W9" s="5" t="s">
         <v>129</v>
       </c>
-      <c r="V9" s="5" t="s">
-        <v>130</v>
-      </c>
-      <c r="W9" s="5" t="s">
+      <c r="X9" s="5" t="s">
         <v>131</v>
       </c>
-      <c r="X9" s="5" t="s">
-        <v>133</v>
-      </c>
       <c r="Y9" s="5" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
     </row>
     <row r="12" spans="1:25" x14ac:dyDescent="0.3">
@@ -1740,7 +1732,7 @@
         <v>9</v>
       </c>
       <c r="R23" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
     </row>
     <row r="24" spans="16:18" x14ac:dyDescent="0.3">
@@ -1784,7 +1776,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:M80"/>
+  <dimension ref="A1:M78"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
@@ -1867,7 +1859,7 @@
         <v>66</v>
       </c>
       <c r="C7" s="7" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.3">
@@ -1878,7 +1870,7 @@
         <v>68</v>
       </c>
       <c r="C8" s="7" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.3">
@@ -1900,7 +1892,7 @@
         <v>72</v>
       </c>
       <c r="C10" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.3">
@@ -1971,7 +1963,7 @@
       <c r="C17" s="10">
         <v>60</v>
       </c>
-      <c r="D17" s="18">
+      <c r="D17" s="19">
         <f>SUM(C17:C22)/100</f>
         <v>1</v>
       </c>
@@ -1986,7 +1978,7 @@
       <c r="C18" s="7">
         <v>20</v>
       </c>
-      <c r="D18" s="19"/>
+      <c r="D18" s="20"/>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A19" s="11" t="s">
@@ -1998,7 +1990,7 @@
       <c r="C19" s="7">
         <v>10</v>
       </c>
-      <c r="D19" s="19"/>
+      <c r="D19" s="20"/>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A20" s="11" t="s">
@@ -2010,7 +2002,7 @@
       <c r="C20" s="7">
         <v>5</v>
       </c>
-      <c r="D20" s="19"/>
+      <c r="D20" s="20"/>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A21" s="11" t="s">
@@ -2022,19 +2014,19 @@
       <c r="C21" s="7">
         <v>3</v>
       </c>
-      <c r="D21" s="19"/>
+      <c r="D21" s="20"/>
     </row>
     <row r="22" spans="1:4" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A22" s="12" t="s">
         <v>26</v>
       </c>
       <c r="B22" s="13" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="C22" s="13">
         <v>2</v>
       </c>
-      <c r="D22" s="20"/>
+      <c r="D22" s="21"/>
     </row>
     <row r="23" spans="1:4" ht="17.25" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
       <c r="A23" s="9" t="s">
@@ -2046,7 +2038,7 @@
       <c r="C23" s="10">
         <v>60</v>
       </c>
-      <c r="D23" s="18">
+      <c r="D23" s="19">
         <f>SUM(C23:C29)/100</f>
         <v>1</v>
       </c>
@@ -2061,7 +2053,7 @@
       <c r="C24" s="7">
         <v>20</v>
       </c>
-      <c r="D24" s="19"/>
+      <c r="D24" s="20"/>
     </row>
     <row r="25" spans="1:4" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="11" t="s">
@@ -2073,7 +2065,7 @@
       <c r="C25" s="7">
         <v>5</v>
       </c>
-      <c r="D25" s="19"/>
+      <c r="D25" s="20"/>
     </row>
     <row r="26" spans="1:4" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="11" t="s">
@@ -2085,7 +2077,7 @@
       <c r="C26" s="7">
         <v>5</v>
       </c>
-      <c r="D26" s="19"/>
+      <c r="D26" s="20"/>
     </row>
     <row r="27" spans="1:4" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="11" t="s">
@@ -2097,7 +2089,7 @@
       <c r="C27" s="7">
         <v>5</v>
       </c>
-      <c r="D27" s="19"/>
+      <c r="D27" s="20"/>
     </row>
     <row r="28" spans="1:4" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="11" t="s">
@@ -2109,7 +2101,7 @@
       <c r="C28" s="7">
         <v>3</v>
       </c>
-      <c r="D28" s="19"/>
+      <c r="D28" s="20"/>
     </row>
     <row r="29" spans="1:4" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A29" s="12" t="s">
@@ -2121,7 +2113,7 @@
       <c r="C29" s="13">
         <v>2</v>
       </c>
-      <c r="D29" s="20"/>
+      <c r="D29" s="21"/>
     </row>
     <row r="30" spans="1:4" ht="17.25" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
       <c r="A30" s="9" t="s">
@@ -2131,9 +2123,9 @@
         <v>92</v>
       </c>
       <c r="C30" s="10">
-        <v>61</v>
-      </c>
-      <c r="D30" s="18">
+        <v>60</v>
+      </c>
+      <c r="D30" s="19">
         <f>SUM(C30:C39)/100</f>
         <v>1</v>
       </c>
@@ -2148,7 +2140,7 @@
       <c r="C31" s="7">
         <v>10</v>
       </c>
-      <c r="D31" s="19"/>
+      <c r="D31" s="20"/>
     </row>
     <row r="32" spans="1:4" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32" s="11" t="s">
@@ -2160,7 +2152,7 @@
       <c r="C32" s="7">
         <v>10</v>
       </c>
-      <c r="D32" s="19"/>
+      <c r="D32" s="20"/>
     </row>
     <row r="33" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A33" s="11" t="s">
@@ -2170,9 +2162,9 @@
         <v>100</v>
       </c>
       <c r="C33" s="7">
-        <v>9.5</v>
-      </c>
-      <c r="D33" s="19"/>
+        <v>8</v>
+      </c>
+      <c r="D33" s="20"/>
     </row>
     <row r="34" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A34" s="11" t="s">
@@ -2184,7 +2176,7 @@
       <c r="C34" s="7">
         <v>5</v>
       </c>
-      <c r="D34" s="19"/>
+      <c r="D34" s="20"/>
     </row>
     <row r="35" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A35" s="11" t="s">
@@ -2196,7 +2188,7 @@
       <c r="C35" s="7">
         <v>1</v>
       </c>
-      <c r="D35" s="19"/>
+      <c r="D35" s="20"/>
     </row>
     <row r="36" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A36" s="11" t="s">
@@ -2208,7 +2200,7 @@
       <c r="C36" s="7">
         <v>1</v>
       </c>
-      <c r="D36" s="19"/>
+      <c r="D36" s="20"/>
     </row>
     <row r="37" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A37" s="11" t="s">
@@ -2218,21 +2210,21 @@
         <v>104</v>
       </c>
       <c r="C37" s="7">
-        <v>1</v>
-      </c>
-      <c r="D37" s="19"/>
+        <v>2</v>
+      </c>
+      <c r="D37" s="20"/>
     </row>
     <row r="38" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A38" s="11" t="s">
         <v>33</v>
       </c>
       <c r="B38" s="7" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="C38" s="7">
-        <v>1</v>
-      </c>
-      <c r="D38" s="19"/>
+        <v>2</v>
+      </c>
+      <c r="D38" s="20"/>
     </row>
     <row r="39" spans="1:13" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A39" s="12" t="s">
@@ -2242,14 +2234,14 @@
         <v>114</v>
       </c>
       <c r="C39" s="13">
-        <v>0.5</v>
-      </c>
-      <c r="D39" s="20"/>
-      <c r="H39" s="21"/>
-      <c r="I39" s="21"/>
-      <c r="J39" s="21"/>
-      <c r="K39" s="21"/>
-      <c r="L39" s="21"/>
+        <v>1</v>
+      </c>
+      <c r="D39" s="21"/>
+      <c r="H39" s="18"/>
+      <c r="I39" s="18"/>
+      <c r="J39" s="18"/>
+      <c r="K39" s="18"/>
+      <c r="L39" s="18"/>
     </row>
     <row r="40" spans="1:13" ht="17.25" thickTop="1" x14ac:dyDescent="0.3">
       <c r="A40" s="9" t="s">
@@ -2259,17 +2251,17 @@
         <v>98</v>
       </c>
       <c r="C40" s="10">
-        <v>63.5</v>
-      </c>
-      <c r="D40" s="18">
+        <v>60</v>
+      </c>
+      <c r="D40" s="19">
         <f>SUM(C40:C47)/100</f>
         <v>1</v>
       </c>
-      <c r="H40" s="21"/>
-      <c r="I40" s="21"/>
-      <c r="J40" s="21"/>
-      <c r="K40" s="21"/>
-      <c r="L40" s="21"/>
+      <c r="H40" s="18"/>
+      <c r="I40" s="18"/>
+      <c r="J40" s="18"/>
+      <c r="K40" s="18"/>
+      <c r="L40" s="18"/>
     </row>
     <row r="41" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A41" s="11" t="s">
@@ -2281,12 +2273,12 @@
       <c r="C41" s="7">
         <v>20</v>
       </c>
-      <c r="D41" s="19"/>
-      <c r="H41" s="21"/>
-      <c r="I41" s="21"/>
-      <c r="J41" s="21"/>
-      <c r="K41" s="21"/>
-      <c r="L41" s="21"/>
+      <c r="D41" s="20"/>
+      <c r="H41" s="18"/>
+      <c r="I41" s="18"/>
+      <c r="J41" s="18"/>
+      <c r="K41" s="18"/>
+      <c r="L41" s="18"/>
     </row>
     <row r="42" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A42" s="11" t="s">
@@ -2296,18 +2288,18 @@
         <v>106</v>
       </c>
       <c r="C42" s="7">
-        <v>10</v>
-      </c>
-      <c r="D42" s="19"/>
-      <c r="G42" s="21"/>
-      <c r="H42" s="21"/>
-      <c r="I42" s="21"/>
-      <c r="J42" s="21"/>
-      <c r="K42" s="21"/>
-      <c r="L42" s="21"/>
-      <c r="M42" s="21"/>
-    </row>
-    <row r="43" spans="1:13" x14ac:dyDescent="0.3">
+        <v>9</v>
+      </c>
+      <c r="D42" s="20"/>
+      <c r="G42" s="18"/>
+      <c r="H42" s="18"/>
+      <c r="I42" s="18"/>
+      <c r="J42" s="18"/>
+      <c r="K42" s="18"/>
+      <c r="L42" s="18"/>
+      <c r="M42" s="18"/>
+    </row>
+    <row r="43" spans="1:13" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A43" s="11" t="s">
         <v>36</v>
       </c>
@@ -2315,35 +2307,41 @@
         <v>104</v>
       </c>
       <c r="C43" s="7">
-        <v>2</v>
-      </c>
-      <c r="D43" s="19"/>
-      <c r="G43" s="21"/>
-      <c r="H43" s="21"/>
-      <c r="I43" s="21"/>
-      <c r="J43" s="21"/>
-      <c r="K43" s="21"/>
-      <c r="L43" s="21"/>
-      <c r="M43" s="21"/>
-    </row>
-    <row r="44" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+        <v>4</v>
+      </c>
+      <c r="D43" s="20"/>
+      <c r="G43" s="18"/>
+      <c r="H43" s="18"/>
+      <c r="I43" s="18"/>
+      <c r="J43" s="18"/>
+      <c r="K43" s="18"/>
+      <c r="L43" s="18"/>
+      <c r="M43" s="18"/>
+    </row>
+    <row r="44" spans="1:13" ht="17.25" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
       <c r="A44" s="11" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="B44" s="7" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="C44" s="7">
-        <v>2</v>
-      </c>
-      <c r="D44" s="19"/>
-      <c r="G44" s="21"/>
-      <c r="H44" s="21"/>
-      <c r="I44" s="21"/>
-      <c r="J44" s="21"/>
-      <c r="K44" s="21"/>
-      <c r="L44" s="21"/>
-      <c r="M44" s="21"/>
+        <v>4</v>
+      </c>
+      <c r="D44" s="20"/>
+      <c r="G44" s="18"/>
+      <c r="H44" s="18"/>
+      <c r="I44" s="10" t="s">
+        <v>42</v>
+      </c>
+      <c r="J44" s="10" t="s">
+        <v>85</v>
+      </c>
+      <c r="K44" s="10">
+        <v>50</v>
+      </c>
+      <c r="L44" s="18"/>
+      <c r="M44" s="18"/>
     </row>
     <row r="45" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A45" s="11" t="s">
@@ -2355,14 +2353,20 @@
       <c r="C45" s="7">
         <v>1</v>
       </c>
-      <c r="D45" s="19"/>
-      <c r="G45" s="21"/>
-      <c r="H45" s="21"/>
-      <c r="I45" s="21"/>
-      <c r="J45" s="21"/>
-      <c r="K45" s="21"/>
-      <c r="L45" s="21"/>
-      <c r="M45" s="21"/>
+      <c r="D45" s="20"/>
+      <c r="G45" s="18"/>
+      <c r="H45" s="18"/>
+      <c r="I45" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="J45" s="7" t="s">
+        <v>104</v>
+      </c>
+      <c r="K45" s="7">
+        <v>16</v>
+      </c>
+      <c r="L45" s="18"/>
+      <c r="M45" s="18"/>
     </row>
     <row r="46" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A46" s="11" t="s">
@@ -2374,14 +2378,20 @@
       <c r="C46" s="7">
         <v>1</v>
       </c>
-      <c r="D46" s="19"/>
-      <c r="G46" s="21"/>
-      <c r="H46" s="21"/>
-      <c r="I46" s="21"/>
-      <c r="J46" s="21"/>
-      <c r="K46" s="21"/>
-      <c r="L46" s="21"/>
-      <c r="M46" s="21"/>
+      <c r="D46" s="20"/>
+      <c r="G46" s="18"/>
+      <c r="H46" s="18"/>
+      <c r="I46" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="J46" s="7" t="s">
+        <v>110</v>
+      </c>
+      <c r="K46" s="7">
+        <v>16</v>
+      </c>
+      <c r="L46" s="18"/>
+      <c r="M46" s="18"/>
     </row>
     <row r="47" spans="1:13" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A47" s="12" t="s">
@@ -2391,16 +2401,22 @@
         <v>115</v>
       </c>
       <c r="C47" s="13">
-        <v>0.5</v>
-      </c>
-      <c r="D47" s="20"/>
-      <c r="G47" s="21"/>
-      <c r="H47" s="21"/>
-      <c r="I47" s="21"/>
-      <c r="J47" s="21"/>
-      <c r="K47" s="21"/>
-      <c r="L47" s="21"/>
-      <c r="M47" s="21"/>
+        <v>1</v>
+      </c>
+      <c r="D47" s="21"/>
+      <c r="G47" s="18"/>
+      <c r="H47" s="18"/>
+      <c r="I47" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="J47" s="7" t="s">
+        <v>87</v>
+      </c>
+      <c r="K47" s="7">
+        <v>12</v>
+      </c>
+      <c r="L47" s="18"/>
+      <c r="M47" s="18"/>
     </row>
     <row r="48" spans="1:13" ht="17.25" thickTop="1" x14ac:dyDescent="0.3">
       <c r="A48" s="9" t="s">
@@ -2410,19 +2426,25 @@
         <v>105</v>
       </c>
       <c r="C48" s="10">
-        <v>60</v>
-      </c>
-      <c r="D48" s="18">
+        <v>51</v>
+      </c>
+      <c r="D48" s="19">
         <f>SUM(C48:C56)/100</f>
         <v>1</v>
       </c>
-      <c r="G48" s="21"/>
-      <c r="H48" s="21"/>
-      <c r="I48" s="21"/>
-      <c r="J48" s="21"/>
-      <c r="K48" s="21"/>
-      <c r="L48" s="21"/>
-      <c r="M48" s="21"/>
+      <c r="G48" s="18"/>
+      <c r="H48" s="18"/>
+      <c r="I48" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="J48" s="7" t="s">
+        <v>89</v>
+      </c>
+      <c r="K48" s="7">
+        <v>2</v>
+      </c>
+      <c r="L48" s="18"/>
+      <c r="M48" s="18"/>
     </row>
     <row r="49" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A49" s="11" t="s">
@@ -2434,14 +2456,20 @@
       <c r="C49" s="7">
         <v>20</v>
       </c>
-      <c r="D49" s="19"/>
-      <c r="G49" s="21"/>
-      <c r="H49" s="21"/>
-      <c r="I49" s="21"/>
-      <c r="J49" s="21"/>
-      <c r="K49" s="21"/>
-      <c r="L49" s="21"/>
-      <c r="M49" s="21"/>
+      <c r="D49" s="20"/>
+      <c r="G49" s="18"/>
+      <c r="H49" s="18"/>
+      <c r="I49" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="J49" s="7" t="s">
+        <v>111</v>
+      </c>
+      <c r="K49" s="7">
+        <v>2</v>
+      </c>
+      <c r="L49" s="18"/>
+      <c r="M49" s="18"/>
     </row>
     <row r="50" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A50" s="11" t="s">
@@ -2451,18 +2479,24 @@
         <v>109</v>
       </c>
       <c r="C50" s="7">
-        <v>8.5</v>
-      </c>
-      <c r="D50" s="19"/>
-      <c r="G50" s="21"/>
-      <c r="H50" s="21"/>
-      <c r="I50" s="21"/>
-      <c r="J50" s="21"/>
-      <c r="K50" s="21"/>
-      <c r="L50" s="21"/>
-      <c r="M50" s="21"/>
-    </row>
-    <row r="51" spans="1:13" x14ac:dyDescent="0.3">
+        <v>8</v>
+      </c>
+      <c r="D50" s="20"/>
+      <c r="G50" s="18"/>
+      <c r="H50" s="18"/>
+      <c r="I50" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="J50" s="7" t="s">
+        <v>90</v>
+      </c>
+      <c r="K50" s="7">
+        <v>1</v>
+      </c>
+      <c r="L50" s="18"/>
+      <c r="M50" s="18"/>
+    </row>
+    <row r="51" spans="1:13" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A51" s="11" t="s">
         <v>39</v>
       </c>
@@ -2470,18 +2504,24 @@
         <v>104</v>
       </c>
       <c r="C51" s="7">
-        <v>4</v>
-      </c>
-      <c r="D51" s="19"/>
-      <c r="G51" s="21"/>
-      <c r="H51" s="21"/>
-      <c r="I51" s="21"/>
-      <c r="J51" s="21"/>
-      <c r="K51" s="21"/>
-      <c r="L51" s="21"/>
-      <c r="M51" s="21"/>
-    </row>
-    <row r="52" spans="1:13" x14ac:dyDescent="0.3">
+        <v>8</v>
+      </c>
+      <c r="D51" s="20"/>
+      <c r="G51" s="18"/>
+      <c r="H51" s="18"/>
+      <c r="I51" s="13" t="s">
+        <v>42</v>
+      </c>
+      <c r="J51" s="13" t="s">
+        <v>139</v>
+      </c>
+      <c r="K51" s="13">
+        <v>1</v>
+      </c>
+      <c r="L51" s="18"/>
+      <c r="M51" s="18"/>
+    </row>
+    <row r="52" spans="1:13" ht="17.25" thickTop="1" x14ac:dyDescent="0.3">
       <c r="A52" s="11" t="s">
         <v>39</v>
       </c>
@@ -2489,16 +2529,16 @@
         <v>110</v>
       </c>
       <c r="C52" s="7">
-        <v>4</v>
-      </c>
-      <c r="D52" s="19"/>
-      <c r="G52" s="21"/>
-      <c r="H52" s="21"/>
-      <c r="I52" s="21"/>
-      <c r="J52" s="21"/>
-      <c r="K52" s="21"/>
-      <c r="L52" s="21"/>
-      <c r="M52" s="21"/>
+        <v>8</v>
+      </c>
+      <c r="D52" s="20"/>
+      <c r="G52" s="18"/>
+      <c r="H52" s="18"/>
+      <c r="I52" s="18"/>
+      <c r="J52" s="18"/>
+      <c r="K52" s="18"/>
+      <c r="L52" s="18"/>
+      <c r="M52" s="18"/>
     </row>
     <row r="53" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A53" s="11" t="s">
@@ -2508,16 +2548,16 @@
         <v>88</v>
       </c>
       <c r="C53" s="7">
-        <v>1.5</v>
-      </c>
-      <c r="D53" s="19"/>
-      <c r="G53" s="21"/>
-      <c r="H53" s="21"/>
-      <c r="I53" s="21"/>
-      <c r="J53" s="21"/>
-      <c r="K53" s="21"/>
-      <c r="L53" s="21"/>
-      <c r="M53" s="21"/>
+        <v>2</v>
+      </c>
+      <c r="D53" s="20"/>
+      <c r="G53" s="18"/>
+      <c r="H53" s="18"/>
+      <c r="I53" s="18"/>
+      <c r="J53" s="18"/>
+      <c r="K53" s="18"/>
+      <c r="L53" s="18"/>
+      <c r="M53" s="18"/>
     </row>
     <row r="54" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A54" s="11" t="s">
@@ -2529,14 +2569,14 @@
       <c r="C54" s="7">
         <v>1</v>
       </c>
-      <c r="D54" s="19"/>
-      <c r="G54" s="21"/>
-      <c r="H54" s="21"/>
-      <c r="I54" s="21"/>
-      <c r="J54" s="21"/>
-      <c r="K54" s="21"/>
-      <c r="L54" s="21"/>
-      <c r="M54" s="21"/>
+      <c r="D54" s="20"/>
+      <c r="G54" s="18"/>
+      <c r="H54" s="18"/>
+      <c r="I54" s="18"/>
+      <c r="J54" s="18"/>
+      <c r="K54" s="18"/>
+      <c r="L54" s="18"/>
+      <c r="M54" s="18"/>
     </row>
     <row r="55" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A55" s="11" t="s">
@@ -2546,34 +2586,34 @@
         <v>111</v>
       </c>
       <c r="C55" s="7">
-        <v>0.5</v>
-      </c>
-      <c r="D55" s="19"/>
-      <c r="G55" s="21"/>
-      <c r="H55" s="21"/>
-      <c r="I55" s="21"/>
-      <c r="J55" s="21"/>
-      <c r="K55" s="21"/>
-      <c r="L55" s="21"/>
-      <c r="M55" s="21"/>
+        <v>1</v>
+      </c>
+      <c r="D55" s="20"/>
+      <c r="G55" s="18"/>
+      <c r="H55" s="18"/>
+      <c r="I55" s="18"/>
+      <c r="J55" s="18"/>
+      <c r="K55" s="18"/>
+      <c r="L55" s="18"/>
+      <c r="M55" s="18"/>
     </row>
     <row r="56" spans="1:13" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A56" s="12" t="s">
         <v>39</v>
       </c>
       <c r="B56" s="13" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="C56" s="13">
-        <v>0.5</v>
-      </c>
-      <c r="D56" s="20"/>
-      <c r="G56" s="21"/>
-      <c r="H56" s="21"/>
-      <c r="I56" s="21"/>
-      <c r="J56" s="21"/>
-      <c r="K56" s="21"/>
-      <c r="L56" s="21"/>
+        <v>1</v>
+      </c>
+      <c r="D56" s="21"/>
+      <c r="G56" s="18"/>
+      <c r="H56" s="18"/>
+      <c r="I56" s="18"/>
+      <c r="J56" s="18"/>
+      <c r="K56" s="18"/>
+      <c r="L56" s="18"/>
     </row>
     <row r="57" spans="1:13" ht="17.25" thickTop="1" x14ac:dyDescent="0.3">
       <c r="A57" s="10" t="s">
@@ -2583,9 +2623,9 @@
         <v>85</v>
       </c>
       <c r="C57" s="10">
-        <v>58.5</v>
-      </c>
-      <c r="D57" s="18">
+        <v>50</v>
+      </c>
+      <c r="D57" s="19">
         <f>SUM(C57:C64)/100</f>
         <v>1</v>
       </c>
@@ -2595,36 +2635,36 @@
         <v>42</v>
       </c>
       <c r="B58" s="7" t="s">
-        <v>87</v>
+        <v>104</v>
       </c>
       <c r="C58" s="7">
-        <v>20</v>
-      </c>
-      <c r="D58" s="19"/>
+        <v>16</v>
+      </c>
+      <c r="D58" s="20"/>
     </row>
     <row r="59" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A59" s="7" t="s">
         <v>42</v>
       </c>
       <c r="B59" s="7" t="s">
-        <v>104</v>
+        <v>110</v>
       </c>
       <c r="C59" s="7">
-        <v>8</v>
-      </c>
-      <c r="D59" s="19"/>
+        <v>16</v>
+      </c>
+      <c r="D59" s="20"/>
     </row>
     <row r="60" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A60" s="7" t="s">
         <v>42</v>
       </c>
       <c r="B60" s="7" t="s">
-        <v>110</v>
+        <v>87</v>
       </c>
       <c r="C60" s="7">
-        <v>8</v>
-      </c>
-      <c r="D60" s="19"/>
+        <v>12</v>
+      </c>
+      <c r="D60" s="20"/>
     </row>
     <row r="61" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A61" s="7" t="s">
@@ -2636,7 +2676,7 @@
       <c r="C61" s="7">
         <v>2</v>
       </c>
-      <c r="D61" s="19"/>
+      <c r="D61" s="20"/>
     </row>
     <row r="62" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A62" s="7" t="s">
@@ -2648,7 +2688,7 @@
       <c r="C62" s="7">
         <v>2</v>
       </c>
-      <c r="D62" s="19"/>
+      <c r="D62" s="20"/>
     </row>
     <row r="63" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A63" s="7" t="s">
@@ -2660,19 +2700,19 @@
       <c r="C63" s="7">
         <v>1</v>
       </c>
-      <c r="D63" s="19"/>
+      <c r="D63" s="20"/>
     </row>
     <row r="64" spans="1:13" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A64" s="13" t="s">
         <v>42</v>
       </c>
       <c r="B64" s="13" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="C64" s="13">
-        <v>0.5</v>
-      </c>
-      <c r="D64" s="20"/>
+        <v>1</v>
+      </c>
+      <c r="D64" s="21"/>
     </row>
     <row r="65" spans="1:4" ht="17.25" thickTop="1" x14ac:dyDescent="0.3">
       <c r="A65" s="10" t="s">
@@ -2682,9 +2722,9 @@
         <v>85</v>
       </c>
       <c r="C65" s="10">
-        <v>50</v>
-      </c>
-      <c r="D65" s="18">
+        <v>42</v>
+      </c>
+      <c r="D65" s="19">
         <f>SUM(C65:C73)/100</f>
         <v>1</v>
       </c>
@@ -2694,12 +2734,12 @@
         <v>45</v>
       </c>
       <c r="B66" s="7" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="C66" s="7">
         <v>20</v>
       </c>
-      <c r="D66" s="19"/>
+      <c r="D66" s="20"/>
     </row>
     <row r="67" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A67" s="7" t="s">
@@ -2711,19 +2751,19 @@
       <c r="C67" s="7">
         <v>20</v>
       </c>
-      <c r="D67" s="19"/>
+      <c r="D67" s="20"/>
     </row>
     <row r="68" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A68" s="7" t="s">
         <v>45</v>
       </c>
       <c r="B68" s="7" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="C68" s="7">
         <v>4</v>
       </c>
-      <c r="D68" s="19"/>
+      <c r="D68" s="20"/>
     </row>
     <row r="69" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A69" s="7" t="s">
@@ -2735,55 +2775,55 @@
       <c r="C69" s="7">
         <v>2</v>
       </c>
-      <c r="D69" s="19"/>
+      <c r="D69" s="20"/>
     </row>
     <row r="70" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A70" s="7" t="s">
         <v>45</v>
       </c>
       <c r="B70" s="7" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="C70" s="7">
-        <v>1</v>
-      </c>
-      <c r="D70" s="19"/>
+        <v>3</v>
+      </c>
+      <c r="D70" s="20"/>
     </row>
     <row r="71" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A71" s="7" t="s">
         <v>45</v>
       </c>
       <c r="B71" s="7" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="C71" s="7">
-        <v>1</v>
-      </c>
-      <c r="D71" s="19"/>
+        <v>3</v>
+      </c>
+      <c r="D71" s="20"/>
     </row>
     <row r="72" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A72" s="14" t="s">
         <v>45</v>
       </c>
       <c r="B72" s="15" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="C72" s="7">
-        <v>1</v>
-      </c>
-      <c r="D72" s="19"/>
+        <v>3</v>
+      </c>
+      <c r="D72" s="20"/>
     </row>
     <row r="73" spans="1:4" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A73" s="16" t="s">
         <v>45</v>
       </c>
       <c r="B73" s="17" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="C73" s="13">
-        <v>1</v>
-      </c>
-      <c r="D73" s="20"/>
+        <v>3</v>
+      </c>
+      <c r="D73" s="21"/>
     </row>
     <row r="74" spans="1:4" ht="17.25" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
       <c r="A74" s="10" t="s">
@@ -2795,8 +2835,8 @@
       <c r="C74" s="10">
         <v>40</v>
       </c>
-      <c r="D74" s="18">
-        <f>SUM(C74:C79)/100</f>
+      <c r="D74" s="19">
+        <f>SUM(C74:C77)/100</f>
         <v>1</v>
       </c>
     </row>
@@ -2810,66 +2850,42 @@
       <c r="C75" s="7">
         <v>30</v>
       </c>
-      <c r="D75" s="19"/>
+      <c r="D75" s="20"/>
     </row>
     <row r="76" spans="1:4" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A76" s="7" t="s">
         <v>50</v>
       </c>
       <c r="B76" s="7" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="C76" s="7">
         <v>20</v>
       </c>
-      <c r="D76" s="19"/>
-    </row>
-    <row r="77" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A77" s="7" t="s">
+      <c r="D76" s="20"/>
+    </row>
+    <row r="77" spans="1:4" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A77" s="13" t="s">
         <v>50</v>
       </c>
-      <c r="B77" s="7" t="s">
-        <v>139</v>
-      </c>
-      <c r="C77" s="7">
-        <v>6</v>
-      </c>
-      <c r="D77" s="19"/>
-    </row>
-    <row r="78" spans="1:4" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A78" s="7" t="s">
-        <v>50</v>
-      </c>
-      <c r="B78" s="7" t="s">
-        <v>116</v>
-      </c>
-      <c r="C78" s="7">
-        <v>2</v>
-      </c>
-      <c r="D78" s="19"/>
-    </row>
-    <row r="79" spans="1:4" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A79" s="13" t="s">
-        <v>50</v>
-      </c>
-      <c r="B79" s="17" t="s">
-        <v>117</v>
-      </c>
-      <c r="C79" s="13">
-        <v>2</v>
-      </c>
-      <c r="D79" s="20"/>
-    </row>
-    <row r="80" spans="1:4" ht="17.25" thickTop="1" x14ac:dyDescent="0.3"/>
+      <c r="B77" s="13" t="s">
+        <v>137</v>
+      </c>
+      <c r="C77" s="13">
+        <v>10</v>
+      </c>
+      <c r="D77" s="21"/>
+    </row>
+    <row r="78" spans="1:4" ht="17.25" thickTop="1" x14ac:dyDescent="0.3"/>
   </sheetData>
   <autoFilter ref="I44:K44" xr:uid="{E7DB1D67-B4A6-4A8E-B4FB-E7773D6B854F}">
-    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="I45:K52">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="I45:K51">
       <sortCondition descending="1" ref="K44"/>
     </sortState>
   </autoFilter>
   <mergeCells count="8">
     <mergeCell ref="D65:D73"/>
-    <mergeCell ref="D74:D79"/>
+    <mergeCell ref="D74:D77"/>
     <mergeCell ref="D17:D22"/>
     <mergeCell ref="D23:D29"/>
     <mergeCell ref="D30:D39"/>

--- a/raid_config.xlsx
+++ b/raid_config.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\new_bot\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7E6DA0AB-EBD6-4C6A-B067-659B96B28DC9}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2BC7FD5D-8701-4292-B2C8-F2FDC590130B}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="1725" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -17,14 +17,14 @@
     <sheet name="DATA" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">DATA!$I$44:$K$44</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">DATA!$I$43:$K$43</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="264" uniqueCount="136">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="260" uniqueCount="138">
   <si>
     <t>활성화여부</t>
   </si>
@@ -432,6 +432,14 @@
   </si>
   <si>
     <t>펫경문_3000</t>
+  </si>
+  <si>
+    <t>지옥2</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>지옥3</t>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -732,7 +740,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
@@ -767,6 +775,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
+    <xf numFmtId="176" fontId="4" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
@@ -1244,7 +1255,7 @@
         <v>40000</v>
       </c>
       <c r="H3" s="5">
-        <v>4000</v>
+        <v>0</v>
       </c>
       <c r="I3" s="5">
         <v>600</v>
@@ -1295,7 +1306,7 @@
         <v>100000</v>
       </c>
       <c r="H4" s="5">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="I4" s="5">
         <v>600</v>
@@ -1305,7 +1316,7 @@
         <v>200</v>
       </c>
       <c r="L4" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M4" s="5"/>
       <c r="N4" s="5"/>
@@ -1337,16 +1348,16 @@
         <v>40</v>
       </c>
       <c r="E5" s="5">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="F5" s="5">
-        <v>180000</v>
+        <v>200000</v>
       </c>
       <c r="G5" s="5">
-        <v>200000</v>
+        <v>220000</v>
       </c>
       <c r="H5" s="5">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I5" s="5">
         <v>600</v>
@@ -1356,7 +1367,7 @@
         <v>300</v>
       </c>
       <c r="L5" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M5" s="5"/>
       <c r="N5" s="5"/>
@@ -1388,26 +1399,26 @@
         <v>43</v>
       </c>
       <c r="E6" s="5">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="F6" s="5">
-        <v>280000</v>
+        <v>360000</v>
       </c>
       <c r="G6" s="5">
-        <v>300000</v>
+        <v>380000</v>
       </c>
       <c r="H6" s="5">
-        <v>20000</v>
+        <v>0</v>
       </c>
       <c r="I6" s="5">
-        <v>900</v>
+        <v>600</v>
       </c>
       <c r="J6" s="5"/>
       <c r="K6" s="5">
         <v>400</v>
       </c>
       <c r="L6" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M6" s="5"/>
       <c r="N6" s="5"/>
@@ -1439,26 +1450,26 @@
         <v>47</v>
       </c>
       <c r="E7" s="5">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="F7" s="5">
-        <v>380000</v>
+        <v>520000</v>
       </c>
       <c r="G7" s="5">
-        <v>400000</v>
+        <v>540000</v>
       </c>
       <c r="H7" s="5">
-        <v>25000</v>
+        <v>0</v>
       </c>
       <c r="I7" s="5">
-        <v>900</v>
+        <v>600</v>
       </c>
       <c r="J7" s="5"/>
       <c r="K7" s="5">
         <v>500</v>
       </c>
       <c r="L7" s="5">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M7" s="5"/>
       <c r="N7" s="5"/>
@@ -1490,7 +1501,7 @@
         <v>51</v>
       </c>
       <c r="E8" s="5">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="F8" s="5">
         <v>600000</v>
@@ -1499,17 +1510,17 @@
         <v>620000</v>
       </c>
       <c r="H8" s="5">
-        <v>30000</v>
+        <v>0</v>
       </c>
       <c r="I8" s="5">
-        <v>900</v>
+        <v>600</v>
       </c>
       <c r="J8" s="5"/>
       <c r="K8" s="5">
         <v>600</v>
       </c>
       <c r="L8" s="5">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M8" s="5">
         <v>60000</v>
@@ -1551,7 +1562,7 @@
         <v>58</v>
       </c>
       <c r="E9" s="5">
-        <v>45</v>
+        <v>35</v>
       </c>
       <c r="F9" s="5">
         <v>600000</v>
@@ -1560,17 +1571,17 @@
         <v>620000</v>
       </c>
       <c r="H9" s="5">
-        <v>30000</v>
+        <v>0</v>
       </c>
       <c r="I9" s="5">
-        <v>900</v>
+        <v>600</v>
       </c>
       <c r="J9" s="5"/>
       <c r="K9" s="5">
         <v>700</v>
       </c>
       <c r="L9" s="5">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M9" s="5">
         <v>70000</v>
@@ -1580,10 +1591,10 @@
       </c>
       <c r="O9" s="5"/>
       <c r="P9" s="5">
-        <v>600000</v>
+        <v>350000</v>
       </c>
       <c r="Q9" s="5">
-        <v>600</v>
+        <v>300</v>
       </c>
       <c r="R9" s="5" t="s">
         <v>59</v>
@@ -1720,13 +1731,13 @@
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup paperSize="9" orientation="portrait"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:K78"/>
+  <dimension ref="A1:K81"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="12" style="18" customWidth="1"/>
@@ -2250,14 +2261,14 @@
         <v>4</v>
       </c>
       <c r="D44" s="20"/>
-      <c r="I44" s="9" t="s">
-        <v>34</v>
-      </c>
-      <c r="J44" s="10" t="s">
-        <v>109</v>
-      </c>
-      <c r="K44" s="10">
-        <v>60</v>
+      <c r="I44" s="10" t="s">
+        <v>137</v>
+      </c>
+      <c r="J44" s="7" t="s">
+        <v>119</v>
+      </c>
+      <c r="K44" s="7">
+        <v>30</v>
       </c>
     </row>
     <row r="45" spans="1:11" x14ac:dyDescent="0.3">
@@ -2271,14 +2282,14 @@
         <v>1</v>
       </c>
       <c r="D45" s="20"/>
-      <c r="I45" s="11" t="s">
-        <v>34</v>
+      <c r="I45" s="7" t="s">
+        <v>137</v>
       </c>
       <c r="J45" s="7" t="s">
-        <v>115</v>
+        <v>120</v>
       </c>
       <c r="K45" s="7">
-        <v>10</v>
+        <v>30</v>
       </c>
     </row>
     <row r="46" spans="1:11" x14ac:dyDescent="0.3">
@@ -2292,14 +2303,14 @@
         <v>1</v>
       </c>
       <c r="D46" s="20"/>
-      <c r="I46" s="11" t="s">
-        <v>34</v>
+      <c r="I46" s="7" t="s">
+        <v>56</v>
       </c>
       <c r="J46" s="7" t="s">
-        <v>116</v>
+        <v>134</v>
       </c>
       <c r="K46" s="7">
-        <v>10</v>
+        <v>15</v>
       </c>
     </row>
     <row r="47" spans="1:11" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
@@ -2313,17 +2324,17 @@
         <v>1</v>
       </c>
       <c r="D47" s="21"/>
-      <c r="I47" s="11" t="s">
-        <v>34</v>
+      <c r="I47" s="7" t="s">
+        <v>56</v>
       </c>
       <c r="J47" s="7" t="s">
-        <v>117</v>
+        <v>107</v>
       </c>
       <c r="K47" s="7">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="48" spans="1:11" ht="17.25" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="48" spans="1:11" ht="17.25" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A48" s="9" t="s">
         <v>41</v>
       </c>
@@ -2337,17 +2348,17 @@
         <f>SUM(C48:C56)/100</f>
         <v>1</v>
       </c>
-      <c r="I48" s="11" t="s">
-        <v>34</v>
-      </c>
-      <c r="J48" s="7" t="s">
-        <v>118</v>
-      </c>
-      <c r="K48" s="7">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="49" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="I48" s="13" t="s">
+        <v>56</v>
+      </c>
+      <c r="J48" s="13" t="s">
+        <v>135</v>
+      </c>
+      <c r="K48" s="13">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="49" spans="1:11" ht="17.25" thickTop="1" x14ac:dyDescent="0.3">
       <c r="A49" s="11" t="s">
         <v>41</v>
       </c>
@@ -2358,15 +2369,9 @@
         <v>20</v>
       </c>
       <c r="D49" s="20"/>
-      <c r="I49" s="11" t="s">
-        <v>34</v>
-      </c>
-      <c r="J49" s="7" t="s">
-        <v>119</v>
-      </c>
-      <c r="K49" s="7">
-        <v>2</v>
-      </c>
+      <c r="I49" s="11"/>
+      <c r="J49" s="7"/>
+      <c r="K49" s="7"/>
     </row>
     <row r="50" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A50" s="11" t="s">
@@ -2379,15 +2384,9 @@
         <v>8</v>
       </c>
       <c r="D50" s="20"/>
-      <c r="I50" s="11" t="s">
-        <v>34</v>
-      </c>
-      <c r="J50" s="7" t="s">
-        <v>120</v>
-      </c>
-      <c r="K50" s="7">
-        <v>2</v>
-      </c>
+      <c r="I50" s="11"/>
+      <c r="J50" s="7"/>
+      <c r="K50" s="7"/>
     </row>
     <row r="51" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A51" s="11" t="s">
@@ -2400,15 +2399,9 @@
         <v>8</v>
       </c>
       <c r="D51" s="20"/>
-      <c r="I51" s="11" t="s">
-        <v>34</v>
-      </c>
-      <c r="J51" s="7" t="s">
-        <v>121</v>
-      </c>
-      <c r="K51" s="7">
-        <v>1</v>
-      </c>
+      <c r="I51" s="11"/>
+      <c r="J51" s="7"/>
+      <c r="K51" s="7"/>
     </row>
     <row r="52" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A52" s="11" t="s">
@@ -2421,15 +2414,9 @@
         <v>8</v>
       </c>
       <c r="D52" s="20"/>
-      <c r="I52" s="11" t="s">
-        <v>34</v>
-      </c>
-      <c r="J52" s="7" t="s">
-        <v>122</v>
-      </c>
-      <c r="K52" s="7">
-        <v>1</v>
-      </c>
+      <c r="I52" s="11"/>
+      <c r="J52" s="7"/>
+      <c r="K52" s="7"/>
     </row>
     <row r="53" spans="1:11" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A53" s="11" t="s">
@@ -2442,15 +2429,9 @@
         <v>2</v>
       </c>
       <c r="D53" s="20"/>
-      <c r="I53" s="12" t="s">
-        <v>34</v>
-      </c>
-      <c r="J53" s="13" t="s">
-        <v>123</v>
-      </c>
-      <c r="K53" s="13">
-        <v>1</v>
-      </c>
+      <c r="I53" s="12"/>
+      <c r="J53" s="13"/>
+      <c r="K53" s="13"/>
     </row>
     <row r="54" spans="1:11" ht="17.25" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
       <c r="A54" s="11" t="s">
@@ -2587,7 +2568,7 @@
       </c>
       <c r="D64" s="21"/>
     </row>
-    <row r="65" spans="1:4" ht="17.25" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:4" ht="17.25" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A65" s="10" t="s">
         <v>49</v>
       </c>
@@ -2595,46 +2576,46 @@
         <v>102</v>
       </c>
       <c r="C65" s="10">
-        <v>42</v>
+        <v>22</v>
       </c>
       <c r="D65" s="19">
-        <f>SUM(C65:C73)/100</f>
+        <f>SUM(C65:C75)/100</f>
         <v>1</v>
       </c>
     </row>
-    <row r="66" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:4" s="18" customFormat="1" ht="17.25" thickTop="1" x14ac:dyDescent="0.3">
       <c r="A66" s="7" t="s">
-        <v>49</v>
+        <v>136</v>
       </c>
       <c r="B66" s="7" t="s">
-        <v>107</v>
+        <v>119</v>
       </c>
       <c r="C66" s="7">
         <v>20</v>
       </c>
-      <c r="D66" s="20"/>
-    </row>
-    <row r="67" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="D66" s="22"/>
+    </row>
+    <row r="67" spans="1:4" s="18" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A67" s="7" t="s">
-        <v>49</v>
+        <v>136</v>
       </c>
       <c r="B67" s="7" t="s">
-        <v>134</v>
+        <v>120</v>
       </c>
       <c r="C67" s="7">
         <v>20</v>
       </c>
-      <c r="D67" s="20"/>
+      <c r="D67" s="22"/>
     </row>
     <row r="68" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A68" s="7" t="s">
         <v>49</v>
       </c>
       <c r="B68" s="7" t="s">
-        <v>135</v>
+        <v>107</v>
       </c>
       <c r="C68" s="7">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="D68" s="20"/>
     </row>
@@ -2643,10 +2624,10 @@
         <v>49</v>
       </c>
       <c r="B69" s="7" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="C69" s="7">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="D69" s="20"/>
     </row>
@@ -2655,10 +2636,10 @@
         <v>49</v>
       </c>
       <c r="B70" s="7" t="s">
-        <v>128</v>
+        <v>135</v>
       </c>
       <c r="C70" s="7">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D70" s="20"/>
     </row>
@@ -2667,93 +2648,129 @@
         <v>49</v>
       </c>
       <c r="B71" s="7" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="C71" s="7">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D71" s="20"/>
     </row>
     <row r="72" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A72" s="14" t="s">
+      <c r="A72" s="7" t="s">
         <v>49</v>
       </c>
-      <c r="B72" s="15" t="s">
-        <v>133</v>
+      <c r="B72" s="7" t="s">
+        <v>128</v>
       </c>
       <c r="C72" s="7">
         <v>3</v>
       </c>
       <c r="D72" s="20"/>
     </row>
-    <row r="73" spans="1:4" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A73" s="16" t="s">
+    <row r="73" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A73" s="7" t="s">
         <v>49</v>
       </c>
-      <c r="B73" s="17" t="s">
+      <c r="B73" s="7" t="s">
+        <v>132</v>
+      </c>
+      <c r="C73" s="7">
+        <v>3</v>
+      </c>
+      <c r="D73" s="20"/>
+    </row>
+    <row r="74" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A74" s="14" t="s">
+        <v>49</v>
+      </c>
+      <c r="B74" s="15" t="s">
+        <v>133</v>
+      </c>
+      <c r="C74" s="7">
+        <v>3</v>
+      </c>
+      <c r="D74" s="20"/>
+    </row>
+    <row r="75" spans="1:4" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A75" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="B75" s="17" t="s">
         <v>123</v>
       </c>
-      <c r="C73" s="13">
+      <c r="C75" s="13">
         <v>3</v>
       </c>
-      <c r="D73" s="21"/>
-    </row>
-    <row r="74" spans="1:4" ht="17.25" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
-      <c r="A74" s="10" t="s">
+      <c r="D75" s="21"/>
+    </row>
+    <row r="76" spans="1:4" ht="17.25" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A76" s="10" t="s">
         <v>56</v>
       </c>
-      <c r="B74" s="10" t="s">
-        <v>102</v>
-      </c>
-      <c r="C74" s="10">
-        <v>40</v>
-      </c>
-      <c r="D74" s="19">
-        <f>SUM(C74:C77)/100</f>
+      <c r="B76" s="7" t="s">
+        <v>119</v>
+      </c>
+      <c r="C76" s="7">
+        <v>30</v>
+      </c>
+      <c r="D76" s="19">
+        <f>SUM(C76:C80)/100</f>
         <v>1</v>
       </c>
     </row>
-    <row r="75" spans="1:4" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A75" s="7" t="s">
+    <row r="77" spans="1:4" s="18" customFormat="1" ht="17.25" thickTop="1" x14ac:dyDescent="0.3">
+      <c r="A77" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="B75" s="7" t="s">
+      <c r="B77" s="7" t="s">
+        <v>120</v>
+      </c>
+      <c r="C77" s="7">
+        <v>30</v>
+      </c>
+      <c r="D77" s="22"/>
+    </row>
+    <row r="78" spans="1:4" s="18" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A78" s="7" t="s">
+        <v>56</v>
+      </c>
+      <c r="B78" s="7" t="s">
         <v>134</v>
       </c>
-      <c r="C75" s="7">
-        <v>30</v>
-      </c>
-      <c r="D75" s="20"/>
-    </row>
-    <row r="76" spans="1:4" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A76" s="7" t="s">
+      <c r="C78" s="7">
+        <v>15</v>
+      </c>
+      <c r="D78" s="22"/>
+    </row>
+    <row r="79" spans="1:4" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A79" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="B76" s="7" t="s">
+      <c r="B79" s="7" t="s">
         <v>107</v>
       </c>
-      <c r="C76" s="7">
-        <v>20</v>
-      </c>
-      <c r="D76" s="20"/>
-    </row>
-    <row r="77" spans="1:4" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A77" s="13" t="s">
+      <c r="C79" s="7">
+        <v>15</v>
+      </c>
+      <c r="D79" s="20"/>
+    </row>
+    <row r="80" spans="1:4" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A80" s="13" t="s">
         <v>56</v>
       </c>
-      <c r="B77" s="13" t="s">
+      <c r="B80" s="13" t="s">
         <v>135</v>
       </c>
-      <c r="C77" s="13">
+      <c r="C80" s="13">
         <v>10</v>
       </c>
-      <c r="D77" s="21"/>
-    </row>
-    <row r="78" spans="1:4" ht="17.25" customHeight="1" thickTop="1" x14ac:dyDescent="0.3"/>
+      <c r="D80" s="21"/>
+    </row>
+    <row r="81" ht="17.25" customHeight="1" thickTop="1" x14ac:dyDescent="0.3"/>
   </sheetData>
-  <autoFilter ref="I44:K44" xr:uid="{00000000-0009-0000-0000-000001000000}">
-    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="I45:K53">
-      <sortCondition descending="1" ref="K44"/>
+  <autoFilter ref="I43:K43" xr:uid="{0EF70075-620B-4549-A91C-D09223DDAD18}">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="I44:K48">
+      <sortCondition descending="1" ref="K43"/>
     </sortState>
   </autoFilter>
   <mergeCells count="8">
@@ -2761,10 +2778,10 @@
     <mergeCell ref="D23:D29"/>
     <mergeCell ref="D48:D56"/>
     <mergeCell ref="D40:D47"/>
-    <mergeCell ref="D74:D77"/>
+    <mergeCell ref="D76:D80"/>
     <mergeCell ref="D30:D39"/>
     <mergeCell ref="D57:D64"/>
-    <mergeCell ref="D65:D73"/>
+    <mergeCell ref="D65:D75"/>
   </mergeCells>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/raid_config.xlsx
+++ b/raid_config.xlsx
@@ -8,23 +8,23 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\new_bot\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2BC7FD5D-8701-4292-B2C8-F2FDC590130B}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1440483C-5172-4A90-9CC9-C2328DDA96DB}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="1725" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="1725" windowWidth="29040" windowHeight="17520" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="레이드설정" sheetId="1" r:id="rId1"/>
     <sheet name="DATA" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">DATA!$I$43:$K$43</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">DATA!$I$51:$K$51</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="260" uniqueCount="138">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="284" uniqueCount="151">
   <si>
     <t>활성화여부</t>
   </si>
@@ -104,18 +104,24 @@
     <t>O</t>
   </si>
   <si>
+    <t>월드보스</t>
+  </si>
+  <si>
+    <t>🌍</t>
+  </si>
+  <si>
+    <t>FF6F00</t>
+  </si>
+  <si>
+    <t>1,2,3,8,10,11,12,13</t>
+  </si>
+  <si>
     <t>이벤트</t>
   </si>
   <si>
     <t>🎉</t>
   </si>
   <si>
-    <t>FF6F00</t>
-  </si>
-  <si>
-    <t>1,2,3,8,10,11,12,13</t>
-  </si>
-  <si>
     <t>하급</t>
   </si>
   <si>
@@ -350,95 +356,138 @@
     <t>초기화꾸러미</t>
   </si>
   <si>
+    <t>정제된강화석_40</t>
+  </si>
+  <si>
+    <t>소환권상자_5</t>
+  </si>
+  <si>
+    <t>강화권_2</t>
+  </si>
+  <si>
+    <t>펫경문_300</t>
+  </si>
+  <si>
+    <t>마력결정체_60</t>
+  </si>
+  <si>
+    <t>월경크레딧</t>
+  </si>
+  <si>
+    <t>강화권_3</t>
+  </si>
+  <si>
+    <t>소환권상자_10</t>
+  </si>
+  <si>
+    <t>각성제</t>
+  </si>
+  <si>
+    <t>배진강화제</t>
+  </si>
+  <si>
+    <t>스탯상자_1</t>
+  </si>
+  <si>
+    <t>펫경문_500</t>
+  </si>
+  <si>
+    <t>쿵야알</t>
+  </si>
+  <si>
+    <t>칠흑의정수_100</t>
+  </si>
+  <si>
+    <t>강화권_4</t>
+  </si>
+  <si>
+    <t>스탯상자_2</t>
+  </si>
+  <si>
+    <t>펫경문_700</t>
+  </si>
+  <si>
+    <t>불지옥의불꽃_400</t>
+  </si>
+  <si>
+    <t>공룡알</t>
+  </si>
+  <si>
+    <t>펫경문_3000</t>
+  </si>
+  <si>
+    <t>강화권_5</t>
+  </si>
+  <si>
+    <t>스탯상자_3</t>
+  </si>
+  <si>
+    <t>지정초기화구슬</t>
+  </si>
+  <si>
+    <t>언딘알</t>
+  </si>
+  <si>
+    <t>카오닉스알</t>
+  </si>
+  <si>
+    <t>월드보스_1</t>
+  </si>
+  <si>
+    <t>월드보스_2</t>
+  </si>
+  <si>
+    <t>월드보스_3</t>
+  </si>
+  <si>
+    <t>월드보스_참가</t>
+  </si>
+  <si>
+    <t>펫경문_2000</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>칠흑의정수_100</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>펫경문_500</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>펫경문_300</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>정제된강화석_40</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
     <t>강화석_10</t>
-  </si>
-  <si>
-    <t>정제된강화석_40</t>
-  </si>
-  <si>
-    <t>소환권상자_5</t>
-  </si>
-  <si>
-    <t>강화권_2</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>마력결정체_60</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>1,2,3,4,5,6,7,8,9,10,11,12,13</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>펫경문_700</t>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>초기화구슬</t>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>완전초기화구슬</t>
-  </si>
-  <si>
-    <t>펫경문_300</t>
-  </si>
-  <si>
-    <t>마력결정체_60</t>
-  </si>
-  <si>
-    <t>월경크레딧</t>
-  </si>
-  <si>
-    <t>강화권_3</t>
-  </si>
-  <si>
-    <t>소환권상자_10</t>
-  </si>
-  <si>
-    <t>각성제</t>
-  </si>
-  <si>
-    <t>배진강화제</t>
-  </si>
-  <si>
-    <t>스탯상자_1</t>
-  </si>
-  <si>
-    <t>펫경문_500</t>
-  </si>
-  <si>
-    <t>쿵야알</t>
-  </si>
-  <si>
-    <t>칠흑의정수_100</t>
-  </si>
-  <si>
-    <t>강화권_4</t>
-  </si>
-  <si>
-    <t>스탯상자_2</t>
-  </si>
-  <si>
-    <t>펫경문_700</t>
-  </si>
-  <si>
-    <t>공룡알</t>
-  </si>
-  <si>
-    <t>강화권_5</t>
-  </si>
-  <si>
-    <t>스탯상자_3</t>
-  </si>
-  <si>
-    <t>지정초기화구슬</t>
-  </si>
-  <si>
-    <t>언딘알</t>
-  </si>
-  <si>
-    <t>카오닉스알</t>
-  </si>
-  <si>
-    <t>불지옥의불꽃_400</t>
-  </si>
-  <si>
-    <t>펫경문_3000</t>
-  </si>
-  <si>
-    <t>지옥2</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>지옥3</t>
+    <t>신수알</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -449,7 +498,7 @@
   <numFmts count="1">
     <numFmt numFmtId="176" formatCode="0.0%"/>
   </numFmts>
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -483,6 +532,15 @@
     <font>
       <b/>
       <sz val="28"/>
+      <color theme="1"/>
+      <name val="맑은 고딕"/>
+      <family val="3"/>
+      <charset val="129"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
       <color theme="1"/>
       <name val="맑은 고딕"/>
       <family val="3"/>
@@ -534,7 +592,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="15">
+  <borders count="14">
     <border>
       <left/>
       <right/>
@@ -670,19 +728,6 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right/>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left/>
       <right style="thin">
         <color auto="1"/>
@@ -699,21 +744,10 @@
       <left style="thin">
         <color auto="1"/>
       </left>
-      <right/>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thick">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
+      <right style="thick">
         <color auto="1"/>
       </right>
-      <top style="thin">
+      <top style="thick">
         <color auto="1"/>
       </top>
       <bottom style="thick">
@@ -731,7 +765,22 @@
       <top style="thick">
         <color auto="1"/>
       </top>
-      <bottom style="thick">
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thick">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
         <color auto="1"/>
       </bottom>
       <diagonal/>
@@ -740,7 +789,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
@@ -765,17 +814,19 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="176" fontId="4" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="4" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
-    <xf numFmtId="176" fontId="4" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="5" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="5" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1080,26 +1131,26 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:Y27"/>
+  <dimension ref="A1:Y28"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="2" width="10" style="18" customWidth="1"/>
-    <col min="3" max="3" width="6" style="18" customWidth="1"/>
-    <col min="4" max="5" width="10" style="18" customWidth="1"/>
-    <col min="6" max="7" width="12" style="18" customWidth="1"/>
-    <col min="8" max="8" width="14" style="18" customWidth="1"/>
-    <col min="9" max="9" width="12" style="18" customWidth="1"/>
-    <col min="10" max="11" width="10" style="18" customWidth="1"/>
-    <col min="12" max="12" width="12" style="18" customWidth="1"/>
-    <col min="13" max="13" width="10" style="18" customWidth="1"/>
-    <col min="14" max="15" width="12" style="18" customWidth="1"/>
-    <col min="16" max="16" width="10" style="18" customWidth="1"/>
-    <col min="17" max="18" width="12" style="18" customWidth="1"/>
-    <col min="19" max="19" width="14" style="18" customWidth="1"/>
-    <col min="20" max="20" width="12" style="18" customWidth="1"/>
-    <col min="21" max="22" width="35" style="18" customWidth="1"/>
-    <col min="23" max="23" width="12" style="18" customWidth="1"/>
-    <col min="24" max="25" width="35" style="18" customWidth="1"/>
+    <col min="1" max="2" width="10" style="14" customWidth="1"/>
+    <col min="3" max="3" width="6" style="14" customWidth="1"/>
+    <col min="4" max="5" width="10" style="14" customWidth="1"/>
+    <col min="6" max="7" width="12" style="14" customWidth="1"/>
+    <col min="8" max="8" width="14" style="14" customWidth="1"/>
+    <col min="9" max="9" width="12" style="14" customWidth="1"/>
+    <col min="10" max="11" width="10" style="14" customWidth="1"/>
+    <col min="12" max="12" width="12" style="14" customWidth="1"/>
+    <col min="13" max="13" width="10" style="14" customWidth="1"/>
+    <col min="14" max="15" width="12" style="14" customWidth="1"/>
+    <col min="16" max="16" width="10" style="14" customWidth="1"/>
+    <col min="17" max="18" width="12" style="14" customWidth="1"/>
+    <col min="19" max="19" width="14" style="14" customWidth="1"/>
+    <col min="20" max="20" width="12" style="14" customWidth="1"/>
+    <col min="21" max="22" width="35" style="14" customWidth="1"/>
+    <col min="23" max="23" width="12" style="14" customWidth="1"/>
+    <col min="24" max="25" width="35" style="14" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:25" x14ac:dyDescent="0.3">
@@ -1196,41 +1247,29 @@
         <v>0</v>
       </c>
       <c r="F2" s="5">
-        <v>90000</v>
+        <v>20000000</v>
       </c>
       <c r="G2" s="5">
-        <v>120000</v>
+        <v>23000000</v>
       </c>
       <c r="H2" s="5">
         <v>0</v>
       </c>
       <c r="I2" s="5">
-        <v>600</v>
+        <v>360</v>
       </c>
       <c r="J2" s="5" t="s">
         <v>25</v>
       </c>
       <c r="K2" s="5">
-        <v>300</v>
+        <v>0</v>
       </c>
       <c r="L2" s="5">
         <v>1</v>
       </c>
-      <c r="M2" s="5"/>
-      <c r="N2" s="5"/>
-      <c r="O2" s="5"/>
-      <c r="P2" s="5"/>
-      <c r="Q2" s="5"/>
-      <c r="R2" s="5"/>
-      <c r="S2" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="T2" s="5"/>
-      <c r="U2" s="5"/>
-      <c r="V2" s="5"/>
-      <c r="W2" s="5"/>
-      <c r="X2" s="5"/>
-      <c r="Y2" s="5"/>
+      <c r="S2" t="s">
+        <v>146</v>
+      </c>
     </row>
     <row r="3" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A3" s="5" t="s">
@@ -1243,16 +1282,16 @@
         <v>31</v>
       </c>
       <c r="D3" s="5" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="E3" s="5">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="F3" s="5">
-        <v>30000</v>
+        <v>90000</v>
       </c>
       <c r="G3" s="5">
-        <v>40000</v>
+        <v>120000</v>
       </c>
       <c r="H3" s="5">
         <v>0</v>
@@ -1260,21 +1299,23 @@
       <c r="I3" s="5">
         <v>600</v>
       </c>
-      <c r="J3" s="5"/>
+      <c r="J3" s="5" t="s">
+        <v>25</v>
+      </c>
       <c r="K3" s="5">
-        <v>100</v>
+        <v>300</v>
       </c>
       <c r="L3" s="5">
         <v>1</v>
       </c>
-      <c r="M3" s="5"/>
+      <c r="M3" s="15"/>
       <c r="N3" s="5"/>
       <c r="O3" s="5"/>
       <c r="P3" s="5"/>
       <c r="Q3" s="5"/>
       <c r="R3" s="5"/>
       <c r="S3" s="5" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="T3" s="5"/>
       <c r="U3" s="5"/>
@@ -1288,22 +1329,22 @@
         <v>25</v>
       </c>
       <c r="B4" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="C4" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="D4" s="5" t="s">
         <v>34</v>
       </c>
-      <c r="C4" s="5" t="s">
-        <v>35</v>
-      </c>
-      <c r="D4" s="5" t="s">
-        <v>36</v>
-      </c>
       <c r="E4" s="5">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="F4" s="5">
-        <v>80000</v>
+        <v>30000</v>
       </c>
       <c r="G4" s="5">
-        <v>100000</v>
+        <v>40000</v>
       </c>
       <c r="H4" s="5">
         <v>0</v>
@@ -1313,19 +1354,19 @@
       </c>
       <c r="J4" s="5"/>
       <c r="K4" s="5">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="L4" s="5">
         <v>1</v>
       </c>
-      <c r="M4" s="5"/>
+      <c r="M4" s="15"/>
       <c r="N4" s="5"/>
       <c r="O4" s="5"/>
       <c r="P4" s="5"/>
       <c r="Q4" s="5"/>
       <c r="R4" s="5"/>
       <c r="S4" s="5" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="T4" s="5"/>
       <c r="U4" s="5"/>
@@ -1339,22 +1380,22 @@
         <v>25</v>
       </c>
       <c r="B5" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="C5" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="D5" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="C5" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="D5" s="5" t="s">
-        <v>40</v>
-      </c>
       <c r="E5" s="5">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="F5" s="5">
-        <v>200000</v>
+        <v>80000</v>
       </c>
       <c r="G5" s="5">
-        <v>220000</v>
+        <v>100000</v>
       </c>
       <c r="H5" s="5">
         <v>0</v>
@@ -1364,19 +1405,19 @@
       </c>
       <c r="J5" s="5"/>
       <c r="K5" s="5">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="L5" s="5">
         <v>1</v>
       </c>
-      <c r="M5" s="5"/>
+      <c r="M5" s="15"/>
       <c r="N5" s="5"/>
       <c r="O5" s="5"/>
       <c r="P5" s="5"/>
       <c r="Q5" s="5"/>
       <c r="R5" s="5"/>
       <c r="S5" s="5" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="T5" s="5"/>
       <c r="U5" s="5"/>
@@ -1390,22 +1431,22 @@
         <v>25</v>
       </c>
       <c r="B6" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="C6" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="C6" s="5" t="s">
+      <c r="D6" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="D6" s="5" t="s">
-        <v>43</v>
-      </c>
       <c r="E6" s="5">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="F6" s="5">
-        <v>360000</v>
+        <v>200000</v>
       </c>
       <c r="G6" s="5">
-        <v>380000</v>
+        <v>220000</v>
       </c>
       <c r="H6" s="5">
         <v>0</v>
@@ -1415,19 +1456,19 @@
       </c>
       <c r="J6" s="5"/>
       <c r="K6" s="5">
-        <v>400</v>
+        <v>300</v>
       </c>
       <c r="L6" s="5">
         <v>1</v>
       </c>
-      <c r="M6" s="5"/>
+      <c r="M6" s="15"/>
       <c r="N6" s="5"/>
       <c r="O6" s="5"/>
       <c r="P6" s="5"/>
       <c r="Q6" s="5"/>
       <c r="R6" s="5"/>
       <c r="S6" s="5" t="s">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="T6" s="5"/>
       <c r="U6" s="5"/>
@@ -1441,22 +1482,22 @@
         <v>25</v>
       </c>
       <c r="B7" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="C7" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="D7" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="C7" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="D7" s="5" t="s">
-        <v>47</v>
-      </c>
       <c r="E7" s="5">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="F7" s="5">
-        <v>520000</v>
+        <v>360000</v>
       </c>
       <c r="G7" s="5">
-        <v>540000</v>
+        <v>380000</v>
       </c>
       <c r="H7" s="5">
         <v>0</v>
@@ -1466,19 +1507,19 @@
       </c>
       <c r="J7" s="5"/>
       <c r="K7" s="5">
-        <v>500</v>
+        <v>400</v>
       </c>
       <c r="L7" s="5">
-        <v>2</v>
-      </c>
-      <c r="M7" s="5"/>
+        <v>1</v>
+      </c>
+      <c r="M7" s="15"/>
       <c r="N7" s="5"/>
       <c r="O7" s="5"/>
       <c r="P7" s="5"/>
       <c r="Q7" s="5"/>
       <c r="R7" s="5"/>
       <c r="S7" s="5" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="T7" s="5"/>
       <c r="U7" s="5"/>
@@ -1492,22 +1533,22 @@
         <v>25</v>
       </c>
       <c r="B8" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="C8" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="D8" s="5" t="s">
         <v>49</v>
       </c>
-      <c r="C8" s="5" t="s">
-        <v>50</v>
-      </c>
-      <c r="D8" s="5" t="s">
-        <v>51</v>
-      </c>
       <c r="E8" s="5">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="F8" s="5">
-        <v>600000</v>
+        <v>520000</v>
       </c>
       <c r="G8" s="5">
-        <v>620000</v>
+        <v>540000</v>
       </c>
       <c r="H8" s="5">
         <v>0</v>
@@ -1517,33 +1558,23 @@
       </c>
       <c r="J8" s="5"/>
       <c r="K8" s="5">
-        <v>600</v>
+        <v>500</v>
       </c>
       <c r="L8" s="5">
         <v>2</v>
       </c>
-      <c r="M8" s="5">
-        <v>60000</v>
-      </c>
-      <c r="N8" s="5">
-        <v>60</v>
-      </c>
+      <c r="M8" s="15"/>
+      <c r="N8" s="5"/>
       <c r="O8" s="5"/>
       <c r="P8" s="5"/>
       <c r="Q8" s="5"/>
       <c r="R8" s="5"/>
       <c r="S8" s="5" t="s">
-        <v>52</v>
-      </c>
-      <c r="T8" s="5" t="s">
-        <v>53</v>
-      </c>
-      <c r="U8" s="5" t="s">
-        <v>54</v>
-      </c>
-      <c r="V8" s="5" t="s">
-        <v>55</v>
-      </c>
+        <v>50</v>
+      </c>
+      <c r="T8" s="5"/>
+      <c r="U8" s="5"/>
+      <c r="V8" s="5"/>
       <c r="W8" s="5"/>
       <c r="X8" s="5"/>
       <c r="Y8" s="5"/>
@@ -1553,16 +1584,16 @@
         <v>25</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="E9" s="5">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="F9" s="5">
         <v>600000</v>
@@ -1578,154 +1609,215 @@
       </c>
       <c r="J9" s="5"/>
       <c r="K9" s="5">
-        <v>700</v>
+        <v>600</v>
       </c>
       <c r="L9" s="5">
         <v>2</v>
       </c>
-      <c r="M9" s="5">
-        <v>70000</v>
+      <c r="M9" s="15">
+        <v>60000</v>
       </c>
       <c r="N9" s="5">
         <v>60</v>
       </c>
       <c r="O9" s="5"/>
-      <c r="P9" s="5">
+      <c r="P9" s="5"/>
+      <c r="Q9" s="5"/>
+      <c r="R9" s="5"/>
+      <c r="S9" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="T9" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="U9" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="V9" s="5" t="s">
+        <v>57</v>
+      </c>
+      <c r="W9" s="5"/>
+      <c r="X9" s="5"/>
+      <c r="Y9" s="5"/>
+    </row>
+    <row r="10" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A10" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="B10" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="C10" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="D10" s="5" t="s">
+        <v>60</v>
+      </c>
+      <c r="E10" s="5">
+        <v>35</v>
+      </c>
+      <c r="F10" s="5">
+        <v>600000</v>
+      </c>
+      <c r="G10" s="5">
+        <v>620000</v>
+      </c>
+      <c r="H10" s="5">
+        <v>0</v>
+      </c>
+      <c r="I10" s="5">
+        <v>600</v>
+      </c>
+      <c r="J10" s="5"/>
+      <c r="K10" s="5">
+        <v>700</v>
+      </c>
+      <c r="L10" s="5">
+        <v>2</v>
+      </c>
+      <c r="M10" s="15">
+        <v>70000</v>
+      </c>
+      <c r="N10" s="5">
+        <v>60</v>
+      </c>
+      <c r="O10" s="5"/>
+      <c r="P10" s="5">
         <v>350000</v>
       </c>
-      <c r="Q9" s="5">
+      <c r="Q10" s="5">
         <v>300</v>
       </c>
-      <c r="R9" s="5" t="s">
-        <v>59</v>
-      </c>
-      <c r="S9" s="5" t="s">
-        <v>60</v>
-      </c>
-      <c r="T9" s="5" t="s">
+      <c r="R10" s="5" t="s">
         <v>61</v>
       </c>
-      <c r="U9" s="5" t="s">
+      <c r="S10" s="5" t="s">
         <v>62</v>
       </c>
-      <c r="V9" s="5" t="s">
+      <c r="T10" s="5" t="s">
         <v>63</v>
       </c>
-      <c r="W9" s="5" t="s">
-        <v>53</v>
-      </c>
-      <c r="X9" s="5" t="s">
+      <c r="U10" s="5" t="s">
         <v>64</v>
       </c>
-      <c r="Y9" s="5" t="s">
+      <c r="V10" s="5" t="s">
         <v>65</v>
       </c>
-    </row>
-    <row r="12" spans="1:25" x14ac:dyDescent="0.3">
-      <c r="S12" s="5"/>
-    </row>
-    <row r="15" spans="1:25" x14ac:dyDescent="0.3">
-      <c r="P15">
-        <v>1</v>
-      </c>
-      <c r="R15" t="s">
+      <c r="W10" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="X10" s="5" t="s">
         <v>66</v>
       </c>
+      <c r="Y10" s="5" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="13" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="S13" s="5"/>
     </row>
     <row r="16" spans="1:25" x14ac:dyDescent="0.3">
       <c r="P16">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R16" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
     <row r="17" spans="16:18" x14ac:dyDescent="0.3">
       <c r="P17">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="R17" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
     </row>
     <row r="18" spans="16:18" x14ac:dyDescent="0.3">
       <c r="P18">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="R18" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
     </row>
     <row r="19" spans="16:18" x14ac:dyDescent="0.3">
       <c r="P19">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="R19" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
     </row>
     <row r="20" spans="16:18" x14ac:dyDescent="0.3">
       <c r="P20">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="R20" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="21" spans="16:18" x14ac:dyDescent="0.3">
       <c r="P21">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="R21" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
     </row>
     <row r="22" spans="16:18" x14ac:dyDescent="0.3">
       <c r="P22">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="R22" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
     </row>
     <row r="23" spans="16:18" x14ac:dyDescent="0.3">
       <c r="P23">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="R23" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
     </row>
     <row r="24" spans="16:18" x14ac:dyDescent="0.3">
       <c r="P24">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="R24" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
     </row>
     <row r="25" spans="16:18" x14ac:dyDescent="0.3">
       <c r="P25">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="R25" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
     </row>
     <row r="26" spans="16:18" x14ac:dyDescent="0.3">
       <c r="P26">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="R26" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="27" spans="16:18" x14ac:dyDescent="0.3">
       <c r="P27">
+        <v>12</v>
+      </c>
+      <c r="R27" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="28" spans="16:18" x14ac:dyDescent="0.3">
+      <c r="P28">
         <v>13</v>
       </c>
-      <c r="R27" t="s">
-        <v>78</v>
+      <c r="R28" t="s">
+        <v>80</v>
       </c>
     </row>
   </sheetData>
@@ -1737,24 +1829,24 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:K81"/>
+  <dimension ref="A1:K102"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="12" style="18" customWidth="1"/>
-    <col min="2" max="2" width="22" style="18" customWidth="1"/>
-    <col min="3" max="3" width="10" style="18" customWidth="1"/>
-    <col min="4" max="4" width="40" style="18" customWidth="1"/>
+    <col min="1" max="1" width="12" style="14" customWidth="1"/>
+    <col min="2" max="2" width="22" style="14" customWidth="1"/>
+    <col min="3" max="3" width="10" style="14" customWidth="1"/>
+    <col min="4" max="4" width="40" style="14" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1" s="6" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="B1" s="6" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="C1" s="6" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.3">
@@ -1762,10 +1854,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="7" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="C2" s="7" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.3">
@@ -1773,10 +1865,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="7" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="C3" s="7" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.3">
@@ -1784,10 +1876,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="7" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="C4" s="7" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.3">
@@ -1795,10 +1887,10 @@
         <v>4</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="C5" s="7" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.3">
@@ -1806,10 +1898,10 @@
         <v>5</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="C6" s="7" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.3">
@@ -1817,10 +1909,10 @@
         <v>6</v>
       </c>
       <c r="B7" s="7" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="C7" s="7" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.3">
@@ -1828,10 +1920,10 @@
         <v>7</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="C8" s="7" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.3">
@@ -1839,10 +1931,10 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="C9" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.3">
@@ -1850,10 +1942,10 @@
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="C10" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.3">
@@ -1861,10 +1953,10 @@
         <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="C11" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.3">
@@ -1872,10 +1964,10 @@
         <v>11</v>
       </c>
       <c r="B12" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="C12" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.3">
@@ -1883,10 +1975,10 @@
         <v>12</v>
       </c>
       <c r="B13" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="C13" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.3">
@@ -1894,671 +1986,680 @@
         <v>13</v>
       </c>
       <c r="B14" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="C14" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
     </row>
     <row r="16" spans="1:4" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A16" s="8" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="B16" s="8" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="C16" s="8" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="D16" s="8" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="17" spans="1:4" ht="17.25" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" s="14" customFormat="1" ht="17.25" thickTop="1" x14ac:dyDescent="0.3">
       <c r="A17" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="B17" s="10" t="s">
-        <v>102</v>
+        <v>135</v>
+      </c>
+      <c r="B17" s="7" t="s">
+        <v>140</v>
       </c>
       <c r="C17" s="10">
+        <v>50</v>
+      </c>
+      <c r="D17" s="19">
+        <f>SUM(C17:C18)/100</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" s="14" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A18" s="11" t="s">
+        <v>135</v>
+      </c>
+      <c r="B18" s="7" t="s">
+        <v>147</v>
+      </c>
+      <c r="C18" s="7">
+        <v>50</v>
+      </c>
+      <c r="D18" s="20"/>
+    </row>
+    <row r="19" spans="1:4" s="14" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A19" s="11" t="s">
+        <v>136</v>
+      </c>
+      <c r="B19" s="7" t="s">
+        <v>145</v>
+      </c>
+      <c r="C19" s="7">
+        <v>70</v>
+      </c>
+      <c r="D19" s="20">
+        <f>SUM(C19:C20)/100</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" s="14" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A20" s="11" t="s">
+        <v>136</v>
+      </c>
+      <c r="B20" s="7" t="s">
+        <v>147</v>
+      </c>
+      <c r="C20" s="7">
+        <v>30</v>
+      </c>
+      <c r="D20" s="20"/>
+    </row>
+    <row r="21" spans="1:4" s="14" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A21" s="11" t="s">
+        <v>137</v>
+      </c>
+      <c r="B21" s="7" t="s">
+        <v>143</v>
+      </c>
+      <c r="C21" s="7">
+        <v>70</v>
+      </c>
+      <c r="D21" s="20">
+        <f>SUM(C21:C22)/100</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" s="14" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A22" s="11" t="s">
+        <v>137</v>
+      </c>
+      <c r="B22" s="7" t="s">
+        <v>141</v>
+      </c>
+      <c r="C22" s="7">
+        <v>30</v>
+      </c>
+      <c r="D22" s="20"/>
+    </row>
+    <row r="23" spans="1:4" s="14" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A23" s="11" t="s">
+        <v>138</v>
+      </c>
+      <c r="B23" s="7" t="s">
+        <v>148</v>
+      </c>
+      <c r="C23" s="7">
+        <v>70</v>
+      </c>
+      <c r="D23" s="20">
+        <f>SUM(C23:C24)/100</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" s="14" customFormat="1" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A24" s="11" t="s">
+        <v>138</v>
+      </c>
+      <c r="B24" s="7" t="s">
+        <v>142</v>
+      </c>
+      <c r="C24" s="7">
+        <v>30</v>
+      </c>
+      <c r="D24" s="20"/>
+    </row>
+    <row r="25" spans="1:4" ht="17.25" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A25" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="B25" s="10" t="s">
+        <v>104</v>
+      </c>
+      <c r="C25" s="10">
         <v>60</v>
       </c>
-      <c r="D17" s="19">
-        <f>SUM(C17:C22)/100</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A18" s="11" t="s">
-        <v>26</v>
-      </c>
-      <c r="B18" s="7" t="s">
-        <v>103</v>
-      </c>
-      <c r="C18" s="7">
-        <v>20</v>
-      </c>
-      <c r="D18" s="20"/>
-    </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A19" s="11" t="s">
-        <v>26</v>
-      </c>
-      <c r="B19" s="7" t="s">
-        <v>104</v>
-      </c>
-      <c r="C19" s="7">
-        <v>10</v>
-      </c>
-      <c r="D19" s="20"/>
-    </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A20" s="11" t="s">
-        <v>26</v>
-      </c>
-      <c r="B20" s="7" t="s">
-        <v>105</v>
-      </c>
-      <c r="C20" s="7">
-        <v>5</v>
-      </c>
-      <c r="D20" s="20"/>
-    </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A21" s="11" t="s">
-        <v>26</v>
-      </c>
-      <c r="B21" s="7" t="s">
-        <v>106</v>
-      </c>
-      <c r="C21" s="7">
-        <v>3</v>
-      </c>
-      <c r="D21" s="20"/>
-    </row>
-    <row r="22" spans="1:4" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A22" s="12" t="s">
-        <v>26</v>
-      </c>
-      <c r="B22" s="13" t="s">
-        <v>107</v>
-      </c>
-      <c r="C22" s="13">
-        <v>2</v>
-      </c>
-      <c r="D22" s="21"/>
-    </row>
-    <row r="23" spans="1:4" ht="17.25" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="9" t="s">
-        <v>30</v>
-      </c>
-      <c r="B23" s="10" t="s">
-        <v>108</v>
-      </c>
-      <c r="C23" s="10">
-        <v>60</v>
-      </c>
-      <c r="D23" s="19">
-        <f>SUM(C23:C29)/100</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="24" spans="1:4" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="11" t="s">
-        <v>30</v>
-      </c>
-      <c r="B24" s="7" t="s">
-        <v>109</v>
-      </c>
-      <c r="C24" s="7">
-        <v>20</v>
-      </c>
-      <c r="D24" s="20"/>
-    </row>
-    <row r="25" spans="1:4" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A25" s="11" t="s">
-        <v>30</v>
-      </c>
-      <c r="B25" s="7" t="s">
-        <v>110</v>
-      </c>
-      <c r="C25" s="7">
-        <v>5</v>
-      </c>
-      <c r="D25" s="20"/>
-    </row>
-    <row r="26" spans="1:4" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="D25" s="16">
+        <f>SUM(C25:C30)/100</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A26" s="11" t="s">
         <v>30</v>
       </c>
       <c r="B26" s="7" t="s">
-        <v>111</v>
+        <v>105</v>
       </c>
       <c r="C26" s="7">
-        <v>5</v>
-      </c>
-      <c r="D26" s="20"/>
-    </row>
-    <row r="27" spans="1:4" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+        <v>20</v>
+      </c>
+      <c r="D26" s="17"/>
+    </row>
+    <row r="27" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A27" s="11" t="s">
         <v>30</v>
       </c>
       <c r="B27" s="7" t="s">
-        <v>112</v>
+        <v>106</v>
       </c>
       <c r="C27" s="7">
-        <v>5</v>
-      </c>
-      <c r="D27" s="20"/>
-    </row>
-    <row r="28" spans="1:4" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+        <v>10</v>
+      </c>
+      <c r="D27" s="17"/>
+    </row>
+    <row r="28" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A28" s="11" t="s">
         <v>30</v>
       </c>
       <c r="B28" s="7" t="s">
-        <v>113</v>
+        <v>107</v>
       </c>
       <c r="C28" s="7">
+        <v>5</v>
+      </c>
+      <c r="D28" s="17"/>
+    </row>
+    <row r="29" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A29" s="11" t="s">
+        <v>30</v>
+      </c>
+      <c r="B29" s="7" t="s">
+        <v>139</v>
+      </c>
+      <c r="C29" s="7">
         <v>3</v>
       </c>
-      <c r="D28" s="20"/>
-    </row>
-    <row r="29" spans="1:4" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A29" s="12" t="s">
+      <c r="D29" s="17"/>
+    </row>
+    <row r="30" spans="1:4" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A30" s="12" t="s">
         <v>30</v>
       </c>
-      <c r="B29" s="13" t="s">
-        <v>114</v>
-      </c>
-      <c r="C29" s="13">
+      <c r="B30" s="13" t="s">
+        <v>109</v>
+      </c>
+      <c r="C30" s="13">
         <v>2</v>
       </c>
-      <c r="D29" s="21"/>
-    </row>
-    <row r="30" spans="1:4" ht="17.25" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
-      <c r="A30" s="9" t="s">
-        <v>34</v>
-      </c>
-      <c r="B30" s="10" t="s">
-        <v>109</v>
-      </c>
-      <c r="C30" s="10">
+      <c r="D30" s="18"/>
+    </row>
+    <row r="31" spans="1:4" ht="17.25" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
+      <c r="A31" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="B31" s="10" t="s">
+        <v>144</v>
+      </c>
+      <c r="C31" s="10">
         <v>60</v>
       </c>
-      <c r="D30" s="19">
-        <f>SUM(C30:C39)/100</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="31" spans="1:4" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A31" s="11" t="s">
-        <v>34</v>
-      </c>
-      <c r="B31" s="7" t="s">
-        <v>115</v>
-      </c>
-      <c r="C31" s="7">
-        <v>10</v>
-      </c>
-      <c r="D31" s="20"/>
+      <c r="D31" s="16">
+        <f>SUM(C31:C37)/100</f>
+        <v>1</v>
+      </c>
     </row>
     <row r="32" spans="1:4" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32" s="11" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="B32" s="7" t="s">
-        <v>116</v>
+        <v>143</v>
       </c>
       <c r="C32" s="7">
-        <v>10</v>
-      </c>
-      <c r="D32" s="20"/>
-    </row>
-    <row r="33" spans="1:11" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+        <v>20</v>
+      </c>
+      <c r="D32" s="17"/>
+    </row>
+    <row r="33" spans="1:4" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A33" s="11" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="B33" s="7" t="s">
-        <v>117</v>
+        <v>111</v>
       </c>
       <c r="C33" s="7">
-        <v>8</v>
-      </c>
-      <c r="D33" s="20"/>
-    </row>
-    <row r="34" spans="1:11" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+        <v>5</v>
+      </c>
+      <c r="D33" s="17"/>
+    </row>
+    <row r="34" spans="1:4" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A34" s="11" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="B34" s="7" t="s">
-        <v>118</v>
+        <v>112</v>
       </c>
       <c r="C34" s="7">
         <v>5</v>
       </c>
-      <c r="D34" s="20"/>
-    </row>
-    <row r="35" spans="1:11" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="D34" s="17"/>
+    </row>
+    <row r="35" spans="1:4" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A35" s="11" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="B35" s="7" t="s">
+        <v>148</v>
+      </c>
+      <c r="C35" s="7">
+        <v>5</v>
+      </c>
+      <c r="D35" s="17"/>
+    </row>
+    <row r="36" spans="1:4" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A36" s="11" t="s">
+        <v>32</v>
+      </c>
+      <c r="B36" s="7" t="s">
+        <v>149</v>
+      </c>
+      <c r="C36" s="7">
+        <v>3</v>
+      </c>
+      <c r="D36" s="17"/>
+    </row>
+    <row r="37" spans="1:4" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A37" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="B37" s="13" t="s">
+        <v>113</v>
+      </c>
+      <c r="C37" s="13">
+        <v>2</v>
+      </c>
+      <c r="D37" s="18"/>
+    </row>
+    <row r="38" spans="1:4" ht="17.25" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
+      <c r="A38" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="B38" s="10" t="s">
+        <v>110</v>
+      </c>
+      <c r="C38" s="10">
+        <v>60</v>
+      </c>
+      <c r="D38" s="16">
+        <f>SUM(C38:C47)/100</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A39" s="11" t="s">
+        <v>36</v>
+      </c>
+      <c r="B39" s="7" t="s">
+        <v>145</v>
+      </c>
+      <c r="C39" s="7">
+        <v>10</v>
+      </c>
+      <c r="D39" s="17"/>
+    </row>
+    <row r="40" spans="1:4" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A40" s="11" t="s">
+        <v>36</v>
+      </c>
+      <c r="B40" s="7" t="s">
+        <v>115</v>
+      </c>
+      <c r="C40" s="7">
+        <v>10</v>
+      </c>
+      <c r="D40" s="17"/>
+    </row>
+    <row r="41" spans="1:4" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A41" s="11" t="s">
+        <v>36</v>
+      </c>
+      <c r="B41" s="7" t="s">
+        <v>116</v>
+      </c>
+      <c r="C41" s="7">
+        <v>8</v>
+      </c>
+      <c r="D41" s="17"/>
+    </row>
+    <row r="42" spans="1:4" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A42" s="11" t="s">
+        <v>36</v>
+      </c>
+      <c r="B42" s="7" t="s">
+        <v>117</v>
+      </c>
+      <c r="C42" s="7">
+        <v>5</v>
+      </c>
+      <c r="D42" s="17"/>
+    </row>
+    <row r="43" spans="1:4" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A43" s="11" t="s">
+        <v>36</v>
+      </c>
+      <c r="B43" s="7" t="s">
+        <v>118</v>
+      </c>
+      <c r="C43" s="7">
+        <v>2</v>
+      </c>
+      <c r="D43" s="17"/>
+    </row>
+    <row r="44" spans="1:4" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A44" s="11" t="s">
+        <v>36</v>
+      </c>
+      <c r="B44" s="7" t="s">
         <v>119</v>
       </c>
-      <c r="C35" s="7">
+      <c r="C44" s="7">
         <v>2</v>
       </c>
-      <c r="D35" s="20"/>
-    </row>
-    <row r="36" spans="1:11" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A36" s="11" t="s">
-        <v>34</v>
-      </c>
-      <c r="B36" s="7" t="s">
+      <c r="D44" s="17"/>
+    </row>
+    <row r="45" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A45" s="11" t="s">
+        <v>36</v>
+      </c>
+      <c r="B45" s="7" t="s">
         <v>120</v>
       </c>
-      <c r="C36" s="7">
-        <v>2</v>
-      </c>
-      <c r="D36" s="20"/>
-    </row>
-    <row r="37" spans="1:11" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A37" s="11" t="s">
-        <v>34</v>
-      </c>
-      <c r="B37" s="7" t="s">
+      <c r="C45" s="7">
+        <v>1</v>
+      </c>
+      <c r="D45" s="17"/>
+    </row>
+    <row r="46" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A46" s="11" t="s">
+        <v>36</v>
+      </c>
+      <c r="B46" s="7" t="s">
         <v>121</v>
       </c>
-      <c r="C37" s="7">
-        <v>1</v>
-      </c>
-      <c r="D37" s="20"/>
-    </row>
-    <row r="38" spans="1:11" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A38" s="11" t="s">
-        <v>34</v>
-      </c>
-      <c r="B38" s="7" t="s">
+      <c r="C46" s="7">
+        <v>1</v>
+      </c>
+      <c r="D46" s="17"/>
+    </row>
+    <row r="47" spans="1:4" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A47" s="12" t="s">
+        <v>36</v>
+      </c>
+      <c r="B47" s="13" t="s">
         <v>122</v>
       </c>
-      <c r="C38" s="7">
-        <v>1</v>
-      </c>
-      <c r="D38" s="20"/>
-    </row>
-    <row r="39" spans="1:11" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A39" s="12" t="s">
-        <v>34</v>
-      </c>
-      <c r="B39" s="13" t="s">
+      <c r="C47" s="13">
+        <v>1</v>
+      </c>
+      <c r="D47" s="18"/>
+    </row>
+    <row r="48" spans="1:4" ht="17.25" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
+      <c r="A48" s="9" t="s">
+        <v>40</v>
+      </c>
+      <c r="B48" s="10" t="s">
+        <v>114</v>
+      </c>
+      <c r="C48" s="10">
+        <v>60</v>
+      </c>
+      <c r="D48" s="16">
+        <f>SUM(C48:C55)/100</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="49" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A49" s="11" t="s">
+        <v>40</v>
+      </c>
+      <c r="B49" s="7" t="s">
         <v>123</v>
-      </c>
-      <c r="C39" s="13">
-        <v>1</v>
-      </c>
-      <c r="D39" s="21"/>
-    </row>
-    <row r="40" spans="1:11" ht="17.25" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
-      <c r="A40" s="9" t="s">
-        <v>38</v>
-      </c>
-      <c r="B40" s="10" t="s">
-        <v>115</v>
-      </c>
-      <c r="C40" s="10">
-        <v>60</v>
-      </c>
-      <c r="D40" s="19">
-        <f>SUM(C40:C47)/100</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="41" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A41" s="11" t="s">
-        <v>38</v>
-      </c>
-      <c r="B41" s="7" t="s">
-        <v>124</v>
-      </c>
-      <c r="C41" s="7">
-        <v>20</v>
-      </c>
-      <c r="D41" s="20"/>
-    </row>
-    <row r="42" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A42" s="11" t="s">
-        <v>38</v>
-      </c>
-      <c r="B42" s="7" t="s">
-        <v>125</v>
-      </c>
-      <c r="C42" s="7">
-        <v>9</v>
-      </c>
-      <c r="D42" s="20"/>
-    </row>
-    <row r="43" spans="1:11" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A43" s="11" t="s">
-        <v>38</v>
-      </c>
-      <c r="B43" s="7" t="s">
-        <v>119</v>
-      </c>
-      <c r="C43" s="7">
-        <v>4</v>
-      </c>
-      <c r="D43" s="20"/>
-    </row>
-    <row r="44" spans="1:11" ht="17.25" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
-      <c r="A44" s="11" t="s">
-        <v>38</v>
-      </c>
-      <c r="B44" s="7" t="s">
-        <v>120</v>
-      </c>
-      <c r="C44" s="7">
-        <v>4</v>
-      </c>
-      <c r="D44" s="20"/>
-      <c r="I44" s="10" t="s">
-        <v>137</v>
-      </c>
-      <c r="J44" s="7" t="s">
-        <v>119</v>
-      </c>
-      <c r="K44" s="7">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="45" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A45" s="11" t="s">
-        <v>38</v>
-      </c>
-      <c r="B45" s="7" t="s">
-        <v>126</v>
-      </c>
-      <c r="C45" s="7">
-        <v>1</v>
-      </c>
-      <c r="D45" s="20"/>
-      <c r="I45" s="7" t="s">
-        <v>137</v>
-      </c>
-      <c r="J45" s="7" t="s">
-        <v>120</v>
-      </c>
-      <c r="K45" s="7">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="46" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A46" s="11" t="s">
-        <v>38</v>
-      </c>
-      <c r="B46" s="7" t="s">
-        <v>127</v>
-      </c>
-      <c r="C46" s="7">
-        <v>1</v>
-      </c>
-      <c r="D46" s="20"/>
-      <c r="I46" s="7" t="s">
-        <v>56</v>
-      </c>
-      <c r="J46" s="7" t="s">
-        <v>134</v>
-      </c>
-      <c r="K46" s="7">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="47" spans="1:11" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A47" s="12" t="s">
-        <v>38</v>
-      </c>
-      <c r="B47" s="13" t="s">
-        <v>128</v>
-      </c>
-      <c r="C47" s="13">
-        <v>1</v>
-      </c>
-      <c r="D47" s="21"/>
-      <c r="I47" s="7" t="s">
-        <v>56</v>
-      </c>
-      <c r="J47" s="7" t="s">
-        <v>107</v>
-      </c>
-      <c r="K47" s="7">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="48" spans="1:11" ht="17.25" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A48" s="9" t="s">
-        <v>41</v>
-      </c>
-      <c r="B48" s="10" t="s">
-        <v>124</v>
-      </c>
-      <c r="C48" s="10">
-        <v>51</v>
-      </c>
-      <c r="D48" s="19">
-        <f>SUM(C48:C56)/100</f>
-        <v>1</v>
-      </c>
-      <c r="I48" s="13" t="s">
-        <v>56</v>
-      </c>
-      <c r="J48" s="13" t="s">
-        <v>135</v>
-      </c>
-      <c r="K48" s="13">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="49" spans="1:11" ht="17.25" thickTop="1" x14ac:dyDescent="0.3">
-      <c r="A49" s="11" t="s">
-        <v>41</v>
-      </c>
-      <c r="B49" s="7" t="s">
-        <v>102</v>
       </c>
       <c r="C49" s="7">
         <v>20</v>
       </c>
-      <c r="D49" s="20"/>
-      <c r="I49" s="11"/>
-      <c r="J49" s="7"/>
-      <c r="K49" s="7"/>
+      <c r="D49" s="17"/>
     </row>
     <row r="50" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A50" s="11" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B50" s="7" t="s">
+        <v>124</v>
+      </c>
+      <c r="C50" s="7">
+        <v>9</v>
+      </c>
+      <c r="D50" s="17"/>
+    </row>
+    <row r="51" spans="1:11" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A51" s="11" t="s">
+        <v>40</v>
+      </c>
+      <c r="B51" s="7" t="s">
+        <v>118</v>
+      </c>
+      <c r="C51" s="7">
+        <v>4</v>
+      </c>
+      <c r="D51" s="17"/>
+    </row>
+    <row r="52" spans="1:11" ht="17.25" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
+      <c r="A52" s="11" t="s">
+        <v>40</v>
+      </c>
+      <c r="B52" s="7" t="s">
+        <v>119</v>
+      </c>
+      <c r="C52" s="7">
+        <v>4</v>
+      </c>
+      <c r="D52" s="17"/>
+      <c r="I52" s="10" t="s">
+        <v>58</v>
+      </c>
+      <c r="J52" s="7" t="s">
+        <v>118</v>
+      </c>
+      <c r="K52" s="7">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="53" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A53" s="11" t="s">
+        <v>40</v>
+      </c>
+      <c r="B53" s="7" t="s">
+        <v>125</v>
+      </c>
+      <c r="C53" s="7">
+        <v>1</v>
+      </c>
+      <c r="D53" s="17"/>
+      <c r="I53" s="7" t="s">
+        <v>58</v>
+      </c>
+      <c r="J53" s="7" t="s">
+        <v>119</v>
+      </c>
+      <c r="K53" s="7">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="54" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A54" s="11" t="s">
+        <v>40</v>
+      </c>
+      <c r="B54" s="7" t="s">
+        <v>126</v>
+      </c>
+      <c r="C54" s="7">
+        <v>1</v>
+      </c>
+      <c r="D54" s="17"/>
+      <c r="I54" s="7" t="s">
+        <v>58</v>
+      </c>
+      <c r="J54" s="7" t="s">
+        <v>127</v>
+      </c>
+      <c r="K54" s="7">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="55" spans="1:11" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A55" s="12" t="s">
+        <v>40</v>
+      </c>
+      <c r="B55" s="13" t="s">
+        <v>128</v>
+      </c>
+      <c r="C55" s="13">
+        <v>1</v>
+      </c>
+      <c r="D55" s="18"/>
+      <c r="I55" s="7" t="s">
+        <v>58</v>
+      </c>
+      <c r="J55" s="7" t="s">
+        <v>109</v>
+      </c>
+      <c r="K55" s="7">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="56" spans="1:11" ht="17.25" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A56" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="B56" s="10" t="s">
+        <v>140</v>
+      </c>
+      <c r="C56" s="10">
+        <v>51</v>
+      </c>
+      <c r="D56" s="16">
+        <f>SUM(C56:C64)/100</f>
+        <v>1</v>
+      </c>
+      <c r="I56" s="13" t="s">
+        <v>58</v>
+      </c>
+      <c r="J56" s="13" t="s">
         <v>129</v>
       </c>
-      <c r="C50" s="7">
+      <c r="K56" s="13">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="57" spans="1:11" ht="17.25" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
+      <c r="A57" s="11" t="s">
+        <v>43</v>
+      </c>
+      <c r="B57" s="7" t="s">
+        <v>104</v>
+      </c>
+      <c r="C57" s="7">
+        <v>20</v>
+      </c>
+      <c r="D57" s="17"/>
+      <c r="I57" s="11"/>
+      <c r="J57" s="7"/>
+      <c r="K57" s="7"/>
+    </row>
+    <row r="58" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A58" s="11" t="s">
+        <v>43</v>
+      </c>
+      <c r="B58" s="7" t="s">
+        <v>130</v>
+      </c>
+      <c r="C58" s="7">
         <v>8</v>
       </c>
-      <c r="D50" s="20"/>
-      <c r="I50" s="11"/>
-      <c r="J50" s="7"/>
-      <c r="K50" s="7"/>
-    </row>
-    <row r="51" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A51" s="11" t="s">
-        <v>41</v>
-      </c>
-      <c r="B51" s="7" t="s">
+      <c r="D58" s="17"/>
+      <c r="I58" s="11"/>
+      <c r="J58" s="7"/>
+      <c r="K58" s="7"/>
+    </row>
+    <row r="59" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A59" s="11" t="s">
+        <v>43</v>
+      </c>
+      <c r="B59" s="7" t="s">
+        <v>118</v>
+      </c>
+      <c r="C59" s="7">
+        <v>8</v>
+      </c>
+      <c r="D59" s="17"/>
+      <c r="I59" s="11"/>
+      <c r="J59" s="7"/>
+      <c r="K59" s="7"/>
+    </row>
+    <row r="60" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A60" s="11" t="s">
+        <v>43</v>
+      </c>
+      <c r="B60" s="7" t="s">
         <v>119</v>
       </c>
-      <c r="C51" s="7">
+      <c r="C60" s="7">
         <v>8</v>
       </c>
-      <c r="D51" s="20"/>
-      <c r="I51" s="11"/>
-      <c r="J51" s="7"/>
-      <c r="K51" s="7"/>
-    </row>
-    <row r="52" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A52" s="11" t="s">
-        <v>41</v>
-      </c>
-      <c r="B52" s="7" t="s">
-        <v>120</v>
-      </c>
-      <c r="C52" s="7">
-        <v>8</v>
-      </c>
-      <c r="D52" s="20"/>
-      <c r="I52" s="11"/>
-      <c r="J52" s="7"/>
-      <c r="K52" s="7"/>
-    </row>
-    <row r="53" spans="1:11" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A53" s="11" t="s">
-        <v>41</v>
-      </c>
-      <c r="B53" s="7" t="s">
-        <v>105</v>
-      </c>
-      <c r="C53" s="7">
-        <v>2</v>
-      </c>
-      <c r="D53" s="20"/>
-      <c r="I53" s="12"/>
-      <c r="J53" s="13"/>
-      <c r="K53" s="13"/>
-    </row>
-    <row r="54" spans="1:11" ht="17.25" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
-      <c r="A54" s="11" t="s">
-        <v>41</v>
-      </c>
-      <c r="B54" s="7" t="s">
-        <v>130</v>
-      </c>
-      <c r="C54" s="7">
-        <v>1</v>
-      </c>
-      <c r="D54" s="20"/>
-    </row>
-    <row r="55" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A55" s="11" t="s">
-        <v>41</v>
-      </c>
-      <c r="B55" s="7" t="s">
-        <v>131</v>
-      </c>
-      <c r="C55" s="7">
-        <v>1</v>
-      </c>
-      <c r="D55" s="20"/>
-    </row>
-    <row r="56" spans="1:11" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A56" s="12" t="s">
-        <v>41</v>
-      </c>
-      <c r="B56" s="13" t="s">
-        <v>132</v>
-      </c>
-      <c r="C56" s="13">
-        <v>1</v>
-      </c>
-      <c r="D56" s="21"/>
-    </row>
-    <row r="57" spans="1:11" ht="17.25" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
-      <c r="A57" s="10" t="s">
-        <v>45</v>
-      </c>
-      <c r="B57" s="10" t="s">
-        <v>102</v>
-      </c>
-      <c r="C57" s="10">
-        <v>50</v>
-      </c>
-      <c r="D57" s="19">
-        <f>SUM(C57:C64)/100</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="58" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A58" s="7" t="s">
-        <v>45</v>
-      </c>
-      <c r="B58" s="7" t="s">
-        <v>119</v>
-      </c>
-      <c r="C58" s="7">
-        <v>16</v>
-      </c>
-      <c r="D58" s="20"/>
-    </row>
-    <row r="59" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A59" s="7" t="s">
-        <v>45</v>
-      </c>
-      <c r="B59" s="7" t="s">
-        <v>120</v>
-      </c>
-      <c r="C59" s="7">
-        <v>16</v>
-      </c>
-      <c r="D59" s="20"/>
-    </row>
-    <row r="60" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A60" s="7" t="s">
-        <v>45</v>
-      </c>
-      <c r="B60" s="7" t="s">
-        <v>104</v>
-      </c>
-      <c r="C60" s="7">
-        <v>12</v>
-      </c>
-      <c r="D60" s="20"/>
-    </row>
-    <row r="61" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A61" s="7" t="s">
-        <v>45</v>
+      <c r="D60" s="17"/>
+      <c r="I60" s="11"/>
+      <c r="J60" s="7"/>
+      <c r="K60" s="7"/>
+    </row>
+    <row r="61" spans="1:11" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A61" s="11" t="s">
+        <v>43</v>
       </c>
       <c r="B61" s="7" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C61" s="7">
         <v>2</v>
       </c>
-      <c r="D61" s="20"/>
-    </row>
-    <row r="62" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A62" s="7" t="s">
-        <v>45</v>
+      <c r="D61" s="17"/>
+      <c r="I61" s="12"/>
+      <c r="J61" s="13"/>
+      <c r="K61" s="13"/>
+    </row>
+    <row r="62" spans="1:11" ht="17.25" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
+      <c r="A62" s="11" t="s">
+        <v>43</v>
       </c>
       <c r="B62" s="7" t="s">
         <v>131</v>
       </c>
       <c r="C62" s="7">
-        <v>2</v>
-      </c>
-      <c r="D62" s="20"/>
+        <v>1</v>
+      </c>
+      <c r="D62" s="17"/>
     </row>
     <row r="63" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A63" s="7" t="s">
-        <v>45</v>
+      <c r="A63" s="11" t="s">
+        <v>43</v>
       </c>
       <c r="B63" s="7" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="C63" s="7">
         <v>1</v>
       </c>
-      <c r="D63" s="20"/>
+      <c r="D63" s="17"/>
     </row>
     <row r="64" spans="1:11" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A64" s="13" t="s">
-        <v>45</v>
+      <c r="A64" s="12" t="s">
+        <v>43</v>
       </c>
       <c r="B64" s="13" t="s">
         <v>133</v>
@@ -2566,222 +2667,398 @@
       <c r="C64" s="13">
         <v>1</v>
       </c>
-      <c r="D64" s="21"/>
-    </row>
-    <row r="65" spans="1:4" ht="17.25" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="D64" s="18"/>
+    </row>
+    <row r="65" spans="1:4" ht="17.25" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
       <c r="A65" s="10" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="B65" s="10" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="C65" s="10">
-        <v>22</v>
-      </c>
-      <c r="D65" s="19">
-        <f>SUM(C65:C75)/100</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="66" spans="1:4" s="18" customFormat="1" ht="17.25" thickTop="1" x14ac:dyDescent="0.3">
+        <v>50</v>
+      </c>
+      <c r="D65" s="16">
+        <f>SUM(C65:C72)/100</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="66" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A66" s="7" t="s">
-        <v>136</v>
+        <v>47</v>
       </c>
       <c r="B66" s="7" t="s">
+        <v>118</v>
+      </c>
+      <c r="C66" s="7">
+        <v>16</v>
+      </c>
+      <c r="D66" s="17"/>
+    </row>
+    <row r="67" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A67" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="B67" s="7" t="s">
         <v>119</v>
       </c>
-      <c r="C66" s="7">
-        <v>20</v>
-      </c>
-      <c r="D66" s="22"/>
-    </row>
-    <row r="67" spans="1:4" s="18" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A67" s="7" t="s">
-        <v>136</v>
-      </c>
-      <c r="B67" s="7" t="s">
-        <v>120</v>
-      </c>
       <c r="C67" s="7">
-        <v>20</v>
-      </c>
-      <c r="D67" s="22"/>
+        <v>16</v>
+      </c>
+      <c r="D67" s="17"/>
     </row>
     <row r="68" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A68" s="7" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="B68" s="7" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C68" s="7">
-        <v>10</v>
-      </c>
-      <c r="D68" s="20"/>
+        <v>12</v>
+      </c>
+      <c r="D68" s="17"/>
     </row>
     <row r="69" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A69" s="7" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="B69" s="7" t="s">
-        <v>134</v>
+        <v>108</v>
       </c>
       <c r="C69" s="7">
-        <v>10</v>
-      </c>
-      <c r="D69" s="20"/>
+        <v>2</v>
+      </c>
+      <c r="D69" s="17"/>
     </row>
     <row r="70" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A70" s="7" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="B70" s="7" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="C70" s="7">
-        <v>4</v>
-      </c>
-      <c r="D70" s="20"/>
+        <v>2</v>
+      </c>
+      <c r="D70" s="17"/>
     </row>
     <row r="71" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A71" s="7" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="B71" s="7" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="C71" s="7">
+        <v>1</v>
+      </c>
+      <c r="D71" s="17"/>
+    </row>
+    <row r="72" spans="1:4" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A72" s="13" t="s">
+        <v>47</v>
+      </c>
+      <c r="B72" s="13" t="s">
+        <v>134</v>
+      </c>
+      <c r="C72" s="13">
+        <v>1</v>
+      </c>
+      <c r="D72" s="18"/>
+    </row>
+    <row r="73" spans="1:4" ht="17.25" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A73" s="10" t="s">
+        <v>51</v>
+      </c>
+      <c r="B73" s="10" t="s">
+        <v>104</v>
+      </c>
+      <c r="C73" s="10">
+        <v>22</v>
+      </c>
+      <c r="D73" s="16">
+        <f>SUM(C73:C84)/100</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="74" spans="1:4" ht="17.25" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
+      <c r="A74" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="B74" s="7" t="s">
+        <v>118</v>
+      </c>
+      <c r="C74" s="7">
+        <v>20</v>
+      </c>
+      <c r="D74" s="17"/>
+    </row>
+    <row r="75" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A75" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="B75" s="7" t="s">
+        <v>119</v>
+      </c>
+      <c r="C75" s="7">
+        <v>20</v>
+      </c>
+      <c r="D75" s="17"/>
+    </row>
+    <row r="76" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A76" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="B76" s="7" t="s">
+        <v>109</v>
+      </c>
+      <c r="C76" s="7">
+        <v>10</v>
+      </c>
+      <c r="D76" s="17"/>
+    </row>
+    <row r="77" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A77" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="B77" s="7" t="s">
+        <v>127</v>
+      </c>
+      <c r="C77" s="7">
+        <v>10</v>
+      </c>
+      <c r="D77" s="17"/>
+    </row>
+    <row r="78" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A78" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="B78" s="7" t="s">
+        <v>129</v>
+      </c>
+      <c r="C78" s="7">
+        <v>3</v>
+      </c>
+      <c r="D78" s="17"/>
+    </row>
+    <row r="79" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A79" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="B79" s="7" t="s">
+        <v>131</v>
+      </c>
+      <c r="C79" s="7">
         <v>2</v>
       </c>
-      <c r="D71" s="20"/>
-    </row>
-    <row r="72" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A72" s="7" t="s">
-        <v>49</v>
-      </c>
-      <c r="B72" s="7" t="s">
+      <c r="D79" s="17"/>
+    </row>
+    <row r="80" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A80" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="B80" s="7" t="s">
         <v>128</v>
       </c>
-      <c r="C72" s="7">
+      <c r="C80" s="7">
         <v>3</v>
       </c>
-      <c r="D72" s="20"/>
-    </row>
-    <row r="73" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A73" s="7" t="s">
-        <v>49</v>
-      </c>
-      <c r="B73" s="7" t="s">
-        <v>132</v>
-      </c>
-      <c r="C73" s="7">
+      <c r="D80" s="17"/>
+    </row>
+    <row r="81" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A81" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="B81" s="7" t="s">
+        <v>133</v>
+      </c>
+      <c r="C81" s="7">
         <v>3</v>
       </c>
-      <c r="D73" s="20"/>
-    </row>
-    <row r="74" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A74" s="14" t="s">
-        <v>49</v>
-      </c>
-      <c r="B74" s="15" t="s">
-        <v>133</v>
-      </c>
-      <c r="C74" s="7">
+      <c r="D81" s="17"/>
+    </row>
+    <row r="82" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A82" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="B82" s="7" t="s">
+        <v>134</v>
+      </c>
+      <c r="C82" s="7">
         <v>3</v>
       </c>
-      <c r="D74" s="20"/>
-    </row>
-    <row r="75" spans="1:4" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A75" s="16" t="s">
-        <v>49</v>
-      </c>
-      <c r="B75" s="17" t="s">
-        <v>123</v>
-      </c>
-      <c r="C75" s="13">
+      <c r="D82" s="17"/>
+    </row>
+    <row r="83" spans="1:4" s="14" customFormat="1" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A83" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="B83" s="7" t="s">
+        <v>122</v>
+      </c>
+      <c r="C83" s="7">
         <v>3</v>
       </c>
-      <c r="D75" s="21"/>
-    </row>
-    <row r="76" spans="1:4" ht="17.25" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A76" s="10" t="s">
-        <v>56</v>
-      </c>
-      <c r="B76" s="7" t="s">
+      <c r="D83" s="17"/>
+    </row>
+    <row r="84" spans="1:4" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A84" s="13" t="s">
+        <v>51</v>
+      </c>
+      <c r="B84" s="13" t="s">
+        <v>150</v>
+      </c>
+      <c r="C84" s="13">
+        <v>1</v>
+      </c>
+      <c r="D84" s="18"/>
+    </row>
+    <row r="85" spans="1:4" ht="17.25" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A85" s="10" t="s">
+        <v>58</v>
+      </c>
+      <c r="B85" s="7" t="s">
+        <v>118</v>
+      </c>
+      <c r="C85" s="7">
+        <v>30</v>
+      </c>
+      <c r="D85" s="16">
+        <f>SUM(C85:C89)/100</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="86" spans="1:4" ht="17.25" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
+      <c r="A86" s="7" t="s">
+        <v>58</v>
+      </c>
+      <c r="B86" s="7" t="s">
         <v>119</v>
       </c>
-      <c r="C76" s="7">
+      <c r="C86" s="7">
         <v>30</v>
       </c>
-      <c r="D76" s="19">
-        <f>SUM(C76:C80)/100</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="77" spans="1:4" s="18" customFormat="1" ht="17.25" thickTop="1" x14ac:dyDescent="0.3">
-      <c r="A77" s="7" t="s">
-        <v>56</v>
-      </c>
-      <c r="B77" s="7" t="s">
-        <v>120</v>
-      </c>
-      <c r="C77" s="7">
-        <v>30</v>
-      </c>
-      <c r="D77" s="22"/>
-    </row>
-    <row r="78" spans="1:4" s="18" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A78" s="7" t="s">
-        <v>56</v>
-      </c>
-      <c r="B78" s="7" t="s">
-        <v>134</v>
-      </c>
-      <c r="C78" s="7">
+      <c r="D86" s="17"/>
+    </row>
+    <row r="87" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A87" s="7" t="s">
+        <v>58</v>
+      </c>
+      <c r="B87" s="7" t="s">
+        <v>127</v>
+      </c>
+      <c r="C87" s="7">
         <v>15</v>
       </c>
-      <c r="D78" s="22"/>
-    </row>
-    <row r="79" spans="1:4" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A79" s="7" t="s">
-        <v>56</v>
-      </c>
-      <c r="B79" s="7" t="s">
-        <v>107</v>
-      </c>
-      <c r="C79" s="7">
+      <c r="D87" s="17"/>
+    </row>
+    <row r="88" spans="1:4" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A88" s="7" t="s">
+        <v>58</v>
+      </c>
+      <c r="B88" s="7" t="s">
+        <v>109</v>
+      </c>
+      <c r="C88" s="7">
         <v>15</v>
       </c>
-      <c r="D79" s="20"/>
-    </row>
-    <row r="80" spans="1:4" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A80" s="13" t="s">
-        <v>56</v>
-      </c>
-      <c r="B80" s="13" t="s">
-        <v>135</v>
-      </c>
-      <c r="C80" s="13">
+      <c r="D88" s="17"/>
+    </row>
+    <row r="89" spans="1:4" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A89" s="13" t="s">
+        <v>58</v>
+      </c>
+      <c r="B89" s="13" t="s">
+        <v>129</v>
+      </c>
+      <c r="C89" s="13">
         <v>10</v>
       </c>
-      <c r="D80" s="21"/>
-    </row>
-    <row r="81" ht="17.25" customHeight="1" thickTop="1" x14ac:dyDescent="0.3"/>
+      <c r="D89" s="18"/>
+    </row>
+    <row r="90" spans="1:4" ht="17.25" customHeight="1" thickTop="1" x14ac:dyDescent="0.3"/>
+    <row r="91" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A91"/>
+      <c r="B91"/>
+      <c r="C91"/>
+      <c r="D91"/>
+    </row>
+    <row r="92" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A92"/>
+      <c r="B92"/>
+      <c r="C92"/>
+    </row>
+    <row r="93" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A93"/>
+      <c r="B93"/>
+      <c r="C93"/>
+    </row>
+    <row r="94" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A94"/>
+      <c r="B94"/>
+      <c r="C94"/>
+    </row>
+    <row r="95" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A95"/>
+      <c r="B95"/>
+      <c r="C95"/>
+    </row>
+    <row r="96" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A96"/>
+      <c r="B96"/>
+      <c r="C96"/>
+    </row>
+    <row r="97" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A97"/>
+      <c r="B97"/>
+      <c r="C97"/>
+    </row>
+    <row r="98" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A98"/>
+      <c r="B98"/>
+      <c r="C98"/>
+    </row>
+    <row r="99" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A99"/>
+      <c r="B99"/>
+      <c r="C99"/>
+    </row>
+    <row r="100" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A100"/>
+      <c r="B100"/>
+      <c r="C100"/>
+    </row>
+    <row r="101" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A101"/>
+      <c r="B101"/>
+      <c r="C101"/>
+    </row>
+    <row r="102" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A102"/>
+      <c r="B102"/>
+      <c r="C102"/>
+    </row>
   </sheetData>
-  <autoFilter ref="I43:K43" xr:uid="{0EF70075-620B-4549-A91C-D09223DDAD18}">
-    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="I44:K48">
-      <sortCondition descending="1" ref="K43"/>
+  <autoFilter ref="I51:K51" xr:uid="{00000000-0009-0000-0000-000001000000}">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="I52:K56">
+      <sortCondition descending="1" ref="K51"/>
     </sortState>
   </autoFilter>
-  <mergeCells count="8">
-    <mergeCell ref="D17:D22"/>
-    <mergeCell ref="D23:D29"/>
-    <mergeCell ref="D48:D56"/>
-    <mergeCell ref="D40:D47"/>
-    <mergeCell ref="D76:D80"/>
-    <mergeCell ref="D30:D39"/>
-    <mergeCell ref="D57:D64"/>
-    <mergeCell ref="D65:D75"/>
+  <mergeCells count="12">
+    <mergeCell ref="D85:D89"/>
+    <mergeCell ref="D31:D37"/>
+    <mergeCell ref="D56:D64"/>
+    <mergeCell ref="D17:D18"/>
+    <mergeCell ref="D19:D20"/>
+    <mergeCell ref="D21:D22"/>
+    <mergeCell ref="D23:D24"/>
+    <mergeCell ref="D73:D84"/>
+    <mergeCell ref="D48:D55"/>
+    <mergeCell ref="D65:D72"/>
+    <mergeCell ref="D38:D47"/>
+    <mergeCell ref="D25:D30"/>
   </mergeCells>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/raid_config.xlsx
+++ b/raid_config.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\new_bot\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1440483C-5172-4A90-9CC9-C2328DDA96DB}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{52FBE2CD-9319-4017-946B-1B61843BF2DE}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="1725" windowWidth="29040" windowHeight="17520" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="284" uniqueCount="151">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="286" uniqueCount="151">
   <si>
     <t>활성화여부</t>
   </si>
@@ -1829,7 +1829,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:K102"/>
+  <dimension ref="A1:K103"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="12" style="14" customWidth="1"/>
@@ -2919,14 +2919,14 @@
       <c r="A85" s="10" t="s">
         <v>58</v>
       </c>
-      <c r="B85" s="7" t="s">
+      <c r="B85" s="10" t="s">
         <v>118</v>
       </c>
-      <c r="C85" s="7">
+      <c r="C85" s="10">
         <v>30</v>
       </c>
       <c r="D85" s="16">
-        <f>SUM(C85:C89)/100</f>
+        <f>SUM(C85:C90)/100</f>
         <v>1</v>
       </c>
     </row>
@@ -2950,11 +2950,11 @@
         <v>127</v>
       </c>
       <c r="C87" s="7">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D87" s="17"/>
     </row>
-    <row r="88" spans="1:4" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:4" s="14" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A88" s="7" t="s">
         <v>58</v>
       </c>
@@ -2962,33 +2962,40 @@
         <v>109</v>
       </c>
       <c r="C88" s="7">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D88" s="17"/>
     </row>
-    <row r="89" spans="1:4" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A89" s="13" t="s">
+    <row r="89" spans="1:4" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A89" s="7" t="s">
         <v>58</v>
       </c>
-      <c r="B89" s="13" t="s">
+      <c r="B89" s="7" t="s">
         <v>129</v>
       </c>
-      <c r="C89" s="13">
+      <c r="C89" s="7">
         <v>10</v>
       </c>
-      <c r="D89" s="18"/>
-    </row>
-    <row r="90" spans="1:4" ht="17.25" customHeight="1" thickTop="1" x14ac:dyDescent="0.3"/>
-    <row r="91" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A91"/>
-      <c r="B91"/>
-      <c r="C91"/>
-      <c r="D91"/>
-    </row>
+      <c r="D89" s="17"/>
+    </row>
+    <row r="90" spans="1:4" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A90" s="13" t="s">
+        <v>58</v>
+      </c>
+      <c r="B90" s="13" t="s">
+        <v>150</v>
+      </c>
+      <c r="C90" s="13">
+        <v>2</v>
+      </c>
+      <c r="D90" s="18"/>
+    </row>
+    <row r="91" spans="1:4" ht="17.25" customHeight="1" thickTop="1" x14ac:dyDescent="0.3"/>
     <row r="92" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A92"/>
       <c r="B92"/>
       <c r="C92"/>
+      <c r="D92"/>
     </row>
     <row r="93" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A93"/>
@@ -3039,6 +3046,11 @@
       <c r="A102"/>
       <c r="B102"/>
       <c r="C102"/>
+    </row>
+    <row r="103" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A103"/>
+      <c r="B103"/>
+      <c r="C103"/>
     </row>
   </sheetData>
   <autoFilter ref="I51:K51" xr:uid="{00000000-0009-0000-0000-000001000000}">
@@ -3047,7 +3059,7 @@
     </sortState>
   </autoFilter>
   <mergeCells count="12">
-    <mergeCell ref="D85:D89"/>
+    <mergeCell ref="D85:D90"/>
     <mergeCell ref="D31:D37"/>
     <mergeCell ref="D56:D64"/>
     <mergeCell ref="D17:D18"/>

--- a/raid_config.xlsx
+++ b/raid_config.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\new_bot\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{52FBE2CD-9319-4017-946B-1B61843BF2DE}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A0B958E6-E217-4408-B965-D22DB3814B40}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="1725" windowWidth="29040" windowHeight="17520" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="레이드설정" sheetId="1" r:id="rId1"/>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="286" uniqueCount="151">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="290" uniqueCount="153">
   <si>
     <t>활성화여부</t>
   </si>
@@ -488,6 +488,13 @@
   </si>
   <si>
     <t>신수알</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>행운초기화구슬</t>
+  </si>
+  <si>
+    <t>행운초기화구슬</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -592,7 +599,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="14">
+  <borders count="15">
     <border>
       <left/>
       <right/>
@@ -785,11 +792,22 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
@@ -829,6 +847,7 @@
     <xf numFmtId="176" fontId="5" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
@@ -1593,7 +1612,7 @@
         <v>53</v>
       </c>
       <c r="E9" s="5">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="F9" s="5">
         <v>600000</v>
@@ -1654,7 +1673,7 @@
         <v>60</v>
       </c>
       <c r="E10" s="5">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="F10" s="5">
         <v>600000</v>
@@ -1829,7 +1848,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:K103"/>
+  <dimension ref="A1:K105"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="12" style="14" customWidth="1"/>
@@ -2669,7 +2688,7 @@
       </c>
       <c r="D64" s="18"/>
     </row>
-    <row r="65" spans="1:4" ht="17.25" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:6" ht="17.25" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
       <c r="A65" s="10" t="s">
         <v>47</v>
       </c>
@@ -2684,7 +2703,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="66" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A66" s="7" t="s">
         <v>47</v>
       </c>
@@ -2696,7 +2715,7 @@
       </c>
       <c r="D66" s="17"/>
     </row>
-    <row r="67" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A67" s="7" t="s">
         <v>47</v>
       </c>
@@ -2708,7 +2727,7 @@
       </c>
       <c r="D67" s="17"/>
     </row>
-    <row r="68" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A68" s="7" t="s">
         <v>47</v>
       </c>
@@ -2720,7 +2739,7 @@
       </c>
       <c r="D68" s="17"/>
     </row>
-    <row r="69" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A69" s="7" t="s">
         <v>47</v>
       </c>
@@ -2732,19 +2751,19 @@
       </c>
       <c r="D69" s="17"/>
     </row>
-    <row r="70" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A70" s="7" t="s">
         <v>47</v>
       </c>
-      <c r="B70" s="7" t="s">
-        <v>132</v>
+      <c r="B70" s="14" t="s">
+        <v>151</v>
       </c>
       <c r="C70" s="7">
         <v>2</v>
       </c>
       <c r="D70" s="17"/>
     </row>
-    <row r="71" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A71" s="7" t="s">
         <v>47</v>
       </c>
@@ -2756,7 +2775,7 @@
       </c>
       <c r="D71" s="17"/>
     </row>
-    <row r="72" spans="1:4" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="72" spans="1:6" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A72" s="13" t="s">
         <v>47</v>
       </c>
@@ -2768,7 +2787,7 @@
       </c>
       <c r="D72" s="18"/>
     </row>
-    <row r="73" spans="1:4" ht="17.25" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="73" spans="1:6" ht="17.25" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A73" s="10" t="s">
         <v>51</v>
       </c>
@@ -2776,14 +2795,15 @@
         <v>104</v>
       </c>
       <c r="C73" s="10">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D73" s="16">
-        <f>SUM(C73:C84)/100</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="74" spans="1:4" ht="17.25" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
+        <f>SUM(C73:C85)/100</f>
+        <v>1</v>
+      </c>
+      <c r="F73" s="14"/>
+    </row>
+    <row r="74" spans="1:6" ht="17.25" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
       <c r="A74" s="7" t="s">
         <v>51</v>
       </c>
@@ -2791,11 +2811,11 @@
         <v>118</v>
       </c>
       <c r="C74" s="7">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="D74" s="17"/>
     </row>
-    <row r="75" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A75" s="7" t="s">
         <v>51</v>
       </c>
@@ -2803,11 +2823,11 @@
         <v>119</v>
       </c>
       <c r="C75" s="7">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="D75" s="17"/>
     </row>
-    <row r="76" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A76" s="7" t="s">
         <v>51</v>
       </c>
@@ -2819,7 +2839,7 @@
       </c>
       <c r="D76" s="17"/>
     </row>
-    <row r="77" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A77" s="7" t="s">
         <v>51</v>
       </c>
@@ -2831,39 +2851,39 @@
       </c>
       <c r="D77" s="17"/>
     </row>
-    <row r="78" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:6" s="14" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A78" s="7" t="s">
         <v>51</v>
       </c>
       <c r="B78" s="7" t="s">
-        <v>129</v>
+        <v>152</v>
       </c>
       <c r="C78" s="7">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D78" s="17"/>
     </row>
-    <row r="79" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A79" s="7" t="s">
         <v>51</v>
       </c>
       <c r="B79" s="7" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="C79" s="7">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D79" s="17"/>
     </row>
-    <row r="80" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A80" s="7" t="s">
         <v>51</v>
       </c>
       <c r="B80" s="7" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="C80" s="7">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D80" s="17"/>
     </row>
@@ -2872,7 +2892,7 @@
         <v>51</v>
       </c>
       <c r="B81" s="7" t="s">
-        <v>133</v>
+        <v>128</v>
       </c>
       <c r="C81" s="7">
         <v>3</v>
@@ -2884,128 +2904,142 @@
         <v>51</v>
       </c>
       <c r="B82" s="7" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C82" s="7">
         <v>3</v>
       </c>
       <c r="D82" s="17"/>
     </row>
-    <row r="83" spans="1:4" s="14" customFormat="1" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A83" s="7" t="s">
         <v>51</v>
       </c>
       <c r="B83" s="7" t="s">
-        <v>122</v>
+        <v>134</v>
       </c>
       <c r="C83" s="7">
         <v>3</v>
       </c>
       <c r="D83" s="17"/>
     </row>
-    <row r="84" spans="1:4" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A84" s="13" t="s">
+    <row r="84" spans="1:4" s="14" customFormat="1" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A84" s="7" t="s">
         <v>51</v>
       </c>
-      <c r="B84" s="13" t="s">
+      <c r="B84" s="7" t="s">
+        <v>122</v>
+      </c>
+      <c r="C84" s="7">
+        <v>3</v>
+      </c>
+      <c r="D84" s="17"/>
+    </row>
+    <row r="85" spans="1:4" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A85" s="13" t="s">
+        <v>51</v>
+      </c>
+      <c r="B85" s="13" t="s">
         <v>150</v>
       </c>
-      <c r="C84" s="13">
-        <v>1</v>
-      </c>
-      <c r="D84" s="18"/>
-    </row>
-    <row r="85" spans="1:4" ht="17.25" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A85" s="10" t="s">
+      <c r="C85" s="13">
+        <v>1</v>
+      </c>
+      <c r="D85" s="18"/>
+    </row>
+    <row r="86" spans="1:4" ht="17.25" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A86" s="10" t="s">
         <v>58</v>
       </c>
-      <c r="B85" s="10" t="s">
+      <c r="B86" s="10" t="s">
         <v>118</v>
       </c>
-      <c r="C85" s="10">
+      <c r="C86" s="10">
         <v>30</v>
       </c>
-      <c r="D85" s="16">
-        <f>SUM(C85:C90)/100</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="86" spans="1:4" ht="17.25" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
-      <c r="A86" s="7" t="s">
-        <v>58</v>
-      </c>
-      <c r="B86" s="7" t="s">
-        <v>119</v>
-      </c>
-      <c r="C86" s="7">
-        <v>30</v>
-      </c>
-      <c r="D86" s="17"/>
-    </row>
-    <row r="87" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="D86" s="16">
+        <f>SUM(C86:C92)/100</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="87" spans="1:4" ht="17.25" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
       <c r="A87" s="7" t="s">
         <v>58</v>
       </c>
       <c r="B87" s="7" t="s">
-        <v>127</v>
+        <v>119</v>
       </c>
       <c r="C87" s="7">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="D87" s="17"/>
     </row>
-    <row r="88" spans="1:4" s="14" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A88" s="7" t="s">
         <v>58</v>
       </c>
       <c r="B88" s="7" t="s">
-        <v>109</v>
+        <v>127</v>
       </c>
       <c r="C88" s="7">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="D88" s="17"/>
     </row>
-    <row r="89" spans="1:4" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:4" s="14" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A89" s="7" t="s">
         <v>58</v>
       </c>
       <c r="B89" s="7" t="s">
-        <v>129</v>
+        <v>109</v>
       </c>
       <c r="C89" s="7">
         <v>10</v>
       </c>
       <c r="D89" s="17"/>
     </row>
-    <row r="90" spans="1:4" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A90" s="13" t="s">
+    <row r="90" spans="1:4" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A90" s="7" t="s">
         <v>58</v>
       </c>
-      <c r="B90" s="13" t="s">
+      <c r="B90" s="7" t="s">
+        <v>129</v>
+      </c>
+      <c r="C90" s="7">
+        <v>10</v>
+      </c>
+      <c r="D90" s="17"/>
+    </row>
+    <row r="91" spans="1:4" s="14" customFormat="1" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A91" s="7" t="s">
+        <v>58</v>
+      </c>
+      <c r="B91" s="21" t="s">
+        <v>151</v>
+      </c>
+      <c r="C91" s="7">
+        <v>10</v>
+      </c>
+      <c r="D91" s="17"/>
+    </row>
+    <row r="92" spans="1:4" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A92" s="13" t="s">
+        <v>58</v>
+      </c>
+      <c r="B92" s="13" t="s">
         <v>150</v>
       </c>
-      <c r="C90" s="13">
+      <c r="C92" s="13">
         <v>2</v>
       </c>
-      <c r="D90" s="18"/>
-    </row>
-    <row r="91" spans="1:4" ht="17.25" customHeight="1" thickTop="1" x14ac:dyDescent="0.3"/>
-    <row r="92" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A92"/>
-      <c r="B92"/>
-      <c r="C92"/>
-      <c r="D92"/>
-    </row>
-    <row r="93" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A93"/>
-      <c r="B93"/>
-      <c r="C93"/>
-    </row>
+      <c r="D92" s="18"/>
+    </row>
+    <row r="93" spans="1:4" ht="17.25" customHeight="1" thickTop="1" x14ac:dyDescent="0.3"/>
     <row r="94" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A94"/>
       <c r="B94"/>
       <c r="C94"/>
+      <c r="D94"/>
     </row>
     <row r="95" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A95"/>
@@ -3051,6 +3085,16 @@
       <c r="A103"/>
       <c r="B103"/>
       <c r="C103"/>
+    </row>
+    <row r="104" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A104"/>
+      <c r="B104"/>
+      <c r="C104"/>
+    </row>
+    <row r="105" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A105"/>
+      <c r="B105"/>
+      <c r="C105"/>
     </row>
   </sheetData>
   <autoFilter ref="I51:K51" xr:uid="{00000000-0009-0000-0000-000001000000}">
@@ -3059,14 +3103,14 @@
     </sortState>
   </autoFilter>
   <mergeCells count="12">
-    <mergeCell ref="D85:D90"/>
+    <mergeCell ref="D86:D92"/>
     <mergeCell ref="D31:D37"/>
     <mergeCell ref="D56:D64"/>
     <mergeCell ref="D17:D18"/>
     <mergeCell ref="D19:D20"/>
     <mergeCell ref="D21:D22"/>
     <mergeCell ref="D23:D24"/>
-    <mergeCell ref="D73:D84"/>
+    <mergeCell ref="D73:D85"/>
     <mergeCell ref="D48:D55"/>
     <mergeCell ref="D65:D72"/>
     <mergeCell ref="D38:D47"/>

--- a/raid_config.xlsx
+++ b/raid_config.xlsx
@@ -8,23 +8,23 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\new_bot\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A0B958E6-E217-4408-B965-D22DB3814B40}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CDBC6535-BCA1-433B-BDB6-0E0C4F00E3A1}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="1725" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="레이드설정" sheetId="1" r:id="rId1"/>
     <sheet name="DATA" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">DATA!$I$51:$K$51</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">DATA!$I$52:$K$52</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="290" uniqueCount="153">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="305" uniqueCount="157">
   <si>
     <t>활성화여부</t>
   </si>
@@ -495,6 +495,21 @@
   </si>
   <si>
     <t>행운초기화구슬</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>지옥4</t>
+  </si>
+  <si>
+    <t>지옥4</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>행운초기화꾸러미</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>6,7,11</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -599,7 +614,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="15">
+  <borders count="19">
     <border>
       <left/>
       <right/>
@@ -623,19 +638,6 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
       <left style="thick">
         <color auto="1"/>
       </left>
@@ -769,21 +771,6 @@
       <right style="thick">
         <color auto="1"/>
       </right>
-      <top style="thick">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thick">
-        <color auto="1"/>
-      </right>
       <top style="thin">
         <color auto="1"/>
       </top>
@@ -803,11 +790,95 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thick">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thick">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thick">
+        <color auto="1"/>
+      </top>
+      <bottom style="thick">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thick">
+        <color auto="1"/>
+      </right>
+      <top style="thick">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thick">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thick">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
@@ -826,28 +897,35 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="176" fontId="4" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="176" fontId="4" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
-    <xf numFmtId="176" fontId="5" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1"/>
+    <xf numFmtId="176" fontId="4" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="5" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
+    <xf numFmtId="176" fontId="5" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1"/>
+    <xf numFmtId="176" fontId="5" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
@@ -1150,26 +1228,26 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:Y28"/>
+  <dimension ref="A1:Y29"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="2" width="10" style="14" customWidth="1"/>
-    <col min="3" max="3" width="6" style="14" customWidth="1"/>
-    <col min="4" max="5" width="10" style="14" customWidth="1"/>
-    <col min="6" max="7" width="12" style="14" customWidth="1"/>
-    <col min="8" max="8" width="14" style="14" customWidth="1"/>
-    <col min="9" max="9" width="12" style="14" customWidth="1"/>
-    <col min="10" max="11" width="10" style="14" customWidth="1"/>
-    <col min="12" max="12" width="12" style="14" customWidth="1"/>
-    <col min="13" max="13" width="10" style="14" customWidth="1"/>
-    <col min="14" max="15" width="12" style="14" customWidth="1"/>
-    <col min="16" max="16" width="10" style="14" customWidth="1"/>
-    <col min="17" max="18" width="12" style="14" customWidth="1"/>
-    <col min="19" max="19" width="14" style="14" customWidth="1"/>
-    <col min="20" max="20" width="12" style="14" customWidth="1"/>
-    <col min="21" max="22" width="35" style="14" customWidth="1"/>
-    <col min="23" max="23" width="12" style="14" customWidth="1"/>
-    <col min="24" max="25" width="35" style="14" customWidth="1"/>
+    <col min="1" max="2" width="10" style="13" customWidth="1"/>
+    <col min="3" max="3" width="6" style="13" customWidth="1"/>
+    <col min="4" max="5" width="10" style="13" customWidth="1"/>
+    <col min="6" max="7" width="12" style="13" customWidth="1"/>
+    <col min="8" max="8" width="14" style="13" customWidth="1"/>
+    <col min="9" max="9" width="12" style="13" customWidth="1"/>
+    <col min="10" max="11" width="10" style="13" customWidth="1"/>
+    <col min="12" max="12" width="12" style="13" customWidth="1"/>
+    <col min="13" max="13" width="10" style="13" customWidth="1"/>
+    <col min="14" max="15" width="12" style="13" customWidth="1"/>
+    <col min="16" max="16" width="10" style="13" customWidth="1"/>
+    <col min="17" max="18" width="12" style="13" customWidth="1"/>
+    <col min="19" max="19" width="14" style="13" customWidth="1"/>
+    <col min="20" max="20" width="12" style="13" customWidth="1"/>
+    <col min="21" max="22" width="35" style="13" customWidth="1"/>
+    <col min="23" max="23" width="12" style="13" customWidth="1"/>
+    <col min="24" max="25" width="35" style="13" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:25" x14ac:dyDescent="0.3">
@@ -1313,7 +1391,7 @@
         <v>120000</v>
       </c>
       <c r="H3" s="5">
-        <v>0</v>
+        <v>30000</v>
       </c>
       <c r="I3" s="5">
         <v>600</v>
@@ -1327,7 +1405,7 @@
       <c r="L3" s="5">
         <v>1</v>
       </c>
-      <c r="M3" s="15"/>
+      <c r="M3" s="14"/>
       <c r="N3" s="5"/>
       <c r="O3" s="5"/>
       <c r="P3" s="5"/>
@@ -1378,7 +1456,7 @@
       <c r="L4" s="5">
         <v>1</v>
       </c>
-      <c r="M4" s="15"/>
+      <c r="M4" s="14"/>
       <c r="N4" s="5"/>
       <c r="O4" s="5"/>
       <c r="P4" s="5"/>
@@ -1429,7 +1507,7 @@
       <c r="L5" s="5">
         <v>1</v>
       </c>
-      <c r="M5" s="15"/>
+      <c r="M5" s="14"/>
       <c r="N5" s="5"/>
       <c r="O5" s="5"/>
       <c r="P5" s="5"/>
@@ -1480,7 +1558,7 @@
       <c r="L6" s="5">
         <v>1</v>
       </c>
-      <c r="M6" s="15"/>
+      <c r="M6" s="14"/>
       <c r="N6" s="5"/>
       <c r="O6" s="5"/>
       <c r="P6" s="5"/>
@@ -1531,7 +1609,7 @@
       <c r="L7" s="5">
         <v>1</v>
       </c>
-      <c r="M7" s="15"/>
+      <c r="M7" s="14"/>
       <c r="N7" s="5"/>
       <c r="O7" s="5"/>
       <c r="P7" s="5"/>
@@ -1582,7 +1660,7 @@
       <c r="L8" s="5">
         <v>2</v>
       </c>
-      <c r="M8" s="15"/>
+      <c r="M8" s="14"/>
       <c r="N8" s="5"/>
       <c r="O8" s="5"/>
       <c r="P8" s="5"/>
@@ -1633,7 +1711,7 @@
       <c r="L9" s="5">
         <v>2</v>
       </c>
-      <c r="M9" s="15">
+      <c r="M9" s="14">
         <v>60000</v>
       </c>
       <c r="N9" s="5">
@@ -1659,7 +1737,7 @@
       <c r="X9" s="5"/>
       <c r="Y9" s="5"/>
     </row>
-    <row r="10" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:25" s="13" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A10" s="5" t="s">
         <v>25</v>
       </c>
@@ -1694,7 +1772,7 @@
       <c r="L10" s="5">
         <v>2</v>
       </c>
-      <c r="M10" s="15">
+      <c r="M10" s="14">
         <v>70000</v>
       </c>
       <c r="N10" s="5">
@@ -1732,110 +1810,161 @@
         <v>67</v>
       </c>
     </row>
-    <row r="13" spans="1:25" x14ac:dyDescent="0.3">
-      <c r="S13" s="5"/>
-    </row>
-    <row r="16" spans="1:25" x14ac:dyDescent="0.3">
-      <c r="P16">
-        <v>1</v>
-      </c>
-      <c r="R16" t="s">
-        <v>68</v>
-      </c>
+    <row r="11" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A11" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="B11" s="5" t="s">
+        <v>154</v>
+      </c>
+      <c r="C11" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="D11" s="5" t="s">
+        <v>60</v>
+      </c>
+      <c r="E11" s="5">
+        <v>25</v>
+      </c>
+      <c r="F11" s="5">
+        <v>2000000</v>
+      </c>
+      <c r="G11" s="5">
+        <v>2020000</v>
+      </c>
+      <c r="H11" s="5">
+        <v>0</v>
+      </c>
+      <c r="I11" s="5">
+        <v>900</v>
+      </c>
+      <c r="J11" s="5"/>
+      <c r="K11" s="5">
+        <v>700</v>
+      </c>
+      <c r="L11" s="5">
+        <v>2</v>
+      </c>
+      <c r="M11" s="14"/>
+      <c r="N11" s="5"/>
+      <c r="O11" s="5"/>
+      <c r="P11" s="5"/>
+      <c r="Q11" s="5"/>
+      <c r="R11" s="5"/>
+      <c r="S11" s="5" t="s">
+        <v>156</v>
+      </c>
+      <c r="T11" s="5"/>
+      <c r="U11" s="5"/>
+      <c r="V11" s="5"/>
+      <c r="W11" s="5"/>
+      <c r="X11" s="5"/>
+      <c r="Y11" s="5"/>
+    </row>
+    <row r="14" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="S14" s="5"/>
     </row>
     <row r="17" spans="16:18" x14ac:dyDescent="0.3">
       <c r="P17">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R17" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="18" spans="16:18" x14ac:dyDescent="0.3">
       <c r="P18">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="R18" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="19" spans="16:18" x14ac:dyDescent="0.3">
       <c r="P19">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="R19" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="20" spans="16:18" x14ac:dyDescent="0.3">
       <c r="P20">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="R20" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="21" spans="16:18" x14ac:dyDescent="0.3">
       <c r="P21">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="R21" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="22" spans="16:18" x14ac:dyDescent="0.3">
       <c r="P22">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="R22" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
     </row>
     <row r="23" spans="16:18" x14ac:dyDescent="0.3">
       <c r="P23">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="R23" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="24" spans="16:18" x14ac:dyDescent="0.3">
       <c r="P24">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="R24" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="25" spans="16:18" x14ac:dyDescent="0.3">
       <c r="P25">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="R25" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="26" spans="16:18" x14ac:dyDescent="0.3">
       <c r="P26">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="R26" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="27" spans="16:18" x14ac:dyDescent="0.3">
       <c r="P27">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="R27" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="28" spans="16:18" x14ac:dyDescent="0.3">
       <c r="P28">
+        <v>12</v>
+      </c>
+      <c r="R28" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="29" spans="16:18" x14ac:dyDescent="0.3">
+      <c r="P29">
         <v>13</v>
       </c>
-      <c r="R28" t="s">
+      <c r="R29" t="s">
         <v>80</v>
       </c>
     </row>
@@ -1848,13 +1977,13 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:K105"/>
+  <dimension ref="A1:K103"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="12" style="14" customWidth="1"/>
-    <col min="2" max="2" width="22" style="14" customWidth="1"/>
-    <col min="3" max="3" width="10" style="14" customWidth="1"/>
-    <col min="4" max="4" width="40" style="14" customWidth="1"/>
+    <col min="1" max="1" width="12" style="13" customWidth="1"/>
+    <col min="2" max="2" width="22" style="13" customWidth="1"/>
+    <col min="3" max="3" width="10" style="13" customWidth="1"/>
+    <col min="4" max="4" width="40" style="13" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.3">
@@ -2011,1110 +2140,1143 @@
         <v>80</v>
       </c>
     </row>
-    <row r="16" spans="1:4" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A16" s="8" t="s">
+    <row r="15" spans="1:4" ht="17.25" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="16" spans="1:4" ht="17.25" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A16" s="18" t="s">
         <v>100</v>
       </c>
-      <c r="B16" s="8" t="s">
+      <c r="B16" s="18" t="s">
         <v>101</v>
       </c>
-      <c r="C16" s="8" t="s">
+      <c r="C16" s="18" t="s">
         <v>102</v>
       </c>
-      <c r="D16" s="8" t="s">
+      <c r="D16" s="18" t="s">
         <v>103</v>
       </c>
     </row>
-    <row r="17" spans="1:4" s="14" customFormat="1" ht="17.25" thickTop="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="9" t="s">
+    <row r="17" spans="1:4" s="13" customFormat="1" ht="17.25" thickTop="1" x14ac:dyDescent="0.3">
+      <c r="A17" s="16" t="s">
         <v>135</v>
       </c>
-      <c r="B17" s="7" t="s">
+      <c r="B17" s="17" t="s">
+        <v>152</v>
+      </c>
+      <c r="C17" s="17">
+        <v>2</v>
+      </c>
+      <c r="D17" s="25">
+        <f>SUM(C17:C19)/100</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" s="13" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A18" s="10" t="s">
+        <v>135</v>
+      </c>
+      <c r="B18" s="7" t="s">
         <v>140</v>
       </c>
-      <c r="C17" s="10">
+      <c r="C18" s="7">
+        <v>48</v>
+      </c>
+      <c r="D18" s="25"/>
+    </row>
+    <row r="19" spans="1:4" s="13" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A19" s="10" t="s">
+        <v>135</v>
+      </c>
+      <c r="B19" s="7" t="s">
+        <v>147</v>
+      </c>
+      <c r="C19" s="7">
         <v>50</v>
       </c>
-      <c r="D17" s="19">
-        <f>SUM(C17:C18)/100</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="18" spans="1:4" s="14" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="11" t="s">
-        <v>135</v>
-      </c>
-      <c r="B18" s="7" t="s">
+      <c r="D19" s="26"/>
+    </row>
+    <row r="20" spans="1:4" s="13" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A20" s="10" t="s">
+        <v>136</v>
+      </c>
+      <c r="B20" s="7" t="s">
+        <v>145</v>
+      </c>
+      <c r="C20" s="7">
+        <v>70</v>
+      </c>
+      <c r="D20" s="26">
+        <f>SUM(C20:C21)/100</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" s="13" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A21" s="10" t="s">
+        <v>136</v>
+      </c>
+      <c r="B21" s="7" t="s">
         <v>147</v>
       </c>
-      <c r="C18" s="7">
-        <v>50</v>
-      </c>
-      <c r="D18" s="20"/>
-    </row>
-    <row r="19" spans="1:4" s="14" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="11" t="s">
-        <v>136</v>
-      </c>
-      <c r="B19" s="7" t="s">
-        <v>145</v>
-      </c>
-      <c r="C19" s="7">
+      <c r="C21" s="7">
+        <v>30</v>
+      </c>
+      <c r="D21" s="26"/>
+    </row>
+    <row r="22" spans="1:4" s="13" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A22" s="10" t="s">
+        <v>137</v>
+      </c>
+      <c r="B22" s="7" t="s">
+        <v>143</v>
+      </c>
+      <c r="C22" s="7">
         <v>70</v>
       </c>
-      <c r="D19" s="20">
-        <f>SUM(C19:C20)/100</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="20" spans="1:4" s="14" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="11" t="s">
-        <v>136</v>
-      </c>
-      <c r="B20" s="7" t="s">
-        <v>147</v>
-      </c>
-      <c r="C20" s="7">
+      <c r="D22" s="26">
+        <f>SUM(C22:C23)/100</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" s="13" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A23" s="10" t="s">
+        <v>137</v>
+      </c>
+      <c r="B23" s="7" t="s">
+        <v>141</v>
+      </c>
+      <c r="C23" s="7">
         <v>30</v>
       </c>
-      <c r="D20" s="20"/>
-    </row>
-    <row r="21" spans="1:4" s="14" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="11" t="s">
-        <v>137</v>
-      </c>
-      <c r="B21" s="7" t="s">
+      <c r="D23" s="26"/>
+    </row>
+    <row r="24" spans="1:4" s="13" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A24" s="10" t="s">
+        <v>138</v>
+      </c>
+      <c r="B24" s="7" t="s">
+        <v>148</v>
+      </c>
+      <c r="C24" s="7">
+        <v>70</v>
+      </c>
+      <c r="D24" s="26">
+        <f>SUM(C24:C25)/100</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" s="13" customFormat="1" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A25" s="10" t="s">
+        <v>138</v>
+      </c>
+      <c r="B25" s="7" t="s">
+        <v>142</v>
+      </c>
+      <c r="C25" s="7">
+        <v>30</v>
+      </c>
+      <c r="D25" s="26"/>
+    </row>
+    <row r="26" spans="1:4" ht="17.25" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A26" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="B26" s="9" t="s">
+        <v>104</v>
+      </c>
+      <c r="C26" s="9">
+        <v>60</v>
+      </c>
+      <c r="D26" s="22">
+        <f>SUM(C26:C31)/100</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A27" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="B27" s="7" t="s">
+        <v>105</v>
+      </c>
+      <c r="C27" s="7">
+        <v>20</v>
+      </c>
+      <c r="D27" s="23"/>
+    </row>
+    <row r="28" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A28" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="B28" s="7" t="s">
+        <v>106</v>
+      </c>
+      <c r="C28" s="7">
+        <v>10</v>
+      </c>
+      <c r="D28" s="23"/>
+    </row>
+    <row r="29" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A29" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="B29" s="7" t="s">
+        <v>107</v>
+      </c>
+      <c r="C29" s="7">
+        <v>5</v>
+      </c>
+      <c r="D29" s="23"/>
+    </row>
+    <row r="30" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A30" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="B30" s="7" t="s">
+        <v>139</v>
+      </c>
+      <c r="C30" s="7">
+        <v>3</v>
+      </c>
+      <c r="D30" s="23"/>
+    </row>
+    <row r="31" spans="1:4" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A31" s="11" t="s">
+        <v>30</v>
+      </c>
+      <c r="B31" s="12" t="s">
+        <v>109</v>
+      </c>
+      <c r="C31" s="12">
+        <v>2</v>
+      </c>
+      <c r="D31" s="24"/>
+    </row>
+    <row r="32" spans="1:4" ht="17.25" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
+      <c r="A32" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="B32" s="9" t="s">
+        <v>144</v>
+      </c>
+      <c r="C32" s="9">
+        <v>60</v>
+      </c>
+      <c r="D32" s="22">
+        <f>SUM(C32:C38)/100</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A33" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="B33" s="7" t="s">
         <v>143</v>
       </c>
-      <c r="C21" s="7">
-        <v>70</v>
-      </c>
-      <c r="D21" s="20">
-        <f>SUM(C21:C22)/100</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="22" spans="1:4" s="14" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="11" t="s">
-        <v>137</v>
-      </c>
-      <c r="B22" s="7" t="s">
-        <v>141</v>
-      </c>
-      <c r="C22" s="7">
-        <v>30</v>
-      </c>
-      <c r="D22" s="20"/>
-    </row>
-    <row r="23" spans="1:4" s="14" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="11" t="s">
-        <v>138</v>
-      </c>
-      <c r="B23" s="7" t="s">
-        <v>148</v>
-      </c>
-      <c r="C23" s="7">
-        <v>70</v>
-      </c>
-      <c r="D23" s="20">
-        <f>SUM(C23:C24)/100</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="24" spans="1:4" s="14" customFormat="1" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A24" s="11" t="s">
-        <v>138</v>
-      </c>
-      <c r="B24" s="7" t="s">
-        <v>142</v>
-      </c>
-      <c r="C24" s="7">
-        <v>30</v>
-      </c>
-      <c r="D24" s="20"/>
-    </row>
-    <row r="25" spans="1:4" ht="17.25" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A25" s="9" t="s">
-        <v>30</v>
-      </c>
-      <c r="B25" s="10" t="s">
-        <v>104</v>
-      </c>
-      <c r="C25" s="10">
-        <v>60</v>
-      </c>
-      <c r="D25" s="16">
-        <f>SUM(C25:C30)/100</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A26" s="11" t="s">
-        <v>30</v>
-      </c>
-      <c r="B26" s="7" t="s">
-        <v>105</v>
-      </c>
-      <c r="C26" s="7">
+      <c r="C33" s="7">
         <v>20</v>
       </c>
-      <c r="D26" s="17"/>
-    </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A27" s="11" t="s">
-        <v>30</v>
-      </c>
-      <c r="B27" s="7" t="s">
-        <v>106</v>
-      </c>
-      <c r="C27" s="7">
-        <v>10</v>
-      </c>
-      <c r="D27" s="17"/>
-    </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A28" s="11" t="s">
-        <v>30</v>
-      </c>
-      <c r="B28" s="7" t="s">
-        <v>107</v>
-      </c>
-      <c r="C28" s="7">
-        <v>5</v>
-      </c>
-      <c r="D28" s="17"/>
-    </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A29" s="11" t="s">
-        <v>30</v>
-      </c>
-      <c r="B29" s="7" t="s">
-        <v>139</v>
-      </c>
-      <c r="C29" s="7">
-        <v>3</v>
-      </c>
-      <c r="D29" s="17"/>
-    </row>
-    <row r="30" spans="1:4" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A30" s="12" t="s">
-        <v>30</v>
-      </c>
-      <c r="B30" s="13" t="s">
-        <v>109</v>
-      </c>
-      <c r="C30" s="13">
-        <v>2</v>
-      </c>
-      <c r="D30" s="18"/>
-    </row>
-    <row r="31" spans="1:4" ht="17.25" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
-      <c r="A31" s="9" t="s">
+      <c r="D33" s="23"/>
+    </row>
+    <row r="34" spans="1:4" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A34" s="10" t="s">
         <v>32</v>
       </c>
-      <c r="B31" s="10" t="s">
-        <v>144</v>
-      </c>
-      <c r="C31" s="10">
-        <v>60</v>
-      </c>
-      <c r="D31" s="16">
-        <f>SUM(C31:C37)/100</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="32" spans="1:4" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A32" s="11" t="s">
-        <v>32</v>
-      </c>
-      <c r="B32" s="7" t="s">
-        <v>143</v>
-      </c>
-      <c r="C32" s="7">
-        <v>20</v>
-      </c>
-      <c r="D32" s="17"/>
-    </row>
-    <row r="33" spans="1:4" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A33" s="11" t="s">
-        <v>32</v>
-      </c>
-      <c r="B33" s="7" t="s">
+      <c r="B34" s="7" t="s">
         <v>111</v>
-      </c>
-      <c r="C33" s="7">
-        <v>5</v>
-      </c>
-      <c r="D33" s="17"/>
-    </row>
-    <row r="34" spans="1:4" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A34" s="11" t="s">
-        <v>32</v>
-      </c>
-      <c r="B34" s="7" t="s">
-        <v>112</v>
       </c>
       <c r="C34" s="7">
         <v>5</v>
       </c>
-      <c r="D34" s="17"/>
+      <c r="D34" s="23"/>
     </row>
     <row r="35" spans="1:4" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A35" s="11" t="s">
+      <c r="A35" s="10" t="s">
         <v>32</v>
       </c>
       <c r="B35" s="7" t="s">
-        <v>148</v>
+        <v>112</v>
       </c>
       <c r="C35" s="7">
         <v>5</v>
       </c>
-      <c r="D35" s="17"/>
+      <c r="D35" s="23"/>
     </row>
     <row r="36" spans="1:4" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A36" s="11" t="s">
+      <c r="A36" s="10" t="s">
         <v>32</v>
       </c>
       <c r="B36" s="7" t="s">
+        <v>148</v>
+      </c>
+      <c r="C36" s="7">
+        <v>5</v>
+      </c>
+      <c r="D36" s="23"/>
+    </row>
+    <row r="37" spans="1:4" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A37" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="B37" s="7" t="s">
         <v>149</v>
       </c>
-      <c r="C36" s="7">
+      <c r="C37" s="7">
         <v>3</v>
       </c>
-      <c r="D36" s="17"/>
-    </row>
-    <row r="37" spans="1:4" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A37" s="12" t="s">
+      <c r="D37" s="23"/>
+    </row>
+    <row r="38" spans="1:4" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A38" s="11" t="s">
         <v>32</v>
       </c>
-      <c r="B37" s="13" t="s">
+      <c r="B38" s="12" t="s">
         <v>113</v>
       </c>
-      <c r="C37" s="13">
+      <c r="C38" s="12">
         <v>2</v>
       </c>
-      <c r="D37" s="18"/>
-    </row>
-    <row r="38" spans="1:4" ht="17.25" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
-      <c r="A38" s="9" t="s">
+      <c r="D38" s="24"/>
+    </row>
+    <row r="39" spans="1:4" ht="17.25" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
+      <c r="A39" s="8" t="s">
         <v>36</v>
       </c>
-      <c r="B38" s="10" t="s">
+      <c r="B39" s="9" t="s">
         <v>110</v>
       </c>
-      <c r="C38" s="10">
+      <c r="C39" s="9">
         <v>60</v>
       </c>
-      <c r="D38" s="16">
-        <f>SUM(C38:C47)/100</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="39" spans="1:4" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A39" s="11" t="s">
+      <c r="D39" s="22">
+        <f>SUM(C39:C48)/100</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="40" spans="1:4" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A40" s="10" t="s">
         <v>36</v>
       </c>
-      <c r="B39" s="7" t="s">
+      <c r="B40" s="7" t="s">
         <v>145</v>
-      </c>
-      <c r="C39" s="7">
-        <v>10</v>
-      </c>
-      <c r="D39" s="17"/>
-    </row>
-    <row r="40" spans="1:4" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A40" s="11" t="s">
-        <v>36</v>
-      </c>
-      <c r="B40" s="7" t="s">
-        <v>115</v>
       </c>
       <c r="C40" s="7">
         <v>10</v>
       </c>
-      <c r="D40" s="17"/>
+      <c r="D40" s="23"/>
     </row>
     <row r="41" spans="1:4" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A41" s="11" t="s">
+      <c r="A41" s="10" t="s">
         <v>36</v>
       </c>
       <c r="B41" s="7" t="s">
+        <v>115</v>
+      </c>
+      <c r="C41" s="7">
+        <v>10</v>
+      </c>
+      <c r="D41" s="23"/>
+    </row>
+    <row r="42" spans="1:4" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A42" s="10" t="s">
+        <v>36</v>
+      </c>
+      <c r="B42" s="7" t="s">
         <v>116</v>
       </c>
-      <c r="C41" s="7">
+      <c r="C42" s="7">
         <v>8</v>
       </c>
-      <c r="D41" s="17"/>
-    </row>
-    <row r="42" spans="1:4" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A42" s="11" t="s">
+      <c r="D42" s="23"/>
+    </row>
+    <row r="43" spans="1:4" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A43" s="10" t="s">
         <v>36</v>
       </c>
-      <c r="B42" s="7" t="s">
+      <c r="B43" s="7" t="s">
         <v>117</v>
       </c>
-      <c r="C42" s="7">
+      <c r="C43" s="7">
         <v>5</v>
       </c>
-      <c r="D42" s="17"/>
-    </row>
-    <row r="43" spans="1:4" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A43" s="11" t="s">
+      <c r="D43" s="23"/>
+    </row>
+    <row r="44" spans="1:4" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A44" s="10" t="s">
         <v>36</v>
       </c>
-      <c r="B43" s="7" t="s">
+      <c r="B44" s="7" t="s">
         <v>118</v>
-      </c>
-      <c r="C43" s="7">
-        <v>2</v>
-      </c>
-      <c r="D43" s="17"/>
-    </row>
-    <row r="44" spans="1:4" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A44" s="11" t="s">
-        <v>36</v>
-      </c>
-      <c r="B44" s="7" t="s">
-        <v>119</v>
       </c>
       <c r="C44" s="7">
         <v>2</v>
       </c>
-      <c r="D44" s="17"/>
-    </row>
-    <row r="45" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A45" s="11" t="s">
+      <c r="D44" s="23"/>
+    </row>
+    <row r="45" spans="1:4" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A45" s="10" t="s">
         <v>36</v>
       </c>
       <c r="B45" s="7" t="s">
+        <v>119</v>
+      </c>
+      <c r="C45" s="7">
+        <v>2</v>
+      </c>
+      <c r="D45" s="23"/>
+    </row>
+    <row r="46" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A46" s="10" t="s">
+        <v>36</v>
+      </c>
+      <c r="B46" s="7" t="s">
         <v>120</v>
       </c>
-      <c r="C45" s="7">
-        <v>1</v>
-      </c>
-      <c r="D45" s="17"/>
-    </row>
-    <row r="46" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A46" s="11" t="s">
+      <c r="C46" s="7">
+        <v>1</v>
+      </c>
+      <c r="D46" s="23"/>
+    </row>
+    <row r="47" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A47" s="10" t="s">
         <v>36</v>
       </c>
-      <c r="B46" s="7" t="s">
+      <c r="B47" s="7" t="s">
         <v>121</v>
       </c>
-      <c r="C46" s="7">
-        <v>1</v>
-      </c>
-      <c r="D46" s="17"/>
-    </row>
-    <row r="47" spans="1:4" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A47" s="12" t="s">
+      <c r="C47" s="7">
+        <v>1</v>
+      </c>
+      <c r="D47" s="23"/>
+    </row>
+    <row r="48" spans="1:4" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A48" s="11" t="s">
         <v>36</v>
       </c>
-      <c r="B47" s="13" t="s">
+      <c r="B48" s="12" t="s">
         <v>122</v>
       </c>
-      <c r="C47" s="13">
-        <v>1</v>
-      </c>
-      <c r="D47" s="18"/>
-    </row>
-    <row r="48" spans="1:4" ht="17.25" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
-      <c r="A48" s="9" t="s">
+      <c r="C48" s="12">
+        <v>1</v>
+      </c>
+      <c r="D48" s="24"/>
+    </row>
+    <row r="49" spans="1:11" ht="17.25" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
+      <c r="A49" s="8" t="s">
         <v>40</v>
       </c>
-      <c r="B48" s="10" t="s">
+      <c r="B49" s="9" t="s">
         <v>114</v>
       </c>
-      <c r="C48" s="10">
+      <c r="C49" s="9">
         <v>60</v>
       </c>
-      <c r="D48" s="16">
-        <f>SUM(C48:C55)/100</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="49" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A49" s="11" t="s">
+      <c r="D49" s="22">
+        <f>SUM(C49:C56)/100</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="50" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A50" s="10" t="s">
         <v>40</v>
       </c>
-      <c r="B49" s="7" t="s">
+      <c r="B50" s="7" t="s">
         <v>123</v>
       </c>
-      <c r="C49" s="7">
+      <c r="C50" s="7">
         <v>20</v>
       </c>
-      <c r="D49" s="17"/>
-    </row>
-    <row r="50" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A50" s="11" t="s">
+      <c r="D50" s="23"/>
+    </row>
+    <row r="51" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A51" s="10" t="s">
         <v>40</v>
       </c>
-      <c r="B50" s="7" t="s">
+      <c r="B51" s="7" t="s">
         <v>124</v>
       </c>
-      <c r="C50" s="7">
+      <c r="C51" s="7">
         <v>9</v>
       </c>
-      <c r="D50" s="17"/>
-    </row>
-    <row r="51" spans="1:11" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A51" s="11" t="s">
+      <c r="D51" s="23"/>
+    </row>
+    <row r="52" spans="1:11" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A52" s="10" t="s">
         <v>40</v>
       </c>
-      <c r="B51" s="7" t="s">
+      <c r="B52" s="7" t="s">
         <v>118</v>
-      </c>
-      <c r="C51" s="7">
-        <v>4</v>
-      </c>
-      <c r="D51" s="17"/>
-    </row>
-    <row r="52" spans="1:11" ht="17.25" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
-      <c r="A52" s="11" t="s">
-        <v>40</v>
-      </c>
-      <c r="B52" s="7" t="s">
-        <v>119</v>
       </c>
       <c r="C52" s="7">
         <v>4</v>
       </c>
-      <c r="D52" s="17"/>
-      <c r="I52" s="10" t="s">
+      <c r="D52" s="23"/>
+    </row>
+    <row r="53" spans="1:11" ht="17.25" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
+      <c r="A53" s="10" t="s">
+        <v>40</v>
+      </c>
+      <c r="B53" s="7" t="s">
+        <v>119</v>
+      </c>
+      <c r="C53" s="7">
+        <v>4</v>
+      </c>
+      <c r="D53" s="23"/>
+      <c r="I53" s="9" t="s">
         <v>58</v>
       </c>
-      <c r="J52" s="7" t="s">
+      <c r="J53" s="7" t="s">
         <v>118</v>
-      </c>
-      <c r="K52" s="7">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="53" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A53" s="11" t="s">
-        <v>40</v>
-      </c>
-      <c r="B53" s="7" t="s">
-        <v>125</v>
-      </c>
-      <c r="C53" s="7">
-        <v>1</v>
-      </c>
-      <c r="D53" s="17"/>
-      <c r="I53" s="7" t="s">
-        <v>58</v>
-      </c>
-      <c r="J53" s="7" t="s">
-        <v>119</v>
       </c>
       <c r="K53" s="7">
         <v>30</v>
       </c>
     </row>
     <row r="54" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A54" s="11" t="s">
+      <c r="A54" s="10" t="s">
         <v>40</v>
       </c>
       <c r="B54" s="7" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C54" s="7">
         <v>1</v>
       </c>
-      <c r="D54" s="17"/>
+      <c r="D54" s="23"/>
       <c r="I54" s="7" t="s">
         <v>58</v>
       </c>
       <c r="J54" s="7" t="s">
-        <v>127</v>
+        <v>119</v>
       </c>
       <c r="K54" s="7">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="55" spans="1:11" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A55" s="12" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="55" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A55" s="10" t="s">
         <v>40</v>
       </c>
-      <c r="B55" s="13" t="s">
-        <v>128</v>
-      </c>
-      <c r="C55" s="13">
-        <v>1</v>
-      </c>
-      <c r="D55" s="18"/>
+      <c r="B55" s="7" t="s">
+        <v>126</v>
+      </c>
+      <c r="C55" s="7">
+        <v>1</v>
+      </c>
+      <c r="D55" s="23"/>
       <c r="I55" s="7" t="s">
         <v>58</v>
       </c>
       <c r="J55" s="7" t="s">
-        <v>109</v>
+        <v>127</v>
       </c>
       <c r="K55" s="7">
         <v>15</v>
       </c>
     </row>
-    <row r="56" spans="1:11" ht="17.25" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A56" s="9" t="s">
+    <row r="56" spans="1:11" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A56" s="11" t="s">
+        <v>40</v>
+      </c>
+      <c r="B56" s="12" t="s">
+        <v>128</v>
+      </c>
+      <c r="C56" s="12">
+        <v>1</v>
+      </c>
+      <c r="D56" s="24"/>
+      <c r="I56" s="7" t="s">
+        <v>58</v>
+      </c>
+      <c r="J56" s="7" t="s">
+        <v>109</v>
+      </c>
+      <c r="K56" s="7">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="57" spans="1:11" ht="17.25" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A57" s="8" t="s">
         <v>43</v>
       </c>
-      <c r="B56" s="10" t="s">
+      <c r="B57" s="9" t="s">
         <v>140</v>
       </c>
-      <c r="C56" s="10">
+      <c r="C57" s="9">
         <v>51</v>
       </c>
-      <c r="D56" s="16">
-        <f>SUM(C56:C64)/100</f>
-        <v>1</v>
-      </c>
-      <c r="I56" s="13" t="s">
+      <c r="D57" s="22">
+        <f>SUM(C57:C65)/100</f>
+        <v>1</v>
+      </c>
+      <c r="I57" s="12" t="s">
         <v>58</v>
       </c>
-      <c r="J56" s="13" t="s">
+      <c r="J57" s="12" t="s">
         <v>129</v>
       </c>
-      <c r="K56" s="13">
+      <c r="K57" s="12">
         <v>10</v>
       </c>
     </row>
-    <row r="57" spans="1:11" ht="17.25" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
-      <c r="A57" s="11" t="s">
+    <row r="58" spans="1:11" ht="17.25" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
+      <c r="A58" s="10" t="s">
         <v>43</v>
       </c>
-      <c r="B57" s="7" t="s">
+      <c r="B58" s="7" t="s">
         <v>104</v>
       </c>
-      <c r="C57" s="7">
+      <c r="C58" s="7">
         <v>20</v>
       </c>
-      <c r="D57" s="17"/>
-      <c r="I57" s="11"/>
-      <c r="J57" s="7"/>
-      <c r="K57" s="7"/>
-    </row>
-    <row r="58" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A58" s="11" t="s">
-        <v>43</v>
-      </c>
-      <c r="B58" s="7" t="s">
-        <v>130</v>
-      </c>
-      <c r="C58" s="7">
-        <v>8</v>
-      </c>
-      <c r="D58" s="17"/>
-      <c r="I58" s="11"/>
+      <c r="D58" s="23"/>
+      <c r="I58" s="10"/>
       <c r="J58" s="7"/>
       <c r="K58" s="7"/>
     </row>
     <row r="59" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A59" s="11" t="s">
+      <c r="A59" s="10" t="s">
         <v>43</v>
       </c>
       <c r="B59" s="7" t="s">
-        <v>118</v>
+        <v>130</v>
       </c>
       <c r="C59" s="7">
         <v>8</v>
       </c>
-      <c r="D59" s="17"/>
-      <c r="I59" s="11"/>
+      <c r="D59" s="23"/>
+      <c r="I59" s="10"/>
       <c r="J59" s="7"/>
       <c r="K59" s="7"/>
     </row>
     <row r="60" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A60" s="11" t="s">
+      <c r="A60" s="10" t="s">
         <v>43</v>
       </c>
       <c r="B60" s="7" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="C60" s="7">
         <v>8</v>
       </c>
-      <c r="D60" s="17"/>
-      <c r="I60" s="11"/>
+      <c r="D60" s="23"/>
+      <c r="I60" s="10"/>
       <c r="J60" s="7"/>
       <c r="K60" s="7"/>
     </row>
-    <row r="61" spans="1:11" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A61" s="11" t="s">
+    <row r="61" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A61" s="10" t="s">
         <v>43</v>
       </c>
       <c r="B61" s="7" t="s">
+        <v>119</v>
+      </c>
+      <c r="C61" s="7">
+        <v>8</v>
+      </c>
+      <c r="D61" s="23"/>
+      <c r="I61" s="10"/>
+      <c r="J61" s="7"/>
+      <c r="K61" s="7"/>
+    </row>
+    <row r="62" spans="1:11" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A62" s="10" t="s">
+        <v>43</v>
+      </c>
+      <c r="B62" s="7" t="s">
         <v>107</v>
       </c>
-      <c r="C61" s="7">
+      <c r="C62" s="7">
         <v>2</v>
       </c>
-      <c r="D61" s="17"/>
-      <c r="I61" s="12"/>
-      <c r="J61" s="13"/>
-      <c r="K61" s="13"/>
-    </row>
-    <row r="62" spans="1:11" ht="17.25" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
-      <c r="A62" s="11" t="s">
+      <c r="D62" s="23"/>
+      <c r="I62" s="11"/>
+      <c r="J62" s="12"/>
+      <c r="K62" s="12"/>
+    </row>
+    <row r="63" spans="1:11" ht="17.25" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
+      <c r="A63" s="10" t="s">
         <v>43</v>
       </c>
-      <c r="B62" s="7" t="s">
+      <c r="B63" s="7" t="s">
         <v>131</v>
       </c>
-      <c r="C62" s="7">
-        <v>1</v>
-      </c>
-      <c r="D62" s="17"/>
-    </row>
-    <row r="63" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A63" s="11" t="s">
+      <c r="C63" s="7">
+        <v>1</v>
+      </c>
+      <c r="D63" s="23"/>
+    </row>
+    <row r="64" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A64" s="10" t="s">
         <v>43</v>
       </c>
-      <c r="B63" s="7" t="s">
+      <c r="B64" s="7" t="s">
         <v>132</v>
       </c>
-      <c r="C63" s="7">
-        <v>1</v>
-      </c>
-      <c r="D63" s="17"/>
-    </row>
-    <row r="64" spans="1:11" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A64" s="12" t="s">
+      <c r="C64" s="7">
+        <v>1</v>
+      </c>
+      <c r="D64" s="23"/>
+    </row>
+    <row r="65" spans="1:6" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A65" s="11" t="s">
         <v>43</v>
       </c>
-      <c r="B64" s="13" t="s">
+      <c r="B65" s="12" t="s">
         <v>133</v>
       </c>
-      <c r="C64" s="13">
-        <v>1</v>
-      </c>
-      <c r="D64" s="18"/>
-    </row>
-    <row r="65" spans="1:6" ht="17.25" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
-      <c r="A65" s="10" t="s">
+      <c r="C65" s="12">
+        <v>1</v>
+      </c>
+      <c r="D65" s="24"/>
+    </row>
+    <row r="66" spans="1:6" ht="17.25" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
+      <c r="A66" s="9" t="s">
         <v>47</v>
       </c>
-      <c r="B65" s="10" t="s">
+      <c r="B66" s="9" t="s">
         <v>104</v>
       </c>
-      <c r="C65" s="10">
+      <c r="C66" s="9">
         <v>50</v>
       </c>
-      <c r="D65" s="16">
-        <f>SUM(C65:C72)/100</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="66" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A66" s="7" t="s">
-        <v>47</v>
-      </c>
-      <c r="B66" s="7" t="s">
-        <v>118</v>
-      </c>
-      <c r="C66" s="7">
-        <v>16</v>
-      </c>
-      <c r="D66" s="17"/>
+      <c r="D66" s="22">
+        <f>SUM(C66:C73)/100</f>
+        <v>1</v>
+      </c>
     </row>
     <row r="67" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A67" s="7" t="s">
         <v>47</v>
       </c>
       <c r="B67" s="7" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="C67" s="7">
         <v>16</v>
       </c>
-      <c r="D67" s="17"/>
+      <c r="D67" s="23"/>
     </row>
     <row r="68" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A68" s="7" t="s">
         <v>47</v>
       </c>
       <c r="B68" s="7" t="s">
-        <v>106</v>
+        <v>119</v>
       </c>
       <c r="C68" s="7">
-        <v>12</v>
-      </c>
-      <c r="D68" s="17"/>
+        <v>16</v>
+      </c>
+      <c r="D68" s="23"/>
     </row>
     <row r="69" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A69" s="7" t="s">
         <v>47</v>
       </c>
       <c r="B69" s="7" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="C69" s="7">
-        <v>2</v>
-      </c>
-      <c r="D69" s="17"/>
+        <v>12</v>
+      </c>
+      <c r="D69" s="23"/>
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A70" s="7" t="s">
         <v>47</v>
       </c>
-      <c r="B70" s="14" t="s">
-        <v>151</v>
+      <c r="B70" s="7" t="s">
+        <v>108</v>
       </c>
       <c r="C70" s="7">
         <v>2</v>
       </c>
-      <c r="D70" s="17"/>
+      <c r="D70" s="23"/>
     </row>
     <row r="71" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A71" s="7" t="s">
         <v>47</v>
       </c>
-      <c r="B71" s="7" t="s">
+      <c r="B71" s="13" t="s">
+        <v>151</v>
+      </c>
+      <c r="C71" s="7">
+        <v>2</v>
+      </c>
+      <c r="D71" s="23"/>
+    </row>
+    <row r="72" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A72" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="B72" s="7" t="s">
         <v>131</v>
       </c>
-      <c r="C71" s="7">
-        <v>1</v>
-      </c>
-      <c r="D71" s="17"/>
-    </row>
-    <row r="72" spans="1:6" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A72" s="13" t="s">
+      <c r="C72" s="7">
+        <v>1</v>
+      </c>
+      <c r="D72" s="23"/>
+    </row>
+    <row r="73" spans="1:6" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A73" s="12" t="s">
         <v>47</v>
       </c>
-      <c r="B72" s="13" t="s">
+      <c r="B73" s="12" t="s">
         <v>134</v>
       </c>
-      <c r="C72" s="13">
-        <v>1</v>
-      </c>
-      <c r="D72" s="18"/>
-    </row>
-    <row r="73" spans="1:6" ht="17.25" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A73" s="10" t="s">
+      <c r="C73" s="12">
+        <v>1</v>
+      </c>
+      <c r="D73" s="24"/>
+    </row>
+    <row r="74" spans="1:6" ht="17.25" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A74" s="9" t="s">
         <v>51</v>
       </c>
-      <c r="B73" s="10" t="s">
+      <c r="B74" s="9" t="s">
         <v>104</v>
       </c>
-      <c r="C73" s="10">
+      <c r="C74" s="9">
         <v>20</v>
       </c>
-      <c r="D73" s="16">
-        <f>SUM(C73:C85)/100</f>
-        <v>1</v>
-      </c>
-      <c r="F73" s="14"/>
-    </row>
-    <row r="74" spans="1:6" ht="17.25" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
-      <c r="A74" s="7" t="s">
-        <v>51</v>
-      </c>
-      <c r="B74" s="7" t="s">
-        <v>118</v>
-      </c>
-      <c r="C74" s="7">
-        <v>18</v>
-      </c>
-      <c r="D74" s="17"/>
-    </row>
-    <row r="75" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="D74" s="22">
+        <f>SUM(C74:C86)/100</f>
+        <v>1</v>
+      </c>
+      <c r="F74" s="13"/>
+    </row>
+    <row r="75" spans="1:6" ht="17.25" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
       <c r="A75" s="7" t="s">
         <v>51</v>
       </c>
       <c r="B75" s="7" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="C75" s="7">
         <v>18</v>
       </c>
-      <c r="D75" s="17"/>
+      <c r="D75" s="23"/>
     </row>
     <row r="76" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A76" s="7" t="s">
         <v>51</v>
       </c>
       <c r="B76" s="7" t="s">
-        <v>109</v>
+        <v>119</v>
       </c>
       <c r="C76" s="7">
-        <v>10</v>
-      </c>
-      <c r="D76" s="17"/>
+        <v>18</v>
+      </c>
+      <c r="D76" s="23"/>
     </row>
     <row r="77" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A77" s="7" t="s">
         <v>51</v>
       </c>
       <c r="B77" s="7" t="s">
-        <v>127</v>
+        <v>109</v>
       </c>
       <c r="C77" s="7">
         <v>10</v>
       </c>
-      <c r="D77" s="17"/>
-    </row>
-    <row r="78" spans="1:6" s="14" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="D77" s="23"/>
+    </row>
+    <row r="78" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A78" s="7" t="s">
         <v>51</v>
       </c>
       <c r="B78" s="7" t="s">
-        <v>152</v>
+        <v>127</v>
       </c>
       <c r="C78" s="7">
-        <v>6</v>
-      </c>
-      <c r="D78" s="17"/>
-    </row>
-    <row r="79" spans="1:6" x14ac:dyDescent="0.3">
+        <v>10</v>
+      </c>
+      <c r="D78" s="23"/>
+    </row>
+    <row r="79" spans="1:6" s="13" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A79" s="7" t="s">
         <v>51</v>
       </c>
       <c r="B79" s="7" t="s">
-        <v>129</v>
+        <v>152</v>
       </c>
       <c r="C79" s="7">
-        <v>3</v>
-      </c>
-      <c r="D79" s="17"/>
+        <v>6</v>
+      </c>
+      <c r="D79" s="23"/>
     </row>
     <row r="80" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A80" s="7" t="s">
         <v>51</v>
       </c>
       <c r="B80" s="7" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="C80" s="7">
-        <v>2</v>
-      </c>
-      <c r="D80" s="17"/>
+        <v>3</v>
+      </c>
+      <c r="D80" s="23"/>
     </row>
     <row r="81" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A81" s="7" t="s">
         <v>51</v>
       </c>
       <c r="B81" s="7" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="C81" s="7">
-        <v>3</v>
-      </c>
-      <c r="D81" s="17"/>
+        <v>2</v>
+      </c>
+      <c r="D81" s="23"/>
     </row>
     <row r="82" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A82" s="7" t="s">
         <v>51</v>
       </c>
       <c r="B82" s="7" t="s">
-        <v>133</v>
+        <v>128</v>
       </c>
       <c r="C82" s="7">
         <v>3</v>
       </c>
-      <c r="D82" s="17"/>
+      <c r="D82" s="23"/>
     </row>
     <row r="83" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A83" s="7" t="s">
         <v>51</v>
       </c>
       <c r="B83" s="7" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C83" s="7">
         <v>3</v>
       </c>
-      <c r="D83" s="17"/>
-    </row>
-    <row r="84" spans="1:4" s="14" customFormat="1" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="D83" s="23"/>
+    </row>
+    <row r="84" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A84" s="7" t="s">
         <v>51</v>
       </c>
       <c r="B84" s="7" t="s">
-        <v>122</v>
+        <v>134</v>
       </c>
       <c r="C84" s="7">
         <v>3</v>
       </c>
-      <c r="D84" s="17"/>
-    </row>
-    <row r="85" spans="1:4" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A85" s="13" t="s">
+      <c r="D84" s="23"/>
+    </row>
+    <row r="85" spans="1:4" s="13" customFormat="1" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A85" s="7" t="s">
         <v>51</v>
       </c>
-      <c r="B85" s="13" t="s">
+      <c r="B85" s="7" t="s">
+        <v>122</v>
+      </c>
+      <c r="C85" s="7">
+        <v>3</v>
+      </c>
+      <c r="D85" s="23"/>
+    </row>
+    <row r="86" spans="1:4" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A86" s="12" t="s">
+        <v>51</v>
+      </c>
+      <c r="B86" s="12" t="s">
         <v>150</v>
       </c>
-      <c r="C85" s="13">
-        <v>1</v>
-      </c>
-      <c r="D85" s="18"/>
-    </row>
-    <row r="86" spans="1:4" ht="17.25" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A86" s="10" t="s">
+      <c r="C86" s="12">
+        <v>1</v>
+      </c>
+      <c r="D86" s="24"/>
+    </row>
+    <row r="87" spans="1:4" ht="17.25" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A87" s="9" t="s">
         <v>58</v>
       </c>
-      <c r="B86" s="10" t="s">
+      <c r="B87" s="9" t="s">
         <v>118</v>
       </c>
-      <c r="C86" s="10">
+      <c r="C87" s="9">
         <v>30</v>
       </c>
-      <c r="D86" s="16">
-        <f>SUM(C86:C92)/100</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="87" spans="1:4" ht="17.25" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
-      <c r="A87" s="7" t="s">
-        <v>58</v>
-      </c>
-      <c r="B87" s="7" t="s">
-        <v>119</v>
-      </c>
-      <c r="C87" s="7">
-        <v>28</v>
-      </c>
-      <c r="D87" s="17"/>
-    </row>
-    <row r="88" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="D87" s="22">
+        <f>SUM(C87:C93)/100</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="88" spans="1:4" ht="17.25" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
       <c r="A88" s="7" t="s">
         <v>58</v>
       </c>
       <c r="B88" s="7" t="s">
-        <v>127</v>
+        <v>119</v>
       </c>
       <c r="C88" s="7">
-        <v>10</v>
-      </c>
-      <c r="D88" s="17"/>
-    </row>
-    <row r="89" spans="1:4" s="14" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+        <v>28</v>
+      </c>
+      <c r="D88" s="23"/>
+    </row>
+    <row r="89" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A89" s="7" t="s">
         <v>58</v>
       </c>
       <c r="B89" s="7" t="s">
-        <v>109</v>
+        <v>127</v>
       </c>
       <c r="C89" s="7">
         <v>10</v>
       </c>
-      <c r="D89" s="17"/>
-    </row>
-    <row r="90" spans="1:4" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="D89" s="23"/>
+    </row>
+    <row r="90" spans="1:4" s="13" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A90" s="7" t="s">
         <v>58</v>
       </c>
       <c r="B90" s="7" t="s">
-        <v>129</v>
+        <v>109</v>
       </c>
       <c r="C90" s="7">
         <v>10</v>
       </c>
-      <c r="D90" s="17"/>
-    </row>
-    <row r="91" spans="1:4" s="14" customFormat="1" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="D90" s="23"/>
+    </row>
+    <row r="91" spans="1:4" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A91" s="7" t="s">
         <v>58</v>
       </c>
-      <c r="B91" s="21" t="s">
-        <v>151</v>
+      <c r="B91" s="7" t="s">
+        <v>129</v>
       </c>
       <c r="C91" s="7">
         <v>10</v>
       </c>
-      <c r="D91" s="17"/>
-    </row>
-    <row r="92" spans="1:4" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A92" s="13" t="s">
+      <c r="D91" s="23"/>
+    </row>
+    <row r="92" spans="1:4" s="13" customFormat="1" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A92" s="7" t="s">
         <v>58</v>
       </c>
-      <c r="B92" s="13" t="s">
+      <c r="B92" s="15" t="s">
+        <v>152</v>
+      </c>
+      <c r="C92" s="7">
+        <v>10</v>
+      </c>
+      <c r="D92" s="23"/>
+    </row>
+    <row r="93" spans="1:4" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A93" s="12" t="s">
+        <v>58</v>
+      </c>
+      <c r="B93" s="12" t="s">
         <v>150</v>
       </c>
-      <c r="C92" s="13">
+      <c r="C93" s="12">
         <v>2</v>
       </c>
-      <c r="D92" s="18"/>
-    </row>
-    <row r="93" spans="1:4" ht="17.25" customHeight="1" thickTop="1" x14ac:dyDescent="0.3"/>
-    <row r="94" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A94"/>
-      <c r="B94"/>
-      <c r="C94"/>
-      <c r="D94"/>
+      <c r="D93" s="24"/>
+    </row>
+    <row r="94" spans="1:4" ht="17.25" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
+      <c r="A94" s="8" t="s">
+        <v>154</v>
+      </c>
+      <c r="B94" s="9" t="s">
+        <v>127</v>
+      </c>
+      <c r="C94" s="9">
+        <v>55</v>
+      </c>
+      <c r="D94" s="19">
+        <f>SUM(C94:C97)/100</f>
+        <v>1</v>
+      </c>
     </row>
     <row r="95" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A95"/>
-      <c r="B95"/>
-      <c r="C95"/>
+      <c r="A95" s="10" t="s">
+        <v>153</v>
+      </c>
+      <c r="B95" s="7" t="s">
+        <v>129</v>
+      </c>
+      <c r="C95" s="7">
+        <v>20</v>
+      </c>
+      <c r="D95" s="20"/>
     </row>
     <row r="96" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A96"/>
-      <c r="B96"/>
-      <c r="C96"/>
-    </row>
-    <row r="97" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A97"/>
-      <c r="B97"/>
-      <c r="C97"/>
-    </row>
-    <row r="98" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A96" s="10" t="s">
+        <v>153</v>
+      </c>
+      <c r="B96" s="15" t="s">
+        <v>152</v>
+      </c>
+      <c r="C96" s="7">
+        <v>20</v>
+      </c>
+      <c r="D96" s="20"/>
+    </row>
+    <row r="97" spans="1:4" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A97" s="11" t="s">
+        <v>153</v>
+      </c>
+      <c r="B97" s="12" t="s">
+        <v>155</v>
+      </c>
+      <c r="C97" s="12">
+        <v>5</v>
+      </c>
+      <c r="D97" s="21"/>
+    </row>
+    <row r="98" spans="1:4" ht="17.25" thickTop="1" x14ac:dyDescent="0.3">
       <c r="A98"/>
       <c r="B98"/>
       <c r="C98"/>
     </row>
-    <row r="99" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A99"/>
       <c r="B99"/>
       <c r="C99"/>
     </row>
-    <row r="100" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A100"/>
       <c r="B100"/>
       <c r="C100"/>
     </row>
-    <row r="101" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A101"/>
       <c r="B101"/>
       <c r="C101"/>
     </row>
-    <row r="102" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A102"/>
       <c r="B102"/>
       <c r="C102"/>
     </row>
-    <row r="103" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A103"/>
       <c r="B103"/>
       <c r="C103"/>
     </row>
-    <row r="104" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A104"/>
-      <c r="B104"/>
-      <c r="C104"/>
-    </row>
-    <row r="105" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A105"/>
-      <c r="B105"/>
-      <c r="C105"/>
-    </row>
   </sheetData>
-  <autoFilter ref="I51:K51" xr:uid="{00000000-0009-0000-0000-000001000000}">
-    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="I52:K56">
-      <sortCondition descending="1" ref="K51"/>
+  <autoFilter ref="I52:K52" xr:uid="{00000000-0009-0000-0000-000001000000}">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="I53:K57">
+      <sortCondition descending="1" ref="K52"/>
     </sortState>
   </autoFilter>
-  <mergeCells count="12">
-    <mergeCell ref="D86:D92"/>
-    <mergeCell ref="D31:D37"/>
-    <mergeCell ref="D56:D64"/>
-    <mergeCell ref="D17:D18"/>
-    <mergeCell ref="D19:D20"/>
-    <mergeCell ref="D21:D22"/>
-    <mergeCell ref="D23:D24"/>
-    <mergeCell ref="D73:D85"/>
-    <mergeCell ref="D48:D55"/>
-    <mergeCell ref="D65:D72"/>
-    <mergeCell ref="D38:D47"/>
-    <mergeCell ref="D25:D30"/>
+  <mergeCells count="13">
+    <mergeCell ref="D94:D97"/>
+    <mergeCell ref="D87:D93"/>
+    <mergeCell ref="D32:D38"/>
+    <mergeCell ref="D57:D65"/>
+    <mergeCell ref="D17:D19"/>
+    <mergeCell ref="D20:D21"/>
+    <mergeCell ref="D22:D23"/>
+    <mergeCell ref="D24:D25"/>
+    <mergeCell ref="D74:D86"/>
+    <mergeCell ref="D49:D56"/>
+    <mergeCell ref="D66:D73"/>
+    <mergeCell ref="D39:D48"/>
+    <mergeCell ref="D26:D31"/>
   </mergeCells>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
